--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="440">
   <si>
     <r>
       <rPr>
@@ -1984,6 +1984,9 @@
   </si>
   <si>
     <t xml:space="preserve">Personal allowance taper threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special rate writing down allowance</t>
   </si>
   <si>
     <t xml:space="preserve">Basic rate applicable on taxable income up to higher rate</t>
@@ -4392,7 +4395,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="I1">
-            <v>13740</v>
+            <v>17740</v>
           </cell>
         </row>
         <row r="1">
@@ -4403,7 +4406,7 @@
             <v>3360</v>
           </cell>
           <cell r="S1">
-            <v>20640</v>
+            <v>29100</v>
           </cell>
         </row>
         <row r="1">
@@ -4421,6 +4424,11 @@
           </cell>
           <cell r="Z1">
             <v>0</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>540</v>
           </cell>
         </row>
       </sheetData>
@@ -7774,7 +7782,9 @@
       <c r="N50" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="O50" s="41"/>
+      <c r="O50" s="41" t="n">
+        <v>640</v>
+      </c>
       <c r="P50" s="41"/>
       <c r="Q50" s="41"/>
       <c r="R50" s="42" t="s">
@@ -8172,13 +8182,17 @@
         <v>46173</v>
       </c>
       <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
+      <c r="D6" s="63" t="s">
+        <v>405</v>
+      </c>
       <c r="E6" s="63"/>
       <c r="F6" s="63"/>
-      <c r="G6" s="353"/>
+      <c r="G6" s="357" t="n">
+        <v>0.06</v>
+      </c>
       <c r="H6" s="63"/>
       <c r="I6" s="356" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J6" s="356"/>
       <c r="K6" s="356"/>
@@ -8188,7 +8202,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="353" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8198,14 +8212,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="356" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E7" s="356"/>
       <c r="F7" s="356"/>
       <c r="G7" s="353"/>
       <c r="H7" s="63"/>
       <c r="I7" s="356" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J7" s="356"/>
       <c r="K7" s="356"/>
@@ -8215,7 +8229,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="353" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8230,7 +8244,7 @@
       <c r="G8" s="359"/>
       <c r="H8" s="63"/>
       <c r="I8" s="356" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J8" s="356"/>
       <c r="K8" s="356"/>
@@ -8240,7 +8254,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="353" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8255,18 +8269,18 @@
       <c r="G9" s="353"/>
       <c r="H9" s="63"/>
       <c r="I9" s="356" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J9" s="356"/>
       <c r="K9" s="356"/>
       <c r="L9" s="360" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M9" s="360" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N9" s="361" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O9" s="353"/>
     </row>
@@ -8296,16 +8310,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="349" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E11" s="349"/>
       <c r="F11" s="349"/>
       <c r="G11" s="353" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="362" t="n">
@@ -8335,7 +8349,7 @@
       <c r="G12" s="353"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="362" t="n">
@@ -8357,7 +8371,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="356" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E13" s="356"/>
       <c r="F13" s="356"/>
@@ -8366,7 +8380,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="362" t="n">
@@ -8388,7 +8402,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="356" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -8397,7 +8411,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="349" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J14" s="349"/>
       <c r="K14" s="349"/>
@@ -8416,7 +8430,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="356" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E15" s="356"/>
       <c r="F15" s="356"/>
@@ -8439,7 +8453,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="356" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E16" s="356"/>
       <c r="F16" s="356"/>
@@ -8448,7 +8462,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="356" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J16" s="356"/>
       <c r="K16" s="356"/>
@@ -8456,7 +8470,7 @@
         <v>3.65</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N16" s="359" t="n">
         <v>7105</v>
@@ -8472,7 +8486,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="356" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E17" s="356"/>
       <c r="F17" s="356"/>
@@ -8514,24 +8528,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="349" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E19" s="349"/>
       <c r="F19" s="353" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G19" s="353" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="365" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J19" s="365"/>
       <c r="K19" s="365"/>
       <c r="L19" s="63"/>
       <c r="M19" s="366" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8568,7 +8582,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="356" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E21" s="356"/>
       <c r="F21" s="359" t="n">
@@ -8593,7 +8607,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="359" t="n">
@@ -8604,13 +8618,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="365" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J22" s="365"/>
       <c r="K22" s="365"/>
       <c r="L22" s="63"/>
       <c r="M22" s="366" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8618,7 +8632,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="355" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8643,11 +8657,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="355" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="349" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E24" s="349"/>
       <c r="F24" s="63"/>
@@ -8685,7 +8699,7 @@
       <c r="B26" s="369"/>
       <c r="C26" s="63"/>
       <c r="D26" s="356" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E26" s="356"/>
       <c r="F26" s="359" t="n">
@@ -8706,7 +8720,7 @@
       <c r="B27" s="369"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="357" t="n">
@@ -11175,8 +11189,8 @@
         <v>33</v>
       </c>
       <c r="O80" s="98" t="n">
-        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$Y$1)&gt;0,[1]Schedule!$R$1+[1]Schedule!$Y$1,0)</f>
-        <v>11500</v>
+        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$Y$1+[1]Schedule!$AC$1)&gt;0,[1]Schedule!$R$1+[1]Schedule!$Y$1+[1]Schedule!$AC$1,0)</f>
+        <v>12040</v>
       </c>
       <c r="P80" s="98"/>
       <c r="Q80" s="98"/>
@@ -11578,7 +11592,7 @@
       </c>
       <c r="D94" s="98" t="n">
         <f aca="false">'Business Details'!O50</f>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="E94" s="98"/>
       <c r="F94" s="98"/>
@@ -11737,7 +11751,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>128469.475166666</v>
+        <v>128569.475166666</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -11950,7 +11964,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>130552.8085</v>
+        <v>130652.8085</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -16050,7 +16064,7 @@
       </c>
       <c r="D114" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
-        <v>13912</v>
+        <v>17912</v>
       </c>
       <c r="E114" s="98"/>
       <c r="F114" s="98"/>
@@ -16072,7 +16086,7 @@
       </c>
       <c r="O114" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B34</f>
-        <v>13740</v>
+        <v>17740</v>
       </c>
       <c r="P114" s="98"/>
       <c r="Q114" s="98"/>
@@ -16308,7 +16322,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>169801.983333333</v>
+        <v>173801.983333333</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -16330,7 +16344,7 @@
       </c>
       <c r="O122" s="98" t="n">
         <f aca="false">O66+O70+O74+O78+O82+O86+O90+O94+O98+O102+O106+O110+O114+O118</f>
-        <v>23071.4585</v>
+        <v>27071.4585</v>
       </c>
       <c r="P122" s="98"/>
       <c r="Q122" s="98"/>
@@ -16519,7 +16533,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>169398.016666666</v>
+        <v>165398.016666666</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -17065,7 +17079,10 @@
       <c r="C147" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D147" s="98"/>
+      <c r="D147" s="98" t="n">
+        <f aca="false">[1]Schedule!$AC$1</f>
+        <v>540</v>
+      </c>
       <c r="E147" s="98"/>
       <c r="F147" s="98"/>
       <c r="G147" s="99" t="s">
@@ -17298,7 +17315,7 @@
       </c>
       <c r="O154" s="98" t="n">
         <f aca="false">D139+D144+D147+D152+D156+D160+O139+O144+O149</f>
-        <v>64000</v>
+        <v>68840</v>
       </c>
       <c r="P154" s="98"/>
       <c r="Q154" s="98"/>
@@ -17346,7 +17363,9 @@
       <c r="C156" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D156" s="98"/>
+      <c r="D156" s="98" t="n">
+        <v>2500</v>
+      </c>
       <c r="E156" s="98"/>
       <c r="F156" s="98"/>
       <c r="G156" s="99" t="s">
@@ -17466,7 +17485,9 @@
       <c r="C160" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D160" s="98"/>
+      <c r="D160" s="98" t="n">
+        <v>1800</v>
+      </c>
       <c r="E160" s="98"/>
       <c r="F160" s="98"/>
       <c r="G160" s="99" t="s">
@@ -17728,7 +17749,7 @@
       </c>
       <c r="D169" s="98" t="n">
         <f aca="false">'Business Details'!O50</f>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="E169" s="98"/>
       <c r="F169" s="98"/>
@@ -17750,7 +17771,7 @@
       </c>
       <c r="O169" s="98" t="n">
         <f aca="false">O154+D179</f>
-        <v>64000</v>
+        <v>69190</v>
       </c>
       <c r="P169" s="98"/>
       <c r="Q169" s="98"/>
@@ -17887,7 +17908,7 @@
       </c>
       <c r="D174" s="98" t="n">
         <f aca="false">O122+O160+D169</f>
-        <v>23071.4585</v>
+        <v>27711.4585</v>
       </c>
       <c r="E174" s="98"/>
       <c r="F174" s="98"/>
@@ -17909,7 +17930,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>128469.475166666</v>
+        <v>123919.475166666</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -18044,7 +18065,9 @@
       <c r="C179" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D179" s="98"/>
+      <c r="D179" s="98" t="n">
+        <v>350</v>
+      </c>
       <c r="E179" s="98"/>
       <c r="F179" s="98"/>
       <c r="G179" s="99" t="s">
@@ -18498,7 +18521,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">O174</f>
-        <v>128469.475166666</v>
+        <v>123919.475166666</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -18952,7 +18975,9 @@
       <c r="C210" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="98"/>
+      <c r="D210" s="98" t="n">
+        <v>90</v>
+      </c>
       <c r="E210" s="98"/>
       <c r="F210" s="98"/>
       <c r="G210" s="99" t="s">
@@ -18973,7 +18998,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>130552.8085</v>
+        <v>126002.8085</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -19219,7 +19244,7 @@
       </c>
       <c r="D219" s="98" t="n">
         <f aca="false">O179+E197+D210+P190</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E219" s="98"/>
       <c r="F219" s="98"/>
@@ -19397,7 +19422,7 @@
       </c>
       <c r="O224" s="98" t="n">
         <f aca="false">D219</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P224" s="98"/>
       <c r="Q224" s="98"/>
@@ -24022,55 +24047,55 @@
       </c>
       <c r="B34" s="171" t="n">
         <f aca="false">SUM(C34:N34)</f>
-        <v>13740</v>
+        <v>17740</v>
       </c>
       <c r="C34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="D34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="E34" s="173" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="F34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="G34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="H34" s="173" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="I34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="J34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="K34" s="173" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="L34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="M34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="N34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1145</v>
+        <v>1478.33333333333</v>
       </c>
       <c r="O34" s="165"/>
     </row>
@@ -24080,55 +24105,55 @@
       </c>
       <c r="B35" s="171" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>149665.316666667</v>
+        <v>153665.316666667</v>
       </c>
       <c r="C35" s="171" t="n">
         <f aca="false">SUM(C21:C34)</f>
-        <v>12012.7833333333</v>
+        <v>12346.1166666667</v>
       </c>
       <c r="D35" s="171" t="n">
         <f aca="false">SUM(D21:D34)</f>
-        <v>11323.5333333333</v>
+        <v>11656.8666666667</v>
       </c>
       <c r="E35" s="171" t="n">
         <f aca="false">SUM(E21:E34)</f>
-        <v>13592.8666666667</v>
+        <v>13926.2</v>
       </c>
       <c r="F35" s="175" t="n">
         <f aca="false">SUM(F21:F34)</f>
-        <v>13829.7833333333</v>
+        <v>14163.1166666667</v>
       </c>
       <c r="G35" s="171" t="n">
         <f aca="false">SUM(G21:G34)</f>
-        <v>11766.1166666667</v>
+        <v>12099.45</v>
       </c>
       <c r="H35" s="171" t="n">
         <f aca="false">SUM(H21:H34)</f>
-        <v>13242.8666666667</v>
+        <v>13576.2</v>
       </c>
       <c r="I35" s="175" t="n">
         <f aca="false">SUM(I21:I34)</f>
-        <v>13692.2833333333</v>
+        <v>14025.6166666667</v>
       </c>
       <c r="J35" s="171" t="n">
         <f aca="false">SUM(J21:J34)</f>
-        <v>10880.5333333333</v>
+        <v>11213.8666666667</v>
       </c>
       <c r="K35" s="171" t="n">
         <f aca="false">SUM(K21:K34)</f>
-        <v>15898.5333333333</v>
+        <v>16231.8666666667</v>
       </c>
       <c r="L35" s="175" t="n">
         <f aca="false">SUM(L21:L34)</f>
-        <v>11392.7833333333</v>
+        <v>11726.1166666667</v>
       </c>
       <c r="M35" s="171" t="n">
         <f aca="false">SUM(M21:M34)</f>
-        <v>11066.0333333333</v>
+        <v>11399.3666666667</v>
       </c>
       <c r="N35" s="171" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>10967.2</v>
+        <v>11300.5333333333</v>
       </c>
       <c r="O35" s="165"/>
     </row>
@@ -24155,55 +24180,55 @@
       </c>
       <c r="B37" s="171" t="n">
         <f aca="false">B19-B35</f>
-        <v>171481.35</v>
+        <v>167481.35</v>
       </c>
       <c r="C37" s="171" t="n">
         <f aca="false">C19-C35</f>
-        <v>15083.05</v>
+        <v>14749.7166666666</v>
       </c>
       <c r="D37" s="171" t="n">
         <f aca="false">D19-D35</f>
-        <v>15102.3</v>
+        <v>14768.9666666666</v>
       </c>
       <c r="E37" s="171" t="n">
         <f aca="false">E19-E35</f>
-        <v>11036.3</v>
+        <v>10702.9666666666</v>
       </c>
       <c r="F37" s="175" t="n">
         <f aca="false">F19-F35</f>
-        <v>13096.05</v>
+        <v>12762.7166666666</v>
       </c>
       <c r="G37" s="171" t="n">
         <f aca="false">G19-G35</f>
-        <v>17563.05</v>
+        <v>17229.7166666666</v>
       </c>
       <c r="H37" s="171" t="n">
         <f aca="false">H19-H35</f>
-        <v>14182.9666666666</v>
+        <v>13849.6333333333</v>
       </c>
       <c r="I37" s="175" t="n">
         <f aca="false">I19-I35</f>
-        <v>15303.55</v>
+        <v>14970.2166666666</v>
       </c>
       <c r="J37" s="171" t="n">
         <f aca="false">J19-J35</f>
-        <v>15145.3</v>
+        <v>14811.9666666666</v>
       </c>
       <c r="K37" s="171" t="n">
         <f aca="false">K19-K35</f>
-        <v>10797.3</v>
+        <v>10463.9666666666</v>
       </c>
       <c r="L37" s="175" t="n">
         <f aca="false">L19-L35</f>
-        <v>17283.05</v>
+        <v>16949.7166666666</v>
       </c>
       <c r="M37" s="171" t="n">
         <f aca="false">M19-M35</f>
-        <v>16479.8</v>
+        <v>16146.4666666666</v>
       </c>
       <c r="N37" s="171" t="n">
         <f aca="false">N19-N35</f>
-        <v>10408.6333333333</v>
+        <v>10075.3</v>
       </c>
       <c r="O37" s="165"/>
     </row>
@@ -24271,55 +24296,55 @@
       </c>
       <c r="B39" s="171" t="n">
         <f aca="false">B37+B38</f>
-        <v>171481.35</v>
+        <v>167481.35</v>
       </c>
       <c r="C39" s="171" t="n">
         <f aca="false">C37+C38</f>
-        <v>15083.05</v>
+        <v>14749.7166666666</v>
       </c>
       <c r="D39" s="171" t="n">
         <f aca="false">D37+D38</f>
-        <v>15102.3</v>
+        <v>14768.9666666666</v>
       </c>
       <c r="E39" s="171" t="n">
         <f aca="false">E37+E38</f>
-        <v>11036.3</v>
+        <v>10702.9666666666</v>
       </c>
       <c r="F39" s="175" t="n">
         <f aca="false">F37+F38</f>
-        <v>13096.05</v>
+        <v>12762.7166666666</v>
       </c>
       <c r="G39" s="171" t="n">
         <f aca="false">G37+G38</f>
-        <v>17563.05</v>
+        <v>17229.7166666666</v>
       </c>
       <c r="H39" s="171" t="n">
         <f aca="false">H37+H38</f>
-        <v>14182.9666666666</v>
+        <v>13849.6333333333</v>
       </c>
       <c r="I39" s="175" t="n">
         <f aca="false">I37+I38</f>
-        <v>15303.55</v>
+        <v>14970.2166666666</v>
       </c>
       <c r="J39" s="171" t="n">
         <f aca="false">J37+J38</f>
-        <v>15145.3</v>
+        <v>14811.9666666666</v>
       </c>
       <c r="K39" s="171" t="n">
         <f aca="false">K37+K38</f>
-        <v>10797.3</v>
+        <v>10463.9666666666</v>
       </c>
       <c r="L39" s="175" t="n">
         <f aca="false">L37+L38</f>
-        <v>17283.05</v>
+        <v>16949.7166666666</v>
       </c>
       <c r="M39" s="171" t="n">
         <f aca="false">M37+M38</f>
-        <v>16479.8</v>
+        <v>16146.4666666666</v>
       </c>
       <c r="N39" s="171" t="n">
         <f aca="false">N37+N38</f>
-        <v>10408.6333333333</v>
+        <v>10075.3</v>
       </c>
       <c r="O39" s="165"/>
     </row>
@@ -24481,55 +24506,55 @@
       </c>
       <c r="B44" s="178" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>43952.4769999998</v>
+        <v>43617.6769999997</v>
       </c>
       <c r="C44" s="178" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="D44" s="178" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="E44" s="178" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="F44" s="178" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="G44" s="178" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="H44" s="178" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="I44" s="178" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="J44" s="178" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="K44" s="178" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="L44" s="178" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="M44" s="178" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="N44" s="178" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3662.70641666665</v>
+        <v>3634.80641666665</v>
       </c>
       <c r="O44" s="165"/>
     </row>
@@ -24539,55 +24564,55 @@
       </c>
       <c r="B45" s="190" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>100528.873</v>
+        <v>96863.6729999998</v>
       </c>
       <c r="C45" s="191" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10420.3435833333</v>
+        <v>10114.91025</v>
       </c>
       <c r="D45" s="192" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10439.5935833333</v>
+        <v>10134.16025</v>
       </c>
       <c r="E45" s="192" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6373.59358333332</v>
+        <v>6068.16024999998</v>
       </c>
       <c r="F45" s="192" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5433.34358333332</v>
+        <v>5127.91024999999</v>
       </c>
       <c r="G45" s="192" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>12900.3435833333</v>
+        <v>12594.91025</v>
       </c>
       <c r="H45" s="192" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9520.26024999999</v>
+        <v>9214.82691666666</v>
       </c>
       <c r="I45" s="192" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7640.84358333332</v>
+        <v>7335.41024999999</v>
       </c>
       <c r="J45" s="192" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10482.5935833333</v>
+        <v>10177.16025</v>
       </c>
       <c r="K45" s="192" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>6134.59358333332</v>
+        <v>5829.16024999998</v>
       </c>
       <c r="L45" s="192" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9620.34358333332</v>
+        <v>9314.91024999999</v>
       </c>
       <c r="M45" s="192" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11817.0935833333</v>
+        <v>11511.66025</v>
       </c>
       <c r="N45" s="192" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-254.073083333347</v>
+        <v>-559.50641666668</v>
       </c>
       <c r="O45" s="165"/>
     </row>
@@ -25339,23 +25364,23 @@
       </c>
       <c r="C26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
-        <v>3478</v>
+        <v>4478</v>
       </c>
       <c r="D26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F33:H34)</f>
-        <v>3478</v>
+        <v>4478</v>
       </c>
       <c r="E26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I33:K34)</f>
-        <v>3478</v>
+        <v>4478</v>
       </c>
       <c r="F26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L33:N34)</f>
-        <v>3478</v>
+        <v>4478</v>
       </c>
       <c r="G26" s="201" t="n">
         <f aca="false">SUM(C26:F26)</f>
-        <v>13912</v>
+        <v>17912</v>
       </c>
       <c r="H26" s="196"/>
       <c r="I26" s="196"/>
@@ -25389,23 +25414,23 @@
       </c>
       <c r="C29" s="204" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
-        <v>43378.35</v>
+        <v>44378.35</v>
       </c>
       <c r="D29" s="204" t="n">
         <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D26)</f>
-        <v>41441.2666666667</v>
+        <v>42441.2666666667</v>
       </c>
       <c r="E29" s="204" t="n">
         <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E26)</f>
-        <v>45153.85</v>
+        <v>46153.85</v>
       </c>
       <c r="F29" s="204" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F26)</f>
-        <v>39828.5166666667</v>
+        <v>40828.5166666667</v>
       </c>
       <c r="G29" s="204" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G26)</f>
-        <v>169801.983333333</v>
+        <v>173801.983333333</v>
       </c>
       <c r="H29" s="205"/>
       <c r="I29" s="196"/>
@@ -25899,23 +25924,23 @@
       </c>
       <c r="C49" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C34:E34)</f>
-        <v>3435</v>
+        <v>4435</v>
       </c>
       <c r="D49" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F34:H34)</f>
-        <v>3435</v>
+        <v>4435</v>
       </c>
       <c r="E49" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I34:K34)</f>
-        <v>3435</v>
+        <v>4435</v>
       </c>
       <c r="F49" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L34:N34)</f>
-        <v>3435</v>
+        <v>4435</v>
       </c>
       <c r="G49" s="201" t="n">
         <f aca="false">SUM(C49:F49)</f>
-        <v>13740</v>
+        <v>17740</v>
       </c>
       <c r="H49" s="196" t="s">
         <v>322</v>
@@ -26061,7 +26086,7 @@
       <c r="D5" s="223"/>
       <c r="E5" s="224" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>130552.8085</v>
+        <v>126002.8085</v>
       </c>
       <c r="F5" s="215"/>
       <c r="G5" s="219"/>
@@ -26094,7 +26119,7 @@
       <c r="D7" s="223"/>
       <c r="E7" s="224" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>130552.8085</v>
+        <v>126002.8085</v>
       </c>
       <c r="F7" s="215"/>
       <c r="G7" s="219"/>
@@ -26158,7 +26183,7 @@
       </c>
       <c r="E10" s="214" t="n">
         <f aca="false">IF(E7&gt;C10,(E7-C10)*D10,0)</f>
-        <v>2435.76382499982</v>
+        <v>388.263824999816</v>
       </c>
       <c r="F10" s="215"/>
       <c r="G10" s="219"/>
@@ -26173,7 +26198,7 @@
       <c r="D11" s="231"/>
       <c r="E11" s="232" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>44951.7638249998</v>
+        <v>42904.2638249998</v>
       </c>
       <c r="F11" s="233"/>
       <c r="G11" s="234"/>
@@ -26249,7 +26274,7 @@
       </c>
       <c r="E16" s="241" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1605.65616999999</v>
+        <v>1514.65616999999</v>
       </c>
       <c r="F16" s="215"/>
       <c r="G16" s="234"/>
@@ -26274,7 +26299,7 @@
       <c r="D18" s="238"/>
       <c r="E18" s="232" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>48819.4199949998</v>
+        <v>46680.9199949998</v>
       </c>
       <c r="F18" s="215"/>
       <c r="G18" s="219"/>
@@ -26356,7 +26381,7 @@
       </c>
       <c r="E25" s="241" t="n">
         <f aca="false">E18</f>
-        <v>48819.4199949998</v>
+        <v>46680.9199949998</v>
       </c>
       <c r="F25" s="215"/>
       <c r="G25" s="219"/>
@@ -26373,7 +26398,7 @@
       </c>
       <c r="E26" s="224" t="n">
         <f aca="false">E25/2</f>
-        <v>24409.7099974999</v>
+        <v>23340.4599974999</v>
       </c>
       <c r="F26" s="215"/>
       <c r="G26" s="219"/>
@@ -26390,7 +26415,7 @@
       </c>
       <c r="E27" s="224" t="n">
         <f aca="false">E25/2</f>
-        <v>24409.7099974999</v>
+        <v>23340.4599974999</v>
       </c>
       <c r="F27" s="215"/>
       <c r="G27" s="219"/>
@@ -29306,55 +29331,55 @@
       </c>
       <c r="C13" s="171" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>149665.316666667</v>
+        <v>153665.316666667</v>
       </c>
       <c r="D13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
-        <v>12012.7833333333</v>
+        <v>12346.1166666667</v>
       </c>
       <c r="E13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D35</f>
-        <v>11323.5333333333</v>
+        <v>11656.8666666667</v>
       </c>
       <c r="F13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E35</f>
-        <v>13592.8666666667</v>
+        <v>13926.2</v>
       </c>
       <c r="G13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F35</f>
-        <v>13829.7833333333</v>
+        <v>14163.1166666667</v>
       </c>
       <c r="H13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G35</f>
-        <v>11766.1166666667</v>
+        <v>12099.45</v>
       </c>
       <c r="I13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
-        <v>13242.8666666667</v>
+        <v>13576.2</v>
       </c>
       <c r="J13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I35</f>
-        <v>13692.2833333333</v>
+        <v>14025.6166666667</v>
       </c>
       <c r="K13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J35</f>
-        <v>10880.5333333333</v>
+        <v>11213.8666666667</v>
       </c>
       <c r="L13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K35</f>
-        <v>15898.5333333333</v>
+        <v>16231.8666666667</v>
       </c>
       <c r="M13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L35</f>
-        <v>11392.7833333333</v>
+        <v>11726.1166666667</v>
       </c>
       <c r="N13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M35</f>
-        <v>11066.0333333333</v>
+        <v>11399.3666666667</v>
       </c>
       <c r="O13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>10967.2</v>
+        <v>11300.5333333333</v>
       </c>
       <c r="P13" s="159"/>
     </row>
@@ -29383,55 +29408,55 @@
       </c>
       <c r="C15" s="171" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>171481.35</v>
+        <v>167481.35</v>
       </c>
       <c r="D15" s="171" t="n">
         <f aca="false">D11-D13</f>
-        <v>15083.05</v>
+        <v>14749.7166666666</v>
       </c>
       <c r="E15" s="171" t="n">
         <f aca="false">E11-E13</f>
-        <v>15102.3</v>
+        <v>14768.9666666666</v>
       </c>
       <c r="F15" s="171" t="n">
         <f aca="false">F11-F13</f>
-        <v>11036.3</v>
+        <v>10702.9666666666</v>
       </c>
       <c r="G15" s="171" t="n">
         <f aca="false">G11-G13</f>
-        <v>13096.05</v>
+        <v>12762.7166666666</v>
       </c>
       <c r="H15" s="171" t="n">
         <f aca="false">H11-H13</f>
-        <v>17563.05</v>
+        <v>17229.7166666666</v>
       </c>
       <c r="I15" s="171" t="n">
         <f aca="false">I11-I13</f>
-        <v>14182.9666666666</v>
+        <v>13849.6333333333</v>
       </c>
       <c r="J15" s="171" t="n">
         <f aca="false">J11-J13</f>
-        <v>15303.55</v>
+        <v>14970.2166666666</v>
       </c>
       <c r="K15" s="171" t="n">
         <f aca="false">K11-K13</f>
-        <v>15145.3</v>
+        <v>14811.9666666666</v>
       </c>
       <c r="L15" s="171" t="n">
         <f aca="false">L11-L13</f>
-        <v>10797.3</v>
+        <v>10463.9666666666</v>
       </c>
       <c r="M15" s="171" t="n">
         <f aca="false">M11-M13</f>
-        <v>17283.05</v>
+        <v>16949.7166666666</v>
       </c>
       <c r="N15" s="171" t="n">
         <f aca="false">N11-N13</f>
-        <v>16479.8</v>
+        <v>16146.4666666666</v>
       </c>
       <c r="O15" s="171" t="n">
         <f aca="false">O11-O13</f>
-        <v>10408.6333333333</v>
+        <v>10075.3</v>
       </c>
       <c r="P15" s="159"/>
     </row>
@@ -29501,55 +29526,55 @@
       </c>
       <c r="C17" s="171" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>171481.35</v>
+        <v>167481.35</v>
       </c>
       <c r="D17" s="171" t="n">
         <f aca="false">D15+D16</f>
-        <v>15083.05</v>
+        <v>14749.7166666666</v>
       </c>
       <c r="E17" s="171" t="n">
         <f aca="false">E15+E16</f>
-        <v>15102.3</v>
+        <v>14768.9666666666</v>
       </c>
       <c r="F17" s="171" t="n">
         <f aca="false">F15+F16</f>
-        <v>11036.3</v>
+        <v>10702.9666666666</v>
       </c>
       <c r="G17" s="171" t="n">
         <f aca="false">G15+G16</f>
-        <v>13096.05</v>
+        <v>12762.7166666666</v>
       </c>
       <c r="H17" s="171" t="n">
         <f aca="false">H15+H16</f>
-        <v>17563.05</v>
+        <v>17229.7166666666</v>
       </c>
       <c r="I17" s="171" t="n">
         <f aca="false">I15+I16</f>
-        <v>14182.9666666666</v>
+        <v>13849.6333333333</v>
       </c>
       <c r="J17" s="171" t="n">
         <f aca="false">J15+J16</f>
-        <v>15303.55</v>
+        <v>14970.2166666666</v>
       </c>
       <c r="K17" s="171" t="n">
         <f aca="false">K15+K16</f>
-        <v>15145.3</v>
+        <v>14811.9666666666</v>
       </c>
       <c r="L17" s="171" t="n">
         <f aca="false">L15+L16</f>
-        <v>10797.3</v>
+        <v>10463.9666666666</v>
       </c>
       <c r="M17" s="171" t="n">
         <f aca="false">M15+M16</f>
-        <v>17283.05</v>
+        <v>16949.7166666666</v>
       </c>
       <c r="N17" s="171" t="n">
         <f aca="false">N15+N16</f>
-        <v>16479.8</v>
+        <v>16146.4666666666</v>
       </c>
       <c r="O17" s="171" t="n">
         <f aca="false">O15+O16</f>
-        <v>10408.6333333333</v>
+        <v>10075.3</v>
       </c>
       <c r="P17" s="159"/>
     </row>
@@ -30022,55 +30047,55 @@
       </c>
       <c r="C30" s="171" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>149665.316666667</v>
+        <v>153665.316666667</v>
       </c>
       <c r="D30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
-        <v>12012.7833333333</v>
+        <v>12346.1166666667</v>
       </c>
       <c r="E30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E13,C13/C21),0)</f>
-        <v>11323.5333333333</v>
+        <v>11656.8666666667</v>
       </c>
       <c r="F30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F13,C13/C21),0)</f>
-        <v>13592.8666666667</v>
+        <v>13926.2</v>
       </c>
       <c r="G30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G13,C13/C21),0)</f>
-        <v>13829.7833333333</v>
+        <v>14163.1166666667</v>
       </c>
       <c r="H30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H13,C13/C21),0)</f>
-        <v>11766.1166666667</v>
+        <v>12099.45</v>
       </c>
       <c r="I30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
-        <v>13242.8666666667</v>
+        <v>13576.2</v>
       </c>
       <c r="J30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J13,C13/C21),0)</f>
-        <v>13692.2833333333</v>
+        <v>14025.6166666667</v>
       </c>
       <c r="K30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K13,C13/C21),0)</f>
-        <v>10880.5333333333</v>
+        <v>11213.8666666667</v>
       </c>
       <c r="L30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L13,C13/C21),0)</f>
-        <v>15898.5333333333</v>
+        <v>16231.8666666667</v>
       </c>
       <c r="M30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M13,C13/C21),0)</f>
-        <v>11392.7833333333</v>
+        <v>11726.1166666667</v>
       </c>
       <c r="N30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N13,C13/C21),0)</f>
-        <v>11066.0333333333</v>
+        <v>11399.3666666667</v>
       </c>
       <c r="O30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>10967.2</v>
+        <v>11300.5333333333</v>
       </c>
       <c r="P30" s="159"/>
     </row>
@@ -30099,55 +30124,55 @@
       </c>
       <c r="C32" s="171" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>171481.35</v>
+        <v>167481.35</v>
       </c>
       <c r="D32" s="171" t="n">
         <f aca="false">D28-D30</f>
-        <v>15083.05</v>
+        <v>14749.7166666666</v>
       </c>
       <c r="E32" s="171" t="n">
         <f aca="false">E28-E30</f>
-        <v>15102.3</v>
+        <v>14768.9666666666</v>
       </c>
       <c r="F32" s="171" t="n">
         <f aca="false">F28-F30</f>
-        <v>11036.3</v>
+        <v>10702.9666666666</v>
       </c>
       <c r="G32" s="171" t="n">
         <f aca="false">G28-G30</f>
-        <v>13096.05</v>
+        <v>12762.7166666666</v>
       </c>
       <c r="H32" s="171" t="n">
         <f aca="false">H28-H30</f>
-        <v>17563.05</v>
+        <v>17229.7166666666</v>
       </c>
       <c r="I32" s="171" t="n">
         <f aca="false">I28-I30</f>
-        <v>14182.9666666666</v>
+        <v>13849.6333333333</v>
       </c>
       <c r="J32" s="171" t="n">
         <f aca="false">J28-J30</f>
-        <v>15303.55</v>
+        <v>14970.2166666666</v>
       </c>
       <c r="K32" s="171" t="n">
         <f aca="false">K28-K30</f>
-        <v>15145.3</v>
+        <v>14811.9666666666</v>
       </c>
       <c r="L32" s="171" t="n">
         <f aca="false">L28-L30</f>
-        <v>10797.3</v>
+        <v>10463.9666666666</v>
       </c>
       <c r="M32" s="171" t="n">
         <f aca="false">M28-M30</f>
-        <v>17283.05</v>
+        <v>16949.7166666666</v>
       </c>
       <c r="N32" s="171" t="n">
         <f aca="false">N28-N30</f>
-        <v>16479.8</v>
+        <v>16146.4666666666</v>
       </c>
       <c r="O32" s="171" t="n">
         <f aca="false">O28-O30</f>
-        <v>10408.6333333333</v>
+        <v>10075.3</v>
       </c>
       <c r="P32" s="159"/>
     </row>
@@ -30217,55 +30242,55 @@
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>171481.35</v>
+        <v>167481.35</v>
       </c>
       <c r="D34" s="171" t="n">
         <f aca="false">D32+D33</f>
-        <v>15083.05</v>
+        <v>14749.7166666666</v>
       </c>
       <c r="E34" s="171" t="n">
         <f aca="false">E32+E33</f>
-        <v>15102.3</v>
+        <v>14768.9666666666</v>
       </c>
       <c r="F34" s="171" t="n">
         <f aca="false">F32+F33</f>
-        <v>11036.3</v>
+        <v>10702.9666666666</v>
       </c>
       <c r="G34" s="171" t="n">
         <f aca="false">G32+G33</f>
-        <v>13096.05</v>
+        <v>12762.7166666666</v>
       </c>
       <c r="H34" s="171" t="n">
         <f aca="false">H32+H33</f>
-        <v>17563.05</v>
+        <v>17229.7166666666</v>
       </c>
       <c r="I34" s="171" t="n">
         <f aca="false">I32+I33</f>
-        <v>14182.9666666666</v>
+        <v>13849.6333333333</v>
       </c>
       <c r="J34" s="171" t="n">
         <f aca="false">J32+J33</f>
-        <v>15303.55</v>
+        <v>14970.2166666666</v>
       </c>
       <c r="K34" s="171" t="n">
         <f aca="false">K32+K33</f>
-        <v>15145.3</v>
+        <v>14811.9666666666</v>
       </c>
       <c r="L34" s="171" t="n">
         <f aca="false">L32+L33</f>
-        <v>10797.3</v>
+        <v>10463.9666666666</v>
       </c>
       <c r="M34" s="171" t="n">
         <f aca="false">M32+M33</f>
-        <v>17283.05</v>
+        <v>16949.7166666666</v>
       </c>
       <c r="N34" s="171" t="n">
         <f aca="false">N32+N33</f>
-        <v>16479.8</v>
+        <v>16146.4666666666</v>
       </c>
       <c r="O34" s="171" t="n">
         <f aca="false">O32+O33</f>
-        <v>10408.6333333333</v>
+        <v>10075.3</v>
       </c>
       <c r="P34" s="159"/>
     </row>
@@ -30314,7 +30339,7 @@
       </c>
       <c r="C37" s="340" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
-        <v>13912</v>
+        <v>17912</v>
       </c>
       <c r="D37" s="159"/>
       <c r="E37" s="159"/>
@@ -30336,8 +30361,8 @@
         <v>390</v>
       </c>
       <c r="C38" s="340" t="n">
-        <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
-        <v>64000</v>
+        <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$AC$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
+        <v>64540</v>
       </c>
       <c r="D38" s="159"/>
       <c r="E38" s="159"/>
@@ -30360,7 +30385,7 @@
       </c>
       <c r="C39" s="340" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>121393.35</v>
+        <v>120853.35</v>
       </c>
       <c r="D39" s="159"/>
       <c r="E39" s="159"/>
@@ -30383,7 +30408,7 @@
       </c>
       <c r="C40" s="340" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>1873.3250000002</v>
+        <v>2143.32500000022</v>
       </c>
       <c r="D40" s="159"/>
       <c r="E40" s="159"/>
@@ -30406,7 +30431,7 @@
       </c>
       <c r="C41" s="340" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>119520.024999999</v>
+        <v>118710.024999999</v>
       </c>
       <c r="D41" s="159"/>
       <c r="E41" s="159"/>
@@ -30452,7 +30477,7 @@
       </c>
       <c r="C43" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>32728.0099999998</v>
+        <v>32404.0099999997</v>
       </c>
       <c r="D43" s="159"/>
       <c r="E43" s="159"/>
@@ -30498,7 +30523,7 @@
       </c>
       <c r="C45" s="340" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3684.46699999999</v>
+        <v>3673.66699999999</v>
       </c>
       <c r="D45" s="159"/>
       <c r="E45" s="159"/>
@@ -30521,7 +30546,7 @@
       </c>
       <c r="C46" s="342" t="n">
         <f aca="false">C42+C43+C44+C45</f>
-        <v>43952.4769999998</v>
+        <v>43617.6769999997</v>
       </c>
       <c r="D46" s="159"/>
       <c r="E46" s="159"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -20149,8 +20149,8 @@
         <v>33</v>
       </c>
       <c r="O194" s="98" t="n">
-        <f aca="false">O174</f>
-        <v>123919.475166666</v>
+        <f aca="false">MAX(0,O174-O179+N(D197)+D210+N(O190))</f>
+        <v>124009.475166666</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -20627,7 +20627,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>126002.8085</v>
+        <v>126092.8085</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -20872,8 +20872,8 @@
         <v>33</v>
       </c>
       <c r="D219" s="98" t="n">
-        <f aca="false">O179-N(D197)-D210-N(O190)</f>
-        <v>-90</v>
+        <f aca="false">MAX(0,O179-O174-N(D197)-D210-N(O190))</f>
+        <v>0</v>
       </c>
       <c r="E219" s="98"/>
       <c r="F219" s="98"/>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="O224" s="98" t="n">
         <f aca="false">D219</f>
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="P224" s="98"/>
       <c r="Q224" s="98"/>
@@ -30395,7 +30395,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>126002.8085</v>
+        <v>126092.8085</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -30428,7 +30428,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>126002.8085</v>
+        <v>126092.8085</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="E10" s="213" t="n">
         <f aca="false">IF(E7&gt;C10,(E7-C10)*D10,0)</f>
-        <v>388.263824999816</v>
+        <v>428.763824999816</v>
       </c>
       <c r="F10" s="214"/>
       <c r="G10" s="218"/>
@@ -30507,7 +30507,7 @@
       <c r="D11" s="230"/>
       <c r="E11" s="231" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>42904.2638249998</v>
+        <v>42944.7638249998</v>
       </c>
       <c r="F11" s="232"/>
       <c r="G11" s="233"/>
@@ -30583,7 +30583,7 @@
       </c>
       <c r="E16" s="240" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1514.65616999999</v>
+        <v>1516.45616999999</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -30608,7 +30608,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>46680.9199949998</v>
+        <v>46723.2199949998</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="E25" s="240" t="n">
         <f aca="false">E18</f>
-        <v>46680.9199949998</v>
+        <v>46723.2199949998</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -31207,7 +31207,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23340.4599974999</v>
+        <v>23361.6099974999</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23340.4599974999</v>
+        <v>23361.6099974999</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4386,7 +4386,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="I1">
-            <v>17740</v>
+            <v>20865</v>
           </cell>
         </row>
         <row r="1">
@@ -4394,10 +4394,10 @@
             <v>52500</v>
           </cell>
           <cell r="R1">
-            <v>3360</v>
+            <v>4144</v>
           </cell>
           <cell r="S1">
-            <v>29100</v>
+            <v>36316</v>
           </cell>
         </row>
         <row r="1">
@@ -4420,6 +4420,17 @@
         <row r="1">
           <cell r="AC1">
             <v>540</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AE1">
+            <v>784</v>
+          </cell>
+          <cell r="AF1">
+            <v>0</v>
+          </cell>
+          <cell r="AG1">
+            <v>7216</v>
           </cell>
         </row>
       </sheetData>
@@ -12351,7 +12362,7 @@
       </c>
       <c r="O80" s="98" t="n">
         <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$Y$1+[1]Schedule!$AC$1)&gt;0,[1]Schedule!$R$1+[1]Schedule!$Y$1+[1]Schedule!$AC$1,0)</f>
-        <v>12040</v>
+        <v>12824</v>
       </c>
       <c r="P80" s="98"/>
       <c r="Q80" s="98"/>
@@ -12487,7 +12498,7 @@
         <v>33</v>
       </c>
       <c r="D85" s="98" t="n">
-        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
+        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
         <v>0</v>
       </c>
       <c r="E85" s="98"/>
@@ -12912,7 +12923,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>128569.475166666</v>
+        <v>127785.475166666</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -13125,7 +13136,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>130652.8085</v>
+        <v>129868.8085</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -17693,7 +17704,7 @@
       </c>
       <c r="D114" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
-        <v>17912</v>
+        <v>21037</v>
       </c>
       <c r="E114" s="98"/>
       <c r="F114" s="98"/>
@@ -17715,7 +17726,7 @@
       </c>
       <c r="O114" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B34</f>
-        <v>17740</v>
+        <v>20865</v>
       </c>
       <c r="P114" s="98"/>
       <c r="Q114" s="98"/>
@@ -17951,7 +17962,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>173801.983333333</v>
+        <v>176926.983333333</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -17973,7 +17984,7 @@
       </c>
       <c r="O122" s="98" t="n">
         <f aca="false">O66+O70+O74+O78+O82+O86+O90+O94+O98+O102+O106+O110+O114+O118</f>
-        <v>27071.4585</v>
+        <v>30196.4585</v>
       </c>
       <c r="P122" s="98"/>
       <c r="Q122" s="98"/>
@@ -18162,7 +18173,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>165398.016666666</v>
+        <v>162273.016666666</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -18609,7 +18620,7 @@
       </c>
       <c r="D144" s="98" t="n">
         <f aca="false">[1]Schedule!$R$1</f>
-        <v>3360</v>
+        <v>4144</v>
       </c>
       <c r="E144" s="98"/>
       <c r="F144" s="98"/>
@@ -18630,7 +18641,7 @@
         <v>33</v>
       </c>
       <c r="O144" s="98" t="n">
-        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$S$1)&lt;1000,[1]Schedule!$S$1,0)</f>
+        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
         <v>0</v>
       </c>
       <c r="P144" s="98"/>
@@ -18944,7 +18955,7 @@
       </c>
       <c r="O154" s="98" t="n">
         <f aca="false">D139+D144+D147+D152+D156+D160+O139+O144+O149</f>
-        <v>68840</v>
+        <v>69624</v>
       </c>
       <c r="P154" s="98"/>
       <c r="Q154" s="98"/>
@@ -19400,7 +19411,7 @@
       </c>
       <c r="O169" s="98" t="n">
         <f aca="false">O154+D179</f>
-        <v>69190</v>
+        <v>69974</v>
       </c>
       <c r="P169" s="98"/>
       <c r="Q169" s="98"/>
@@ -19537,7 +19548,7 @@
       </c>
       <c r="D174" s="98" t="n">
         <f aca="false">O122+O160+D169</f>
-        <v>27711.4585</v>
+        <v>30836.4585</v>
       </c>
       <c r="E174" s="98"/>
       <c r="F174" s="98"/>
@@ -19559,7 +19570,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>123919.475166666</v>
+        <v>123135.475166666</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -20150,7 +20161,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">MAX(0,O174-O179+N(D197)+D210+N(O190))</f>
-        <v>124009.475166666</v>
+        <v>123225.475166666</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -20627,7 +20638,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>126092.8085</v>
+        <v>125308.8085</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -27612,55 +27623,55 @@
       </c>
       <c r="B34" s="170" t="n">
         <f aca="false">SUM(C34:N34)</f>
-        <v>17740</v>
+        <v>20865</v>
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="D34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="E34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="F34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="G34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="H34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="I34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="J34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="K34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="L34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="M34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="N34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>1478.33333333333</v>
+        <v>1738.75</v>
       </c>
       <c r="O34" s="164"/>
     </row>
@@ -27670,55 +27681,55 @@
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>153665.316666667</v>
+        <v>156790.316666667</v>
       </c>
       <c r="C35" s="170" t="n">
         <f aca="false">SUM(C21:C34)</f>
-        <v>12346.1166666667</v>
+        <v>12606.5333333333</v>
       </c>
       <c r="D35" s="170" t="n">
         <f aca="false">SUM(D21:D34)</f>
-        <v>11656.8666666667</v>
+        <v>11917.2833333333</v>
       </c>
       <c r="E35" s="170" t="n">
         <f aca="false">SUM(E21:E34)</f>
-        <v>13926.2</v>
+        <v>14186.6166666667</v>
       </c>
       <c r="F35" s="174" t="n">
         <f aca="false">SUM(F21:F34)</f>
-        <v>14163.1166666667</v>
+        <v>14423.5333333333</v>
       </c>
       <c r="G35" s="170" t="n">
         <f aca="false">SUM(G21:G34)</f>
-        <v>12099.45</v>
+        <v>12359.8666666667</v>
       </c>
       <c r="H35" s="170" t="n">
         <f aca="false">SUM(H21:H34)</f>
-        <v>13576.2</v>
+        <v>13836.6166666667</v>
       </c>
       <c r="I35" s="174" t="n">
         <f aca="false">SUM(I21:I34)</f>
-        <v>14025.6166666667</v>
+        <v>14286.0333333333</v>
       </c>
       <c r="J35" s="170" t="n">
         <f aca="false">SUM(J21:J34)</f>
-        <v>11213.8666666667</v>
+        <v>11474.2833333333</v>
       </c>
       <c r="K35" s="170" t="n">
         <f aca="false">SUM(K21:K34)</f>
-        <v>16231.8666666667</v>
+        <v>16492.2833333333</v>
       </c>
       <c r="L35" s="174" t="n">
         <f aca="false">SUM(L21:L34)</f>
-        <v>11726.1166666667</v>
+        <v>11986.5333333333</v>
       </c>
       <c r="M35" s="170" t="n">
         <f aca="false">SUM(M21:M34)</f>
-        <v>11399.3666666667</v>
+        <v>11659.7833333333</v>
       </c>
       <c r="N35" s="170" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>11300.5333333333</v>
+        <v>11560.95</v>
       </c>
       <c r="O35" s="164"/>
     </row>
@@ -27745,55 +27756,55 @@
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
-        <v>167481.35</v>
+        <v>164356.35</v>
       </c>
       <c r="C37" s="170" t="n">
         <f aca="false">C19-C35</f>
-        <v>14749.7166666666</v>
+        <v>14489.3</v>
       </c>
       <c r="D37" s="170" t="n">
         <f aca="false">D19-D35</f>
-        <v>14768.9666666666</v>
+        <v>14508.55</v>
       </c>
       <c r="E37" s="170" t="n">
         <f aca="false">E19-E35</f>
-        <v>10702.9666666666</v>
+        <v>10442.55</v>
       </c>
       <c r="F37" s="174" t="n">
         <f aca="false">F19-F35</f>
-        <v>12762.7166666666</v>
+        <v>12502.3</v>
       </c>
       <c r="G37" s="170" t="n">
         <f aca="false">G19-G35</f>
-        <v>17229.7166666666</v>
+        <v>16969.3</v>
       </c>
       <c r="H37" s="170" t="n">
         <f aca="false">H19-H35</f>
-        <v>13849.6333333333</v>
+        <v>13589.2166666666</v>
       </c>
       <c r="I37" s="174" t="n">
         <f aca="false">I19-I35</f>
-        <v>14970.2166666666</v>
+        <v>14709.8</v>
       </c>
       <c r="J37" s="170" t="n">
         <f aca="false">J19-J35</f>
-        <v>14811.9666666666</v>
+        <v>14551.55</v>
       </c>
       <c r="K37" s="170" t="n">
         <f aca="false">K19-K35</f>
-        <v>10463.9666666666</v>
+        <v>10203.55</v>
       </c>
       <c r="L37" s="174" t="n">
         <f aca="false">L19-L35</f>
-        <v>16949.7166666666</v>
+        <v>16689.3</v>
       </c>
       <c r="M37" s="170" t="n">
         <f aca="false">M19-M35</f>
-        <v>16146.4666666666</v>
+        <v>15886.05</v>
       </c>
       <c r="N37" s="170" t="n">
         <f aca="false">N19-N35</f>
-        <v>10075.3</v>
+        <v>9814.8833333333</v>
       </c>
       <c r="O37" s="164"/>
     </row>
@@ -27861,55 +27872,55 @@
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
-        <v>167481.35</v>
+        <v>164356.35</v>
       </c>
       <c r="C39" s="170" t="n">
         <f aca="false">C37+C38</f>
-        <v>14749.7166666666</v>
+        <v>14489.3</v>
       </c>
       <c r="D39" s="170" t="n">
         <f aca="false">D37+D38</f>
-        <v>14768.9666666666</v>
+        <v>14508.55</v>
       </c>
       <c r="E39" s="170" t="n">
         <f aca="false">E37+E38</f>
-        <v>10702.9666666666</v>
+        <v>10442.55</v>
       </c>
       <c r="F39" s="174" t="n">
         <f aca="false">F37+F38</f>
-        <v>12762.7166666666</v>
+        <v>12502.3</v>
       </c>
       <c r="G39" s="170" t="n">
         <f aca="false">G37+G38</f>
-        <v>17229.7166666666</v>
+        <v>16969.3</v>
       </c>
       <c r="H39" s="170" t="n">
         <f aca="false">H37+H38</f>
-        <v>13849.6333333333</v>
+        <v>13589.2166666666</v>
       </c>
       <c r="I39" s="174" t="n">
         <f aca="false">I37+I38</f>
-        <v>14970.2166666666</v>
+        <v>14709.8</v>
       </c>
       <c r="J39" s="170" t="n">
         <f aca="false">J37+J38</f>
-        <v>14811.9666666666</v>
+        <v>14551.55</v>
       </c>
       <c r="K39" s="170" t="n">
         <f aca="false">K37+K38</f>
-        <v>10463.9666666666</v>
+        <v>10203.55</v>
       </c>
       <c r="L39" s="174" t="n">
         <f aca="false">L37+L38</f>
-        <v>16949.7166666666</v>
+        <v>16689.3</v>
       </c>
       <c r="M39" s="170" t="n">
         <f aca="false">M37+M38</f>
-        <v>16146.4666666666</v>
+        <v>15886.05</v>
       </c>
       <c r="N39" s="170" t="n">
         <f aca="false">N37+N38</f>
-        <v>10075.3</v>
+        <v>9814.8833333333</v>
       </c>
       <c r="O39" s="164"/>
     </row>
@@ -28071,55 +28082,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>43617.6769999997</v>
+        <v>43131.5969999998</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3634.80641666665</v>
+        <v>3594.29974999998</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -28129,55 +28140,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>96863.6729999998</v>
+        <v>94224.7529999998</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10114.91025</v>
+        <v>9895.00024999999</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10134.16025</v>
+        <v>9914.25024999999</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6068.16024999998</v>
+        <v>5848.25024999998</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5127.91024999999</v>
+        <v>4908.00024999999</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>12594.91025</v>
+        <v>12375.00025</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9214.82691666666</v>
+        <v>8994.91691666666</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7335.41024999999</v>
+        <v>7115.50024999999</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10177.16025</v>
+        <v>9957.25024999999</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>5829.16024999998</v>
+        <v>5609.25024999998</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9314.91024999999</v>
+        <v>9095.00024999999</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11511.66025</v>
+        <v>11291.75025</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-559.50641666668</v>
+        <v>-779.416416666681</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -29673,23 +29684,23 @@
       </c>
       <c r="C26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
-        <v>4478</v>
+        <v>5259.25</v>
       </c>
       <c r="D26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F33:H34)</f>
-        <v>4478</v>
+        <v>5259.25</v>
       </c>
       <c r="E26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I33:K34)</f>
-        <v>4478</v>
+        <v>5259.25</v>
       </c>
       <c r="F26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L33:N34)</f>
-        <v>4478</v>
+        <v>5259.25</v>
       </c>
       <c r="G26" s="200" t="n">
         <f aca="false">SUM(C26:F26)</f>
-        <v>17912</v>
+        <v>21037</v>
       </c>
       <c r="H26" s="195"/>
       <c r="I26" s="195"/>
@@ -29723,23 +29734,23 @@
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
-        <v>44378.35</v>
+        <v>45159.6</v>
       </c>
       <c r="D29" s="203" t="n">
         <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D26)</f>
-        <v>42441.2666666667</v>
+        <v>43222.5166666667</v>
       </c>
       <c r="E29" s="203" t="n">
         <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E26)</f>
-        <v>46153.85</v>
+        <v>46935.1</v>
       </c>
       <c r="F29" s="203" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F26)</f>
-        <v>40828.5166666667</v>
+        <v>41609.7666666667</v>
       </c>
       <c r="G29" s="203" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G26)</f>
-        <v>173801.983333333</v>
+        <v>176926.983333333</v>
       </c>
       <c r="H29" s="204"/>
       <c r="I29" s="195"/>
@@ -30233,23 +30244,23 @@
       </c>
       <c r="C49" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C34:E34)</f>
-        <v>4435</v>
+        <v>5216.25</v>
       </c>
       <c r="D49" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F34:H34)</f>
-        <v>4435</v>
+        <v>5216.25</v>
       </c>
       <c r="E49" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I34:K34)</f>
-        <v>4435</v>
+        <v>5216.25</v>
       </c>
       <c r="F49" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L34:N34)</f>
-        <v>4435</v>
+        <v>5216.25</v>
       </c>
       <c r="G49" s="200" t="n">
         <f aca="false">SUM(C49:F49)</f>
-        <v>17740</v>
+        <v>20865</v>
       </c>
       <c r="H49" s="195" t="s">
         <v>322</v>
@@ -30395,7 +30406,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>126092.8085</v>
+        <v>125308.8085</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -30428,7 +30439,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>126092.8085</v>
+        <v>125308.8085</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -30492,7 +30503,7 @@
       </c>
       <c r="E10" s="213" t="n">
         <f aca="false">IF(E7&gt;C10,(E7-C10)*D10,0)</f>
-        <v>428.763824999816</v>
+        <v>75.9638249998163</v>
       </c>
       <c r="F10" s="214"/>
       <c r="G10" s="218"/>
@@ -30507,7 +30518,7 @@
       <c r="D11" s="230"/>
       <c r="E11" s="231" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>42944.7638249998</v>
+        <v>42591.9638249998</v>
       </c>
       <c r="F11" s="232"/>
       <c r="G11" s="233"/>
@@ -30583,7 +30594,7 @@
       </c>
       <c r="E16" s="240" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1516.45616999999</v>
+        <v>1500.77616999999</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -30608,7 +30619,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>46723.2199949998</v>
+        <v>46354.7399949998</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -31190,7 +31201,7 @@
       </c>
       <c r="E25" s="240" t="n">
         <f aca="false">E18</f>
-        <v>46723.2199949998</v>
+        <v>46354.7399949998</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -31207,7 +31218,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23361.6099974999</v>
+        <v>23177.3699974999</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -31224,7 +31235,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23361.6099974999</v>
+        <v>23177.3699974999</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -36299,55 +36310,55 @@
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>153665.316666667</v>
+        <v>156790.316666667</v>
       </c>
       <c r="D13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
-        <v>12346.1166666667</v>
+        <v>12606.5333333333</v>
       </c>
       <c r="E13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D35</f>
-        <v>11656.8666666667</v>
+        <v>11917.2833333333</v>
       </c>
       <c r="F13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E35</f>
-        <v>13926.2</v>
+        <v>14186.6166666667</v>
       </c>
       <c r="G13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F35</f>
-        <v>14163.1166666667</v>
+        <v>14423.5333333333</v>
       </c>
       <c r="H13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G35</f>
-        <v>12099.45</v>
+        <v>12359.8666666667</v>
       </c>
       <c r="I13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
-        <v>13576.2</v>
+        <v>13836.6166666667</v>
       </c>
       <c r="J13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I35</f>
-        <v>14025.6166666667</v>
+        <v>14286.0333333333</v>
       </c>
       <c r="K13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J35</f>
-        <v>11213.8666666667</v>
+        <v>11474.2833333333</v>
       </c>
       <c r="L13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K35</f>
-        <v>16231.8666666667</v>
+        <v>16492.2833333333</v>
       </c>
       <c r="M13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L35</f>
-        <v>11726.1166666667</v>
+        <v>11986.5333333333</v>
       </c>
       <c r="N13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M35</f>
-        <v>11399.3666666667</v>
+        <v>11659.7833333333</v>
       </c>
       <c r="O13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>11300.5333333333</v>
+        <v>11560.95</v>
       </c>
       <c r="P13" s="158"/>
     </row>
@@ -36376,55 +36387,55 @@
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>167481.35</v>
+        <v>164356.35</v>
       </c>
       <c r="D15" s="170" t="n">
         <f aca="false">D11-D13</f>
-        <v>14749.7166666666</v>
+        <v>14489.3</v>
       </c>
       <c r="E15" s="170" t="n">
         <f aca="false">E11-E13</f>
-        <v>14768.9666666666</v>
+        <v>14508.55</v>
       </c>
       <c r="F15" s="170" t="n">
         <f aca="false">F11-F13</f>
-        <v>10702.9666666666</v>
+        <v>10442.55</v>
       </c>
       <c r="G15" s="170" t="n">
         <f aca="false">G11-G13</f>
-        <v>12762.7166666666</v>
+        <v>12502.3</v>
       </c>
       <c r="H15" s="170" t="n">
         <f aca="false">H11-H13</f>
-        <v>17229.7166666666</v>
+        <v>16969.3</v>
       </c>
       <c r="I15" s="170" t="n">
         <f aca="false">I11-I13</f>
-        <v>13849.6333333333</v>
+        <v>13589.2166666666</v>
       </c>
       <c r="J15" s="170" t="n">
         <f aca="false">J11-J13</f>
-        <v>14970.2166666666</v>
+        <v>14709.8</v>
       </c>
       <c r="K15" s="170" t="n">
         <f aca="false">K11-K13</f>
-        <v>14811.9666666666</v>
+        <v>14551.55</v>
       </c>
       <c r="L15" s="170" t="n">
         <f aca="false">L11-L13</f>
-        <v>10463.9666666666</v>
+        <v>10203.55</v>
       </c>
       <c r="M15" s="170" t="n">
         <f aca="false">M11-M13</f>
-        <v>16949.7166666666</v>
+        <v>16689.3</v>
       </c>
       <c r="N15" s="170" t="n">
         <f aca="false">N11-N13</f>
-        <v>16146.4666666666</v>
+        <v>15886.05</v>
       </c>
       <c r="O15" s="170" t="n">
         <f aca="false">O11-O13</f>
-        <v>10075.3</v>
+        <v>9814.8833333333</v>
       </c>
       <c r="P15" s="158"/>
     </row>
@@ -36494,55 +36505,55 @@
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>167481.35</v>
+        <v>164356.35</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">D15+D16</f>
-        <v>14749.7166666666</v>
+        <v>14489.3</v>
       </c>
       <c r="E17" s="170" t="n">
         <f aca="false">E15+E16</f>
-        <v>14768.9666666666</v>
+        <v>14508.55</v>
       </c>
       <c r="F17" s="170" t="n">
         <f aca="false">F15+F16</f>
-        <v>10702.9666666666</v>
+        <v>10442.55</v>
       </c>
       <c r="G17" s="170" t="n">
         <f aca="false">G15+G16</f>
-        <v>12762.7166666666</v>
+        <v>12502.3</v>
       </c>
       <c r="H17" s="170" t="n">
         <f aca="false">H15+H16</f>
-        <v>17229.7166666666</v>
+        <v>16969.3</v>
       </c>
       <c r="I17" s="170" t="n">
         <f aca="false">I15+I16</f>
-        <v>13849.6333333333</v>
+        <v>13589.2166666666</v>
       </c>
       <c r="J17" s="170" t="n">
         <f aca="false">J15+J16</f>
-        <v>14970.2166666666</v>
+        <v>14709.8</v>
       </c>
       <c r="K17" s="170" t="n">
         <f aca="false">K15+K16</f>
-        <v>14811.9666666666</v>
+        <v>14551.55</v>
       </c>
       <c r="L17" s="170" t="n">
         <f aca="false">L15+L16</f>
-        <v>10463.9666666666</v>
+        <v>10203.55</v>
       </c>
       <c r="M17" s="170" t="n">
         <f aca="false">M15+M16</f>
-        <v>16949.7166666666</v>
+        <v>16689.3</v>
       </c>
       <c r="N17" s="170" t="n">
         <f aca="false">N15+N16</f>
-        <v>16146.4666666666</v>
+        <v>15886.05</v>
       </c>
       <c r="O17" s="170" t="n">
         <f aca="false">O15+O16</f>
-        <v>10075.3</v>
+        <v>9814.8833333333</v>
       </c>
       <c r="P17" s="158"/>
     </row>
@@ -38461,55 +38472,55 @@
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>153665.316666667</v>
+        <v>156790.316666667</v>
       </c>
       <c r="D30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
-        <v>12346.1166666667</v>
+        <v>12606.5333333333</v>
       </c>
       <c r="E30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E13,C13/C21),0)</f>
-        <v>11656.8666666667</v>
+        <v>11917.2833333333</v>
       </c>
       <c r="F30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F13,C13/C21),0)</f>
-        <v>13926.2</v>
+        <v>14186.6166666667</v>
       </c>
       <c r="G30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G13,C13/C21),0)</f>
-        <v>14163.1166666667</v>
+        <v>14423.5333333333</v>
       </c>
       <c r="H30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H13,C13/C21),0)</f>
-        <v>12099.45</v>
+        <v>12359.8666666667</v>
       </c>
       <c r="I30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
-        <v>13576.2</v>
+        <v>13836.6166666667</v>
       </c>
       <c r="J30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J13,C13/C21),0)</f>
-        <v>14025.6166666667</v>
+        <v>14286.0333333333</v>
       </c>
       <c r="K30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K13,C13/C21),0)</f>
-        <v>11213.8666666667</v>
+        <v>11474.2833333333</v>
       </c>
       <c r="L30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L13,C13/C21),0)</f>
-        <v>16231.8666666667</v>
+        <v>16492.2833333333</v>
       </c>
       <c r="M30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M13,C13/C21),0)</f>
-        <v>11726.1166666667</v>
+        <v>11986.5333333333</v>
       </c>
       <c r="N30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N13,C13/C21),0)</f>
-        <v>11399.3666666667</v>
+        <v>11659.7833333333</v>
       </c>
       <c r="O30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>11300.5333333333</v>
+        <v>11560.95</v>
       </c>
       <c r="P30" s="158"/>
     </row>
@@ -38538,55 +38549,55 @@
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>167481.35</v>
+        <v>164356.35</v>
       </c>
       <c r="D32" s="170" t="n">
         <f aca="false">D28-D30</f>
-        <v>14749.7166666666</v>
+        <v>14489.3</v>
       </c>
       <c r="E32" s="170" t="n">
         <f aca="false">E28-E30</f>
-        <v>14768.9666666666</v>
+        <v>14508.55</v>
       </c>
       <c r="F32" s="170" t="n">
         <f aca="false">F28-F30</f>
-        <v>10702.9666666666</v>
+        <v>10442.55</v>
       </c>
       <c r="G32" s="170" t="n">
         <f aca="false">G28-G30</f>
-        <v>12762.7166666666</v>
+        <v>12502.3</v>
       </c>
       <c r="H32" s="170" t="n">
         <f aca="false">H28-H30</f>
-        <v>17229.7166666666</v>
+        <v>16969.3</v>
       </c>
       <c r="I32" s="170" t="n">
         <f aca="false">I28-I30</f>
-        <v>13849.6333333333</v>
+        <v>13589.2166666666</v>
       </c>
       <c r="J32" s="170" t="n">
         <f aca="false">J28-J30</f>
-        <v>14970.2166666666</v>
+        <v>14709.8</v>
       </c>
       <c r="K32" s="170" t="n">
         <f aca="false">K28-K30</f>
-        <v>14811.9666666666</v>
+        <v>14551.55</v>
       </c>
       <c r="L32" s="170" t="n">
         <f aca="false">L28-L30</f>
-        <v>10463.9666666666</v>
+        <v>10203.55</v>
       </c>
       <c r="M32" s="170" t="n">
         <f aca="false">M28-M30</f>
-        <v>16949.7166666666</v>
+        <v>16689.3</v>
       </c>
       <c r="N32" s="170" t="n">
         <f aca="false">N28-N30</f>
-        <v>16146.4666666666</v>
+        <v>15886.05</v>
       </c>
       <c r="O32" s="170" t="n">
         <f aca="false">O28-O30</f>
-        <v>10075.3</v>
+        <v>9814.8833333333</v>
       </c>
       <c r="P32" s="158"/>
     </row>
@@ -38656,55 +38667,55 @@
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>167481.35</v>
+        <v>164356.35</v>
       </c>
       <c r="D34" s="170" t="n">
         <f aca="false">D32+D33</f>
-        <v>14749.7166666666</v>
+        <v>14489.3</v>
       </c>
       <c r="E34" s="170" t="n">
         <f aca="false">E32+E33</f>
-        <v>14768.9666666666</v>
+        <v>14508.55</v>
       </c>
       <c r="F34" s="170" t="n">
         <f aca="false">F32+F33</f>
-        <v>10702.9666666666</v>
+        <v>10442.55</v>
       </c>
       <c r="G34" s="170" t="n">
         <f aca="false">G32+G33</f>
-        <v>12762.7166666666</v>
+        <v>12502.3</v>
       </c>
       <c r="H34" s="170" t="n">
         <f aca="false">H32+H33</f>
-        <v>17229.7166666666</v>
+        <v>16969.3</v>
       </c>
       <c r="I34" s="170" t="n">
         <f aca="false">I32+I33</f>
-        <v>13849.6333333333</v>
+        <v>13589.2166666666</v>
       </c>
       <c r="J34" s="170" t="n">
         <f aca="false">J32+J33</f>
-        <v>14970.2166666666</v>
+        <v>14709.8</v>
       </c>
       <c r="K34" s="170" t="n">
         <f aca="false">K32+K33</f>
-        <v>14811.9666666666</v>
+        <v>14551.55</v>
       </c>
       <c r="L34" s="170" t="n">
         <f aca="false">L32+L33</f>
-        <v>10463.9666666666</v>
+        <v>10203.55</v>
       </c>
       <c r="M34" s="170" t="n">
         <f aca="false">M32+M33</f>
-        <v>16949.7166666666</v>
+        <v>16689.3</v>
       </c>
       <c r="N34" s="170" t="n">
         <f aca="false">N32+N33</f>
-        <v>16146.4666666666</v>
+        <v>15886.05</v>
       </c>
       <c r="O34" s="170" t="n">
         <f aca="false">O32+O33</f>
-        <v>10075.3</v>
+        <v>9814.8833333333</v>
       </c>
       <c r="P34" s="158"/>
     </row>
@@ -38753,7 +38764,7 @@
       </c>
       <c r="C37" s="339" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
-        <v>17912</v>
+        <v>21037</v>
       </c>
       <c r="D37" s="158"/>
       <c r="E37" s="158"/>
@@ -38776,7 +38787,7 @@
       </c>
       <c r="C38" s="339" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$AC$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
-        <v>64540</v>
+        <v>65324</v>
       </c>
       <c r="D38" s="158"/>
       <c r="E38" s="158"/>
@@ -38799,7 +38810,7 @@
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>120853.35</v>
+        <v>120069.35</v>
       </c>
       <c r="D39" s="158"/>
       <c r="E39" s="158"/>
@@ -38822,7 +38833,7 @@
       </c>
       <c r="C40" s="339" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>2143.32500000022</v>
+        <v>2535.3250000002</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -38845,7 +38856,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>118710.024999999</v>
+        <v>117534.024999999</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -38891,7 +38902,7 @@
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>32404.0099999997</v>
+        <v>31933.6099999998</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -38937,7 +38948,7 @@
       </c>
       <c r="C45" s="339" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3673.66699999999</v>
+        <v>3657.98699999999</v>
       </c>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
@@ -38960,7 +38971,7 @@
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44+C45</f>
-        <v>43617.6769999997</v>
+        <v>43131.5969999998</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4396,9 +4396,6 @@
           <cell r="R1">
             <v>4144</v>
           </cell>
-          <cell r="S1">
-            <v>36316</v>
-          </cell>
         </row>
         <row r="1">
           <cell r="V1">
@@ -4429,8 +4426,13 @@
           <cell r="AF1">
             <v>0</v>
           </cell>
-          <cell r="AG1">
-            <v>7216</v>
+        </row>
+        <row r="1">
+          <cell r="AH1">
+            <v>20640</v>
+          </cell>
+          <cell r="AI1">
+            <v>8460</v>
           </cell>
         </row>
       </sheetData>
@@ -12498,7 +12500,7 @@
         <v>33</v>
       </c>
       <c r="D85" s="98" t="n">
-        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
+        <f aca="false">IF(([1]Schedule!$R$1-[1]Schedule!$AE$1+[1]Schedule!$AH$1)&lt;1000,[1]Schedule!$AH$1,0)+IF(([1]Schedule!$AC$1-[1]Schedule!$AF$1+[1]Schedule!$AI$1)&lt;1000,[1]Schedule!$AI$1,0)</f>
         <v>0</v>
       </c>
       <c r="E85" s="98"/>
@@ -18641,7 +18643,7 @@
         <v>33</v>
       </c>
       <c r="O144" s="98" t="n">
-        <f aca="false">IF(([1]Schedule!$R$1+[1]Schedule!$S$1-[1]Schedule!$AE$1-[1]Schedule!$AF$1-[1]Schedule!$AG$1)&lt;1000,[1]Schedule!$S$1-[1]Schedule!$AG$1,0)</f>
+        <f aca="false">IF(([1]Schedule!$R$1-[1]Schedule!$AE$1+[1]Schedule!$AH$1)&lt;1000,[1]Schedule!$AH$1,0)+IF(([1]Schedule!$AC$1-[1]Schedule!$AF$1+[1]Schedule!$AI$1)&lt;1000,[1]Schedule!$AI$1,0)</f>
         <v>0</v>
       </c>
       <c r="P144" s="98"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="443">
   <si>
     <r>
       <rPr>
@@ -1216,16 +1216,19 @@
     <t xml:space="preserve">Zero-emission goods vehicle allowance</t>
   </si>
   <si>
+    <t xml:space="preserve">Zero-emission car allowance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total capital allowances (total of boxes 49 to 56)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zero-emission car allowance</t>
+    <t xml:space="preserve">The Structures and Buildings Allowance</t>
   </si>
   <si>
     <t xml:space="preserve">Balancing charge on sales of assets or on the cessation of</t>
   </si>
   <si>
-    <t xml:space="preserve">The Structures and Buildings Allowance</t>
+    <t xml:space="preserve">Freeport and Investment Zones Structures and Buildings Allowance</t>
   </si>
   <si>
     <t xml:space="preserve">business use (including where Business Premises Renovation</t>
@@ -2004,6 +2007,9 @@
     <t xml:space="preserve">Additional rate applicable above the higher rate limit</t>
   </si>
   <si>
+    <t xml:space="preserve">Structures and buildings allowance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taxable Bands Allowances</t>
   </si>
   <si>
@@ -2014,6 +2020,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Tax Band </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freeport and Investment Zone SBA</t>
   </si>
   <si>
     <t xml:space="preserve">Depreciation Rates Applied</t>
@@ -4435,6 +4444,16 @@
             <v>8460</v>
           </cell>
         </row>
+        <row r="120">
+          <cell r="K120">
+            <v>1800</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="K121">
+            <v>1024.65753424658</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
@@ -8760,7 +8779,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="344" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="345"/>
@@ -8783,7 +8802,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="348" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E2" s="348"/>
       <c r="F2" s="348"/>
@@ -8794,7 +8813,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="350" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K2" s="350"/>
       <c r="L2" s="348" t="str">
@@ -8840,7 +8859,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="354" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J4" s="354"/>
       <c r="K4" s="354"/>
@@ -8860,7 +8879,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="354" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E5" s="354"/>
       <c r="F5" s="354"/>
@@ -8869,7 +8888,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="354" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J5" s="354"/>
       <c r="K5" s="354"/>
@@ -8889,7 +8908,7 @@
       </c>
       <c r="C6" s="63"/>
       <c r="D6" s="63" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E6" s="63"/>
       <c r="F6" s="63"/>
@@ -8898,7 +8917,7 @@
       </c>
       <c r="H6" s="63"/>
       <c r="I6" s="354" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J6" s="354"/>
       <c r="K6" s="354"/>
@@ -8908,7 +8927,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="351" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8918,14 +8937,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="354" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E7" s="354"/>
       <c r="F7" s="354"/>
       <c r="G7" s="351"/>
       <c r="H7" s="63"/>
       <c r="I7" s="354" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J7" s="354"/>
       <c r="K7" s="354"/>
@@ -8935,7 +8954,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="351" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8950,7 +8969,7 @@
       <c r="G8" s="357"/>
       <c r="H8" s="63"/>
       <c r="I8" s="354" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J8" s="354"/>
       <c r="K8" s="354"/>
@@ -8960,7 +8979,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="351" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8969,24 +8988,28 @@
         <v>46265</v>
       </c>
       <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
+      <c r="D9" s="63" t="s">
+        <v>412</v>
+      </c>
       <c r="E9" s="351"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="351"/>
+      <c r="G9" s="355" t="n">
+        <v>0.03</v>
+      </c>
       <c r="H9" s="63"/>
       <c r="I9" s="354" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J9" s="354"/>
       <c r="K9" s="354"/>
       <c r="L9" s="358" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M9" s="358" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N9" s="359" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O9" s="351"/>
     </row>
@@ -8996,10 +9019,14 @@
         <v>46295</v>
       </c>
       <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
+      <c r="D10" s="63" t="s">
+        <v>417</v>
+      </c>
       <c r="E10" s="351"/>
       <c r="F10" s="63"/>
-      <c r="G10" s="351"/>
+      <c r="G10" s="355" t="n">
+        <v>0.1</v>
+      </c>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
       <c r="J10" s="63"/>
@@ -9016,16 +9043,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="348" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E11" s="348"/>
       <c r="F11" s="348"/>
       <c r="G11" s="351" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="360" t="n">
@@ -9055,7 +9082,7 @@
       <c r="G12" s="351"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="360" t="n">
@@ -9077,7 +9104,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="354" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E13" s="354"/>
       <c r="F13" s="354"/>
@@ -9086,7 +9113,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="360" t="n">
@@ -9108,7 +9135,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="354" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E14" s="354"/>
       <c r="F14" s="354"/>
@@ -9117,7 +9144,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="348" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J14" s="348"/>
       <c r="K14" s="348"/>
@@ -9136,7 +9163,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="354" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E15" s="354"/>
       <c r="F15" s="354"/>
@@ -9159,7 +9186,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="354" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E16" s="354"/>
       <c r="F16" s="354"/>
@@ -9168,7 +9195,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="354" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="J16" s="354"/>
       <c r="K16" s="354"/>
@@ -9176,7 +9203,7 @@
         <v>3.65</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N16" s="357" t="n">
         <v>7105</v>
@@ -9192,7 +9219,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="354" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E17" s="354"/>
       <c r="F17" s="354"/>
@@ -9234,24 +9261,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="348" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E19" s="348"/>
       <c r="F19" s="351" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G19" s="351" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="363" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J19" s="363"/>
       <c r="K19" s="363"/>
       <c r="L19" s="63"/>
       <c r="M19" s="364" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -9288,7 +9315,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="354" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E21" s="354"/>
       <c r="F21" s="357" t="n">
@@ -9313,7 +9340,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="357" t="n">
@@ -9324,13 +9351,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="363" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J22" s="363"/>
       <c r="K22" s="363"/>
       <c r="L22" s="63"/>
       <c r="M22" s="364" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -9338,7 +9365,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="353" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -9363,11 +9390,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="353" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="348" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E24" s="348"/>
       <c r="F24" s="63"/>
@@ -9405,7 +9432,7 @@
       <c r="B26" s="367"/>
       <c r="C26" s="63"/>
       <c r="D26" s="354" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E26" s="354"/>
       <c r="F26" s="357" t="n">
@@ -9426,7 +9453,7 @@
       <c r="B27" s="367"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="355" t="n">
@@ -18822,16 +18849,24 @@
       <c r="V149" s="63"/>
       <c r="W149" s="82"/>
     </row>
-    <row r="150" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="79"/>
       <c r="B150" s="63"/>
-      <c r="C150" s="64"/>
-      <c r="D150" s="63"/>
-      <c r="E150" s="63"/>
-      <c r="F150" s="63"/>
-      <c r="G150" s="63"/>
-      <c r="H150" s="63"/>
-      <c r="I150" s="63"/>
+      <c r="C150" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" s="98"/>
+      <c r="E150" s="98"/>
+      <c r="F150" s="98"/>
+      <c r="G150" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H150" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="100" t="n">
+        <v>0</v>
+      </c>
       <c r="J150" s="63"/>
       <c r="K150" s="63"/>
       <c r="L150" s="63"/>
@@ -18848,9 +18883,13 @@
       <c r="W150" s="82"/>
     </row>
     <row r="151" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="106"/>
+      <c r="A151" s="75" t="n">
+        <v>52.1</v>
+      </c>
       <c r="B151" s="63"/>
-      <c r="C151" s="64"/>
+      <c r="C151" s="64" t="s">
+        <v>167</v>
+      </c>
       <c r="D151" s="64"/>
       <c r="E151" s="64"/>
       <c r="F151" s="64"/>
@@ -18864,7 +18903,7 @@
       </c>
       <c r="M151" s="63"/>
       <c r="N151" s="64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O151" s="63"/>
       <c r="P151" s="63"/>
@@ -18882,7 +18921,9 @@
       <c r="C152" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="98"/>
+      <c r="D152" s="98" t="n">
+        <v>2500</v>
+      </c>
       <c r="E152" s="98"/>
       <c r="F152" s="98"/>
       <c r="G152" s="99" t="s">
@@ -18936,11 +18977,11 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="75" t="n">
-        <v>52.1</v>
+        <v>53</v>
       </c>
       <c r="B154" s="63"/>
       <c r="C154" s="64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D154" s="64"/>
       <c r="E154" s="64"/>
@@ -18956,8 +18997,8 @@
         <v>33</v>
       </c>
       <c r="O154" s="98" t="n">
-        <f aca="false">D139+D144+D147+D152+D156+D160+O139+O144+O149</f>
-        <v>69624</v>
+        <f aca="false">D139+D144+D147+D150+D152+D156+D160+O139+O144+O149</f>
+        <v>70648.6575342466</v>
       </c>
       <c r="P154" s="98"/>
       <c r="Q154" s="98"/>
@@ -19006,7 +19047,8 @@
         <v>33</v>
       </c>
       <c r="D156" s="98" t="n">
-        <v>2500</v>
+        <f aca="false">[1]Schedule!$K$120</f>
+        <v>1800</v>
       </c>
       <c r="E156" s="98"/>
       <c r="F156" s="98"/>
@@ -19026,7 +19068,7 @@
       </c>
       <c r="M156" s="63"/>
       <c r="N156" s="64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O156" s="63"/>
       <c r="P156" s="63"/>
@@ -19040,11 +19082,11 @@
     </row>
     <row r="157" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="75" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="B157" s="63"/>
       <c r="C157" s="64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D157" s="64"/>
       <c r="E157" s="64"/>
@@ -19057,7 +19099,7 @@
       <c r="L157" s="63"/>
       <c r="M157" s="63"/>
       <c r="N157" s="64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O157" s="63"/>
       <c r="P157" s="63"/>
@@ -19084,7 +19126,7 @@
       <c r="L158" s="63"/>
       <c r="M158" s="63"/>
       <c r="N158" s="64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O158" s="63"/>
       <c r="P158" s="63"/>
@@ -19128,7 +19170,8 @@
         <v>33</v>
       </c>
       <c r="D160" s="98" t="n">
-        <v>1800</v>
+        <f aca="false">[1]Schedule!$K$121</f>
+        <v>1024.65753424658</v>
       </c>
       <c r="E160" s="98"/>
       <c r="F160" s="98"/>
@@ -19194,7 +19237,7 @@
     </row>
     <row r="162" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B162" s="103"/>
       <c r="C162" s="103"/>
@@ -19221,7 +19264,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="104" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B163" s="104"/>
       <c r="C163" s="104"/>
@@ -19248,7 +19291,7 @@
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B164" s="104"/>
       <c r="C164" s="104"/>
@@ -19304,7 +19347,7 @@
       </c>
       <c r="B166" s="63"/>
       <c r="C166" s="64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D166" s="64"/>
       <c r="E166" s="64"/>
@@ -19319,7 +19362,7 @@
       </c>
       <c r="M166" s="63"/>
       <c r="N166" s="64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O166" s="63"/>
       <c r="P166" s="63"/>
@@ -19346,7 +19389,7 @@
       <c r="L167" s="64"/>
       <c r="M167" s="63"/>
       <c r="N167" s="64" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O167" s="110"/>
       <c r="P167" s="110"/>
@@ -19413,7 +19456,7 @@
       </c>
       <c r="O169" s="98" t="n">
         <f aca="false">O154+D179</f>
-        <v>69974</v>
+        <v>70998.6575342466</v>
       </c>
       <c r="P169" s="98"/>
       <c r="Q169" s="98"/>
@@ -19461,7 +19504,7 @@
       </c>
       <c r="B171" s="63"/>
       <c r="C171" s="64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D171" s="64"/>
       <c r="E171" s="64"/>
@@ -19476,7 +19519,7 @@
       </c>
       <c r="M171" s="63"/>
       <c r="N171" s="64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O171" s="63"/>
       <c r="P171" s="63"/>
@@ -19492,7 +19535,7 @@
       <c r="A172" s="106"/>
       <c r="B172" s="63"/>
       <c r="C172" s="64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D172" s="64"/>
       <c r="E172" s="64"/>
@@ -19505,7 +19548,7 @@
       <c r="L172" s="64"/>
       <c r="M172" s="63"/>
       <c r="N172" s="64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O172" s="63"/>
       <c r="P172" s="63"/>
@@ -19572,7 +19615,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>123135.475166666</v>
+        <v>122110.81763242</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -19620,7 +19663,7 @@
       </c>
       <c r="B176" s="63"/>
       <c r="C176" s="64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D176" s="64"/>
       <c r="E176" s="64"/>
@@ -19635,7 +19678,7 @@
       </c>
       <c r="M176" s="63"/>
       <c r="N176" s="64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O176" s="63"/>
       <c r="P176" s="63"/>
@@ -19651,7 +19694,7 @@
       <c r="A177" s="79"/>
       <c r="B177" s="63"/>
       <c r="C177" s="64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D177" s="63"/>
       <c r="E177" s="63"/>
@@ -19664,7 +19707,7 @@
       <c r="L177" s="63"/>
       <c r="M177" s="63"/>
       <c r="N177" s="64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O177" s="63"/>
       <c r="P177" s="63"/>
@@ -19774,7 +19817,7 @@
     </row>
     <row r="181" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="103" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B181" s="103"/>
       <c r="C181" s="103"/>
@@ -19801,7 +19844,7 @@
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="104" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B182" s="104"/>
       <c r="C182" s="104"/>
@@ -19828,7 +19871,7 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="104" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B183" s="104"/>
       <c r="C183" s="104"/>
@@ -19855,7 +19898,7 @@
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="133" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B184" s="133"/>
       <c r="C184" s="133"/>
@@ -19909,7 +19952,7 @@
       <c r="A186" s="75"/>
       <c r="B186" s="63"/>
       <c r="C186" s="64" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D186" s="64"/>
       <c r="E186" s="64"/>
@@ -19924,7 +19967,7 @@
       </c>
       <c r="M186" s="63"/>
       <c r="N186" s="64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O186" s="63"/>
       <c r="P186" s="63"/>
@@ -19951,7 +19994,7 @@
       <c r="L187" s="64"/>
       <c r="M187" s="63"/>
       <c r="N187" s="80" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O187" s="63"/>
       <c r="P187" s="63"/>
@@ -19978,7 +20021,7 @@
       <c r="L188" s="64"/>
       <c r="M188" s="63"/>
       <c r="N188" s="92" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O188" s="63"/>
       <c r="P188" s="63"/>
@@ -20005,7 +20048,7 @@
       <c r="L189" s="64"/>
       <c r="M189" s="63"/>
       <c r="N189" s="92" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O189" s="110"/>
       <c r="P189" s="110"/>
@@ -20035,7 +20078,7 @@
         <v>33</v>
       </c>
       <c r="O190" s="136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P190" s="137"/>
       <c r="Q190" s="137"/>
@@ -20083,7 +20126,7 @@
       </c>
       <c r="B192" s="63"/>
       <c r="C192" s="64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D192" s="112"/>
       <c r="E192" s="112"/>
@@ -20098,7 +20141,7 @@
       </c>
       <c r="M192" s="63"/>
       <c r="N192" s="64" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O192" s="63"/>
       <c r="P192" s="63"/>
@@ -20117,7 +20160,7 @@
       <c r="A193" s="79"/>
       <c r="B193" s="63"/>
       <c r="C193" s="64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D193" s="64"/>
       <c r="E193" s="64"/>
@@ -20130,7 +20173,7 @@
       <c r="L193" s="64"/>
       <c r="M193" s="64"/>
       <c r="N193" s="80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O193" s="112"/>
       <c r="P193" s="112"/>
@@ -20146,7 +20189,7 @@
       <c r="A194" s="79"/>
       <c r="B194" s="63"/>
       <c r="C194" s="80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D194" s="64"/>
       <c r="E194" s="64"/>
@@ -20163,7 +20206,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">MAX(0,O174-O179+N(D197)+D210+N(O190))</f>
-        <v>123225.475166666</v>
+        <v>122200.81763242</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -20222,7 +20265,7 @@
       </c>
       <c r="M196" s="63"/>
       <c r="N196" s="64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O196" s="63"/>
       <c r="P196" s="63"/>
@@ -20241,7 +20284,7 @@
         <v>33</v>
       </c>
       <c r="D197" s="136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E197" s="137"/>
       <c r="F197" s="137"/>
@@ -20259,7 +20302,7 @@
       <c r="L197" s="63"/>
       <c r="M197" s="63"/>
       <c r="N197" s="80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O197" s="63"/>
       <c r="P197" s="63"/>
@@ -20300,7 +20343,7 @@
       <c r="A199" s="75"/>
       <c r="B199" s="63"/>
       <c r="C199" s="64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D199" s="63"/>
       <c r="E199" s="63"/>
@@ -20376,7 +20419,7 @@
       </c>
       <c r="M201" s="63"/>
       <c r="N201" s="64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O201" s="63"/>
       <c r="P201" s="63"/>
@@ -20403,7 +20446,7 @@
       <c r="L202" s="63"/>
       <c r="M202" s="63"/>
       <c r="N202" s="64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O202" s="63"/>
       <c r="P202" s="63"/>
@@ -20545,7 +20588,7 @@
       <c r="L207" s="63"/>
       <c r="M207" s="63"/>
       <c r="N207" s="64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O207" s="63"/>
       <c r="P207" s="63"/>
@@ -20563,7 +20606,7 @@
       </c>
       <c r="B208" s="63"/>
       <c r="C208" s="64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D208" s="64"/>
       <c r="E208" s="64"/>
@@ -20640,7 +20683,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>125308.8085</v>
+        <v>124284.150965753</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -20684,7 +20727,7 @@
     </row>
     <row r="212" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="111" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B212" s="111"/>
       <c r="C212" s="111"/>
@@ -20711,7 +20754,7 @@
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="104" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B213" s="104"/>
       <c r="C213" s="104"/>
@@ -20738,7 +20781,7 @@
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B214" s="104"/>
       <c r="C214" s="104"/>
@@ -20794,7 +20837,7 @@
       </c>
       <c r="B216" s="63"/>
       <c r="C216" s="64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D216" s="64"/>
       <c r="E216" s="64"/>
@@ -20803,7 +20846,7 @@
         <v>2026-27</v>
       </c>
       <c r="G216" s="64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H216" s="64"/>
       <c r="I216" s="64"/>
@@ -20814,7 +20857,7 @@
       </c>
       <c r="M216" s="63"/>
       <c r="N216" s="64" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O216" s="63"/>
       <c r="P216" s="63"/>
@@ -20953,7 +20996,7 @@
       </c>
       <c r="B221" s="63"/>
       <c r="C221" s="64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D221" s="64"/>
       <c r="E221" s="64"/>
@@ -21108,7 +21151,7 @@
     </row>
     <row r="226" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="147" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B226" s="147"/>
       <c r="C226" s="147"/>
@@ -21164,7 +21207,7 @@
       </c>
       <c r="B228" s="63"/>
       <c r="C228" s="64" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D228" s="64"/>
       <c r="E228" s="64"/>
@@ -21179,7 +21222,7 @@
       </c>
       <c r="M228" s="63"/>
       <c r="N228" s="64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O228" s="63"/>
       <c r="P228" s="63"/>
@@ -21195,7 +21238,7 @@
       <c r="A229" s="106"/>
       <c r="B229" s="63"/>
       <c r="C229" s="64" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D229" s="64"/>
       <c r="E229" s="64"/>
@@ -21314,7 +21357,7 @@
     </row>
     <row r="233" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="103" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B233" s="103"/>
       <c r="C233" s="103"/>
@@ -21341,7 +21384,7 @@
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="104" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B234" s="104"/>
       <c r="C234" s="104"/>
@@ -21368,7 +21411,7 @@
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="104" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B235" s="104"/>
       <c r="C235" s="104"/>
@@ -21422,7 +21465,7 @@
       <c r="A237" s="79"/>
       <c r="B237" s="63"/>
       <c r="C237" s="129" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D237" s="63"/>
       <c r="E237" s="63"/>
@@ -21435,7 +21478,7 @@
       <c r="L237" s="63"/>
       <c r="M237" s="63"/>
       <c r="N237" s="129" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O237" s="63"/>
       <c r="P237" s="63"/>
@@ -21478,7 +21521,7 @@
       </c>
       <c r="B239" s="63"/>
       <c r="C239" s="64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D239" s="64"/>
       <c r="E239" s="64"/>
@@ -21493,7 +21536,7 @@
       </c>
       <c r="M239" s="63"/>
       <c r="N239" s="64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O239" s="63"/>
       <c r="P239" s="63"/>
@@ -21602,7 +21645,7 @@
       </c>
       <c r="B243" s="63"/>
       <c r="C243" s="64" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D243" s="64"/>
       <c r="E243" s="64"/>
@@ -21617,7 +21660,7 @@
       </c>
       <c r="M243" s="63"/>
       <c r="N243" s="64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O243" s="63"/>
       <c r="P243" s="63"/>
@@ -21726,7 +21769,7 @@
       </c>
       <c r="B247" s="63"/>
       <c r="C247" s="64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D247" s="64"/>
       <c r="E247" s="64"/>
@@ -21741,7 +21784,7 @@
       </c>
       <c r="M247" s="63"/>
       <c r="N247" s="64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O247" s="63"/>
       <c r="P247" s="63"/>
@@ -21850,7 +21893,7 @@
       </c>
       <c r="B251" s="63"/>
       <c r="C251" s="64" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D251" s="64"/>
       <c r="E251" s="64"/>
@@ -21863,7 +21906,7 @@
       <c r="L251" s="63"/>
       <c r="M251" s="63"/>
       <c r="N251" s="129" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O251" s="112"/>
       <c r="P251" s="112"/>
@@ -21925,7 +21968,7 @@
       </c>
       <c r="M253" s="63"/>
       <c r="N253" s="64" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O253" s="63"/>
       <c r="P253" s="63"/>
@@ -21968,7 +22011,7 @@
       </c>
       <c r="B255" s="63"/>
       <c r="C255" s="64" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D255" s="64"/>
       <c r="E255" s="64"/>
@@ -21984,7 +22027,7 @@
         <v>33</v>
       </c>
       <c r="O255" s="149" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P255" s="98"/>
       <c r="Q255" s="98"/>
@@ -22049,7 +22092,7 @@
       <c r="L257" s="63"/>
       <c r="M257" s="63"/>
       <c r="N257" s="129" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O257" s="63"/>
       <c r="P257" s="63"/>
@@ -22092,7 +22135,7 @@
       </c>
       <c r="B259" s="63"/>
       <c r="C259" s="64" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D259" s="64"/>
       <c r="E259" s="64"/>
@@ -22107,7 +22150,7 @@
       </c>
       <c r="M259" s="63"/>
       <c r="N259" s="64" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O259" s="63"/>
       <c r="P259" s="63"/>
@@ -22170,7 +22213,7 @@
         <v>33</v>
       </c>
       <c r="O261" s="136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P261" s="98"/>
       <c r="Q261" s="98"/>
@@ -22218,7 +22261,7 @@
       </c>
       <c r="B263" s="63"/>
       <c r="C263" s="64" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D263" s="64"/>
       <c r="E263" s="64"/>
@@ -22233,7 +22276,7 @@
       </c>
       <c r="M263" s="63"/>
       <c r="N263" s="64" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O263" s="63"/>
       <c r="P263" s="63"/>
@@ -22296,7 +22339,7 @@
         <v>33</v>
       </c>
       <c r="O265" s="136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P265" s="98"/>
       <c r="Q265" s="98"/>
@@ -22344,7 +22387,7 @@
       </c>
       <c r="B267" s="63"/>
       <c r="C267" s="64" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D267" s="64"/>
       <c r="E267" s="64"/>
@@ -22359,7 +22402,7 @@
       </c>
       <c r="M267" s="63"/>
       <c r="N267" s="64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O267" s="63"/>
       <c r="P267" s="63"/>
@@ -22479,7 +22522,7 @@
       </c>
       <c r="M271" s="63"/>
       <c r="N271" s="64" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O271" s="63"/>
       <c r="P271" s="63"/>
@@ -22591,7 +22634,7 @@
       </c>
       <c r="M275" s="63"/>
       <c r="N275" s="64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O275" s="63"/>
       <c r="P275" s="63"/>
@@ -22646,7 +22689,7 @@
         <v>33</v>
       </c>
       <c r="O277" s="136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P277" s="98"/>
       <c r="Q277" s="98"/>
@@ -22690,7 +22733,7 @@
     </row>
     <row r="279" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B279" s="111"/>
       <c r="C279" s="111"/>
@@ -22717,7 +22760,7 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="104" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B280" s="104"/>
       <c r="C280" s="104"/>
@@ -22732,7 +22775,7 @@
         <v>12570</v>
       </c>
       <c r="K280" s="104" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L280" s="104"/>
       <c r="M280" s="104"/>
@@ -22749,7 +22792,7 @@
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="151" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="151"/>
@@ -22805,7 +22848,7 @@
       </c>
       <c r="B283" s="63"/>
       <c r="C283" s="64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D283" s="63"/>
       <c r="E283" s="63"/>
@@ -22820,7 +22863,7 @@
       </c>
       <c r="M283" s="63"/>
       <c r="N283" s="64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O283" s="63"/>
       <c r="P283" s="63"/>
@@ -22836,7 +22879,7 @@
       <c r="A284" s="79"/>
       <c r="B284" s="63"/>
       <c r="C284" s="64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D284" s="63"/>
       <c r="E284" s="63"/>
@@ -22849,7 +22892,7 @@
       <c r="L284" s="63"/>
       <c r="M284" s="63"/>
       <c r="N284" s="90" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O284" s="63"/>
       <c r="P284" s="63"/>
@@ -22950,7 +22993,7 @@
       </c>
       <c r="B288" s="63"/>
       <c r="C288" s="64" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D288" s="63"/>
       <c r="E288" s="63"/>
@@ -22977,7 +23020,7 @@
       <c r="A289" s="79"/>
       <c r="B289" s="63"/>
       <c r="C289" s="64" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D289" s="63"/>
       <c r="E289" s="63"/>
@@ -23102,7 +23145,7 @@
     </row>
     <row r="294" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="103" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B294" s="103"/>
       <c r="C294" s="103"/>
@@ -23158,7 +23201,7 @@
       </c>
       <c r="B296" s="63"/>
       <c r="C296" s="64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D296" s="63"/>
       <c r="E296" s="63"/>
@@ -23882,7 +23925,7 @@
       <c r="W324" s="95"/>
     </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="150">
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="G1:M2"/>
     <mergeCell ref="N1:W1"/>
@@ -23963,6 +24006,7 @@
     <mergeCell ref="H146:I146"/>
     <mergeCell ref="D147:F147"/>
     <mergeCell ref="O149:Q149"/>
+    <mergeCell ref="D150:F150"/>
     <mergeCell ref="D152:F152"/>
     <mergeCell ref="O154:Q154"/>
     <mergeCell ref="D156:F156"/>
@@ -24084,10 +24128,10 @@
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="160" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B2" s="161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C2" s="162" t="n">
         <f aca="false">Admin!B5</f>
@@ -24204,7 +24248,7 @@
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="169" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B5" s="170" t="n">
         <f aca="false">SUM(C5:N5)</f>
@@ -24262,7 +24306,7 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="169" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B6" s="170" t="n">
         <f aca="false">SUM(C6:N6)</f>
@@ -24320,7 +24364,7 @@
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="169" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B7" s="170" t="n">
         <f aca="false">SUM(C7:N7)</f>
@@ -24378,7 +24422,7 @@
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="169" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B8" s="170" t="n">
         <f aca="false">SUM(C8:N8)</f>
@@ -24436,7 +24480,7 @@
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="173" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B9" s="170" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -24995,7 +25039,7 @@
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="169" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B11" s="170" t="n">
         <f aca="false">SUM(C11:N11)</f>
@@ -25312,7 +25356,7 @@
     </row>
     <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="180" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B13" s="177"/>
       <c r="C13" s="177"/>
@@ -25573,7 +25617,7 @@
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="169" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B14" s="170" t="n">
         <f aca="false">SUM(C14:N14)</f>
@@ -25631,7 +25675,7 @@
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="169" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B15" s="170" t="n">
         <f aca="false">SUM(C15:N15)</f>
@@ -25689,7 +25733,7 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="169" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B16" s="170" t="n">
         <f aca="false">SUM(C16:N16)</f>
@@ -25747,7 +25791,7 @@
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="173" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B17" s="170" t="n">
         <f aca="false">SUM(B14:B16)</f>
@@ -26306,7 +26350,7 @@
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="173" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B19" s="170" t="n">
         <f aca="false">B9+B11-B17</f>
@@ -26606,7 +26650,7 @@
     </row>
     <row r="20" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="180" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B20" s="177"/>
       <c r="C20" s="181"/>
@@ -26867,7 +26911,7 @@
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="169" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B21" s="170" t="n">
         <f aca="false">SUM(C21:N21)</f>
@@ -26925,7 +26969,7 @@
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="182" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B22" s="170" t="n">
         <f aca="false">SUM(C22:N22)</f>
@@ -26983,7 +27027,7 @@
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="182" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B23" s="170" t="n">
         <f aca="false">SUM(C23:N23)</f>
@@ -27041,7 +27085,7 @@
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="182" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" s="170" t="n">
         <f aca="false">SUM(C24:N24)</f>
@@ -27099,7 +27143,7 @@
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="182" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" s="170" t="n">
         <f aca="false">SUM(C25:N25)</f>
@@ -27157,7 +27201,7 @@
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="182" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" s="170" t="n">
         <f aca="false">SUM(C26:N26)</f>
@@ -27215,7 +27259,7 @@
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" s="170" t="n">
         <f aca="false">SUM(C27:N27)</f>
@@ -27273,7 +27317,7 @@
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="182" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" s="170" t="n">
         <f aca="false">SUM(C28:N28)</f>
@@ -27331,7 +27375,7 @@
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="182" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B29" s="170" t="n">
         <f aca="false">SUM(C29:N29)</f>
@@ -27389,7 +27433,7 @@
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" s="170" t="n">
         <f aca="false">SUM(C30:N30)</f>
@@ -27447,7 +27491,7 @@
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="182" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" s="170" t="n">
         <f aca="false">SUM(C31:N31)</f>
@@ -27505,7 +27549,7 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="182" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B32" s="170" t="n">
         <f aca="false">SUM(C32:N32)</f>
@@ -27563,7 +27607,7 @@
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="169" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" s="170" t="n">
         <f aca="false">SUM(C33:N33)</f>
@@ -27621,7 +27665,7 @@
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="169" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B34" s="170" t="n">
         <f aca="false">SUM(C34:N34)</f>
@@ -27679,7 +27723,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="173" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
@@ -27754,7 +27798,7 @@
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="173" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
@@ -27812,7 +27856,7 @@
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="169" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B38" s="170" t="n">
         <f aca="false">SUM(C38:N38)</f>
@@ -27870,7 +27914,7 @@
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="173" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
@@ -27945,7 +27989,7 @@
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="187" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" s="156"/>
       <c r="C41" s="157"/>
@@ -27964,7 +28008,7 @@
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="182" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B42" s="177" t="n">
         <f aca="false">SUM(C42:N42)</f>
@@ -28022,7 +28066,7 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="182" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B43" s="177" t="n">
         <f aca="false">SUM(C43:N43)</f>
@@ -28080,7 +28124,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="182" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
@@ -28138,7 +28182,7 @@
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="188" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
@@ -28196,7 +28240,7 @@
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="182" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B46" s="177" t="n">
         <f aca="false">SUM(C46:N46)</f>
@@ -28271,7 +28315,7 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="182" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B49" s="170" t="n">
         <f aca="false">SUM(C49:N49)</f>
@@ -28386,25 +28430,25 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="195"/>
       <c r="B2" s="197" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C2" s="197" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D2" s="197" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F2" s="197" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G2" s="197" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H2" s="197" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I2" s="195"/>
       <c r="J2" s="196"/>
@@ -28929,7 +28973,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="195"/>
       <c r="B5" s="195" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C5" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -28957,7 +29001,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="195"/>
       <c r="B6" s="195" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C6" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -28985,7 +29029,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="195"/>
       <c r="B7" s="195" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C7" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -29283,7 +29327,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="195"/>
       <c r="B10" s="202" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C10" s="195"/>
       <c r="D10" s="195"/>
@@ -29307,7 +29351,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="195"/>
       <c r="B12" s="195" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C12" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -29335,7 +29379,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="195"/>
       <c r="B13" s="195" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C13" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -29363,7 +29407,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="195"/>
       <c r="B14" s="195" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C14" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -29391,7 +29435,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="195"/>
       <c r="B15" s="195" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C15" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -29419,7 +29463,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="195"/>
       <c r="B16" s="195" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -29447,7 +29491,7 @@
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="195"/>
       <c r="B17" s="195" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -29475,7 +29519,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="195"/>
       <c r="B18" s="195" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C18" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -29503,7 +29547,7 @@
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="195"/>
       <c r="B19" s="195" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C19" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -29531,7 +29575,7 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="195"/>
       <c r="B20" s="195" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C20" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -29559,7 +29603,7 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="195"/>
       <c r="B21" s="195" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C21" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -29587,7 +29631,7 @@
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="195"/>
       <c r="B22" s="195" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C22" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -29626,7 +29670,7 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="195"/>
       <c r="B24" s="195" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C24" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -29654,7 +29698,7 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="195"/>
       <c r="B25" s="195" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C25" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C49:E49)</f>
@@ -29682,7 +29726,7 @@
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="195"/>
       <c r="B26" s="195" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
@@ -29732,7 +29776,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="195"/>
       <c r="B29" s="202" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
@@ -29828,7 +29872,7 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="195"/>
       <c r="B36" s="195" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C36" s="200" t="n">
         <f aca="false">C7*$I$36</f>
@@ -29851,7 +29895,7 @@
         <v>269.4</v>
       </c>
       <c r="H36" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I36" s="195" t="n">
         <v>0.02</v>
@@ -29860,7 +29904,7 @@
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="195"/>
       <c r="B37" s="195" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C37" s="200" t="n">
         <f aca="false">C24*$I$37</f>
@@ -29883,7 +29927,7 @@
         <v>200</v>
       </c>
       <c r="H37" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I37" s="195" t="n">
         <v>0.03</v>
@@ -29892,7 +29936,7 @@
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="195"/>
       <c r="B38" s="195" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C38" s="200" t="n">
         <f aca="false">C12*$I$38</f>
@@ -29915,7 +29959,7 @@
         <v>3709.42933333333</v>
       </c>
       <c r="H38" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I38" s="195" t="n">
         <v>0.04</v>
@@ -29924,7 +29968,7 @@
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="195"/>
       <c r="B39" s="195" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C39" s="200" t="n">
         <f aca="false">C17*$I$39</f>
@@ -29947,7 +29991,7 @@
         <v>1996.0625</v>
       </c>
       <c r="H39" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I39" s="195" t="n">
         <v>0.25</v>
@@ -29956,7 +30000,7 @@
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="195"/>
       <c r="B40" s="195" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" s="200" t="n">
         <f aca="false">C13*$I$40</f>
@@ -29979,7 +30023,7 @@
         <v>660</v>
       </c>
       <c r="H40" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I40" s="195" t="n">
         <v>0.05</v>
@@ -29988,7 +30032,7 @@
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="195"/>
       <c r="B41" s="195" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C41" s="200" t="n">
         <f aca="false">C14*$I$41</f>
@@ -30011,7 +30055,7 @@
         <v>57</v>
       </c>
       <c r="H41" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I41" s="195" t="n">
         <v>0.06</v>
@@ -30020,7 +30064,7 @@
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="195"/>
       <c r="B42" s="195" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C42" s="200" t="n">
         <f aca="false">C15*$I$42</f>
@@ -30043,7 +30087,7 @@
         <v>212.45</v>
       </c>
       <c r="H42" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I42" s="195" t="n">
         <v>0.07</v>
@@ -30052,7 +30096,7 @@
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="195"/>
       <c r="B43" s="195" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C43" s="200" t="n">
         <f aca="false">C18*$I$43</f>
@@ -30075,7 +30119,7 @@
         <v>327.333333333333</v>
       </c>
       <c r="H43" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I43" s="195" t="n">
         <v>0.08</v>
@@ -30084,7 +30128,7 @@
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="195"/>
       <c r="B44" s="195" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C44" s="200" t="n">
         <f aca="false">C25</f>
@@ -30107,14 +30151,14 @@
         <v>291.666666666667</v>
       </c>
       <c r="H44" s="195" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I44" s="195"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="195"/>
       <c r="B45" s="195" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C45" s="200" t="n">
         <f aca="false">C21*$I$45</f>
@@ -30137,7 +30181,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I45" s="195" t="n">
         <v>0.09</v>
@@ -30146,7 +30190,7 @@
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="195"/>
       <c r="B46" s="195" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C46" s="200" t="n">
         <f aca="false">C16*$I$46</f>
@@ -30169,7 +30213,7 @@
         <v>390</v>
       </c>
       <c r="H46" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I46" s="195" t="n">
         <v>0.1</v>
@@ -30178,7 +30222,7 @@
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="195"/>
       <c r="B47" s="195" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C47" s="200" t="n">
         <f aca="false">C20*$I$47</f>
@@ -30201,7 +30245,7 @@
         <v>-33</v>
       </c>
       <c r="H47" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I47" s="195" t="n">
         <v>0.11</v>
@@ -30210,7 +30254,7 @@
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="195"/>
       <c r="B48" s="195" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C48" s="200" t="n">
         <f aca="false">C19*$I$48</f>
@@ -30233,7 +30277,7 @@
         <v>831</v>
       </c>
       <c r="H48" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I48" s="195" t="n">
         <v>0.12</v>
@@ -30242,7 +30286,7 @@
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="195"/>
       <c r="B49" s="195" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C49" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C34:E34)</f>
@@ -30265,14 +30309,14 @@
         <v>20865</v>
       </c>
       <c r="H49" s="195" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I49" s="195"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="195"/>
       <c r="B50" s="195" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C50" s="200" t="n">
         <f aca="false">C22*$I$50</f>
@@ -30295,7 +30339,7 @@
         <v>420.116666666666</v>
       </c>
       <c r="H50" s="195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I50" s="195" t="n">
         <v>0.13</v>
@@ -30368,14 +30412,14 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="211"/>
       <c r="B2" s="215" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C2" s="216" t="str">
         <f aca="false">Admin!L2</f>
         <v>2026-27</v>
       </c>
       <c r="D2" s="217" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E2" s="217"/>
       <c r="F2" s="217"/>
@@ -30402,13 +30446,13 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="211"/>
       <c r="B5" s="222" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C5" s="222"/>
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>125308.8085</v>
+        <v>124284.150965753</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -30417,7 +30461,7 @@
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="211"/>
       <c r="B6" s="220" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C6" s="220" t="str">
         <f aca="false">C2</f>
@@ -30426,7 +30470,7 @@
       <c r="D6" s="225"/>
       <c r="E6" s="218" t="n">
         <f aca="false">IF(E5&lt;=0,0,MAX(0,Admin!N$4-MAX(0,E5-Admin!N$5)/2))</f>
-        <v>0</v>
+        <v>427.924517123494</v>
       </c>
       <c r="F6" s="214"/>
       <c r="G6" s="218"/>
@@ -30435,13 +30479,13 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="211"/>
       <c r="B7" s="222" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C7" s="222"/>
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>125308.8085</v>
+        <v>123856.22644863</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -30450,7 +30494,7 @@
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="211"/>
       <c r="B8" s="220" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C8" s="220" t="n">
         <f aca="false">Admin!N$11</f>
@@ -30472,7 +30516,7 @@
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="211"/>
       <c r="B9" s="220" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C9" s="220" t="n">
         <f aca="false">Admin!M$11</f>
@@ -30484,7 +30528,7 @@
       </c>
       <c r="E9" s="213" t="n">
         <f aca="false">IF(E7&gt;C9,(MIN(E7,C10)-C9)*D9,0)</f>
-        <v>34976</v>
+        <v>34462.4905794518</v>
       </c>
       <c r="F9" s="214"/>
       <c r="G9" s="218"/>
@@ -30493,7 +30537,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="211"/>
       <c r="B10" s="220" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C10" s="220" t="n">
         <f aca="false">Admin!N$13</f>
@@ -30505,7 +30549,7 @@
       </c>
       <c r="E10" s="213" t="n">
         <f aca="false">IF(E7&gt;C10,(E7-C10)*D10,0)</f>
-        <v>75.9638249998163</v>
+        <v>0</v>
       </c>
       <c r="F10" s="214"/>
       <c r="G10" s="218"/>
@@ -30514,13 +30558,13 @@
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="211"/>
       <c r="B11" s="228" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C11" s="229"/>
       <c r="D11" s="230"/>
       <c r="E11" s="231" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>42591.9638249998</v>
+        <v>42002.4905794518</v>
       </c>
       <c r="F11" s="232"/>
       <c r="G11" s="233"/>
@@ -30529,7 +30573,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="211"/>
       <c r="B12" s="220" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C12" s="220"/>
       <c r="D12" s="234"/>
@@ -30544,7 +30588,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="211"/>
       <c r="B13" s="235" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C13" s="236" t="n">
         <f aca="false">Admin!B21</f>
@@ -30569,7 +30613,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="211"/>
       <c r="B15" s="239" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C15" s="239"/>
       <c r="D15" s="226" t="n">
@@ -30587,7 +30631,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="211"/>
       <c r="B16" s="239" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C16" s="239"/>
       <c r="D16" s="226" t="n">
@@ -30596,7 +30640,7 @@
       </c>
       <c r="E16" s="240" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1500.77616999999</v>
+        <v>1480.28301931506</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -30615,13 +30659,13 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="211"/>
       <c r="B18" s="241" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C18" s="241"/>
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>46354.7399949998</v>
+        <v>45744.7735987669</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -30648,11 +30692,11 @@
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="211"/>
       <c r="B21" s="228" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C21" s="243"/>
       <c r="D21" s="244" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E21" s="244"/>
       <c r="F21" s="244"/>
@@ -30672,10 +30716,10 @@
       <c r="B23" s="220"/>
       <c r="C23" s="220"/>
       <c r="D23" s="246" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E23" s="247" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F23" s="248"/>
       <c r="G23" s="218"/>
@@ -31192,18 +31236,18 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="211"/>
       <c r="B25" s="220" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C25" s="250" t="str">
         <f aca="false">Admin!B24</f>
         <v>2027-28</v>
       </c>
       <c r="D25" s="251" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E25" s="240" t="n">
         <f aca="false">E18</f>
-        <v>46354.7399949998</v>
+        <v>45744.7735987669</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -31211,7 +31255,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="211"/>
       <c r="B26" s="220" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C26" s="220"/>
       <c r="D26" s="252" t="n">
@@ -31220,7 +31264,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23177.3699974999</v>
+        <v>22872.3867993834</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -31228,7 +31272,7 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="211"/>
       <c r="B27" s="220" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C27" s="220"/>
       <c r="D27" s="252" t="n">
@@ -31237,7 +31281,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23177.3699974999</v>
+        <v>22872.3867993834</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -31254,7 +31298,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="211"/>
       <c r="B29" s="253" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C29" s="254"/>
       <c r="D29" s="237"/>
@@ -31265,7 +31309,7 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="211"/>
       <c r="B30" s="255" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C30" s="255"/>
       <c r="D30" s="211"/>
@@ -31276,7 +31320,7 @@
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="211"/>
       <c r="B31" s="258" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C31" s="258"/>
       <c r="D31" s="259"/>
@@ -31287,7 +31331,7 @@
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="211"/>
       <c r="B32" s="260" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C32" s="258"/>
       <c r="D32" s="259"/>
@@ -31298,7 +31342,7 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="211"/>
       <c r="B33" s="254" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C33" s="254"/>
       <c r="D33" s="259"/>
@@ -31309,7 +31353,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="211"/>
       <c r="B34" s="254" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C34" s="254"/>
       <c r="D34" s="259"/>
@@ -31320,7 +31364,7 @@
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="211"/>
       <c r="B35" s="254" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C35" s="254"/>
       <c r="D35" s="259"/>
@@ -31395,32 +31439,32 @@
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="267"/>
       <c r="B2" s="268" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" s="269" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D2" s="269" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E2" s="269" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F2" s="269" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G2" s="269" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H2" s="269" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I2" s="269" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J2" s="270"/>
       <c r="K2" s="268" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L2" s="271"/>
       <c r="M2" s="272"/>
@@ -31672,7 +31716,7 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="267"/>
       <c r="B3" s="273" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C3" s="273"/>
       <c r="D3" s="274"/>
@@ -31966,7 +32010,7 @@
       </c>
       <c r="J4" s="158"/>
       <c r="K4" s="278" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L4" s="164"/>
     </row>
@@ -32120,7 +32164,7 @@
       </c>
       <c r="J8" s="158"/>
       <c r="K8" s="278" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L8" s="164"/>
     </row>
@@ -32472,7 +32516,7 @@
       <c r="F1" s="287"/>
       <c r="G1" s="287"/>
       <c r="H1" s="288" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I1" s="288"/>
       <c r="J1" s="288"/>
@@ -32480,7 +32524,7 @@
       <c r="L1" s="288"/>
       <c r="M1" s="287"/>
       <c r="N1" s="288" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O1" s="288"/>
       <c r="P1" s="288"/>
@@ -32488,7 +32532,7 @@
       <c r="R1" s="288"/>
       <c r="S1" s="287"/>
       <c r="T1" s="288" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U1" s="288"/>
       <c r="V1" s="288"/>
@@ -32508,63 +32552,63 @@
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="292"/>
       <c r="B2" s="293" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C2" s="294"/>
       <c r="D2" s="295" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E2" s="296"/>
       <c r="F2" s="295" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G2" s="296"/>
       <c r="H2" s="297" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I2" s="296"/>
       <c r="J2" s="295" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K2" s="296"/>
       <c r="L2" s="295" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M2" s="296"/>
       <c r="N2" s="297" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O2" s="296"/>
       <c r="P2" s="295" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q2" s="296"/>
       <c r="R2" s="295" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S2" s="296"/>
       <c r="T2" s="297" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U2" s="296"/>
       <c r="V2" s="295" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="W2" s="296"/>
       <c r="X2" s="298" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y2" s="299"/>
       <c r="Z2" s="295" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA2" s="296"/>
       <c r="AB2" s="295" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AC2" s="300"/>
       <c r="AD2" s="301" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AE2" s="301"/>
       <c r="AF2" s="301"/>
@@ -32825,7 +32869,7 @@
       <c r="AB3" s="305"/>
       <c r="AC3" s="164"/>
       <c r="AD3" s="309" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AE3" s="309"/>
       <c r="AF3" s="309"/>
@@ -32835,7 +32879,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="276"/>
       <c r="B4" s="310" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C4" s="310"/>
       <c r="D4" s="310"/>
@@ -33215,7 +33259,7 @@
       <c r="AB11" s="177"/>
       <c r="AC11" s="164"/>
       <c r="AD11" s="309" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AE11" s="309"/>
       <c r="AF11" s="309"/>
@@ -33445,7 +33489,7 @@
       <c r="AB15" s="177"/>
       <c r="AC15" s="164"/>
       <c r="AD15" s="309" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AE15" s="309"/>
       <c r="AF15" s="309"/>
@@ -33675,7 +33719,7 @@
       <c r="AB19" s="177"/>
       <c r="AC19" s="164"/>
       <c r="AD19" s="309" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AE19" s="309"/>
       <c r="AF19" s="309"/>
@@ -33905,7 +33949,7 @@
       <c r="AB23" s="177"/>
       <c r="AC23" s="164"/>
       <c r="AD23" s="309" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AE23" s="309"/>
       <c r="AF23" s="309"/>
@@ -34213,7 +34257,7 @@
       </c>
       <c r="AC28" s="164"/>
       <c r="AD28" s="309" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AE28" s="309"/>
       <c r="AF28" s="309"/>
@@ -34431,10 +34475,10 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="158"/>
       <c r="B2" s="330" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C2" s="161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D2" s="162" t="n">
         <f aca="false">Admin!B5</f>
@@ -34554,7 +34598,7 @@
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="178"/>
       <c r="B5" s="332" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C5" s="170" t="n">
         <f aca="false">SUM(D5:O5)</f>
@@ -35113,7 +35157,7 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="158"/>
       <c r="B7" s="334" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C7" s="170" t="n">
         <f aca="false">SUM(D7:O7)</f>
@@ -35190,7 +35234,7 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="178"/>
       <c r="B9" s="333" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C9" s="170" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -35749,7 +35793,7 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="178"/>
       <c r="B11" s="332" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C11" s="170" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -36308,7 +36352,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="158"/>
       <c r="B13" s="333" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
@@ -36385,7 +36429,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="158"/>
       <c r="B15" s="332" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -36444,7 +36488,7 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="158"/>
       <c r="B16" s="334" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C16" s="170" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -36503,7 +36547,7 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="158"/>
       <c r="B17" s="335" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
@@ -36580,10 +36624,10 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="158"/>
       <c r="B19" s="337" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C19" s="161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D19" s="162" t="n">
         <f aca="false">D2</f>
@@ -36716,7 +36760,7 @@
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="178"/>
       <c r="B22" s="332" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="170" t="n">
         <f aca="false">SUM(D22:O22)</f>
@@ -37275,7 +37319,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="158"/>
       <c r="B24" s="334" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C24" s="170" t="n">
         <f aca="false">SUM(D24:O24)</f>
@@ -37352,7 +37396,7 @@
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="178"/>
       <c r="B26" s="333" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="170" t="n">
         <f aca="false">SUM(D26:O26)</f>
@@ -37911,7 +37955,7 @@
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="178"/>
       <c r="B28" s="332" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="170" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -38470,7 +38514,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="158"/>
       <c r="B30" s="333" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -38547,7 +38591,7 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="158"/>
       <c r="B32" s="332" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
@@ -38606,7 +38650,7 @@
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="158"/>
       <c r="B33" s="334" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" s="170" t="n">
         <f aca="false">SUM(D33:O33)</f>
@@ -38665,7 +38709,7 @@
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="158"/>
       <c r="B34" s="335" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
@@ -38742,7 +38786,7 @@
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="158"/>
       <c r="B36" s="338" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C36" s="338"/>
       <c r="D36" s="158"/>
@@ -38762,7 +38806,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="158"/>
       <c r="B37" s="169" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C37" s="339" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
@@ -38785,7 +38829,7 @@
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="158"/>
       <c r="B38" s="169" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C38" s="339" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$AC$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
@@ -38808,7 +38852,7 @@
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="158"/>
       <c r="B39" s="169" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
@@ -38831,7 +38875,7 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="158"/>
       <c r="B40" s="182" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C40" s="339" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
@@ -38854,7 +38898,7 @@
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="158"/>
       <c r="B41" s="182" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
@@ -38877,7 +38921,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="158"/>
       <c r="B42" s="182" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C42" s="339" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
@@ -38900,7 +38944,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="158"/>
       <c r="B43" s="182" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
@@ -38923,7 +38967,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="158"/>
       <c r="B44" s="182" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C44" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
@@ -38946,7 +38990,7 @@
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="158"/>
       <c r="B45" s="182" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C45" s="339" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
@@ -38969,7 +39013,7 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="158"/>
       <c r="B46" s="182" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44+C45</f>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="458">
   <si>
     <r>
       <rPr>
@@ -467,6 +467,42 @@
   </si>
   <si>
     <t xml:space="preserve">Calculated no entry required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTER: Overlap profit brought forward from earlier years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTER: Transition profit not yet treated as arising at the start of this tax year</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - box 69; the 2023-24 return uses all of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - your 2023-24 transition profit less every amount already charged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlap relief used this year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transition profit treated as arising this year, before any election</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlap profit carried forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTER: Additional transition profit you elect to treat as arising this year</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - the election itself goes in box 103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTER: Profit of your next accounting period, a loss with a minus sign, provisional until its accounts are final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transition profit carried forward to next year</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - only if box 9 is not 31 March to 5 April; box 68 apportions both periods to the tax year by days</t>
   </si>
   <si>
     <t xml:space="preserve">Copyright (C) 2006-2026 DIY Accounting Limited</t>
@@ -1348,13 +1384,19 @@
     <t xml:space="preserve">this year's adjusted profit</t>
   </si>
   <si>
+    <t xml:space="preserve">Spread of the transition profit treated as arising in this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tax year - see the working sheet in the notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any other business income not included in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boxes 15, 16 or 60</t>
+  </si>
+  <si>
     <t xml:space="preserve">Boxes 69 and 70 are not in use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any other business income not included in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boxes 15, 16 or 60</t>
   </si>
   <si>
     <t xml:space="preserve">Adjustment for change of accounting practice</t>
@@ -1754,6 +1796,9 @@
   </si>
   <si>
     <t xml:space="preserve">Amounts Payable by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Tax on transition profit (box 73.3), charged as the top slice</t>
   </si>
   <si>
     <t xml:space="preserve">Class 4 NI Contribution Lower - Upper profits</t>
@@ -3850,15 +3895,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="175" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="true"/>
-    </xf>
     <xf numFmtId="164" fontId="32" fillId="2" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
     <xf numFmtId="175" fontId="32" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="175" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
@@ -6423,7 +6468,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IW59"/>
+  <dimension ref="A1:IW77"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.66"/>
@@ -7540,10 +7585,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
-      <c r="N32" s="27" t="n">
-        <f aca="false">Admin!B17</f>
-        <v>46482</v>
-      </c>
+      <c r="N32" s="27"/>
       <c r="O32" s="27"/>
       <c r="P32" s="27"/>
       <c r="Q32" s="27"/>
@@ -8705,18 +8747,607 @@
       <c r="V56" s="36"/>
       <c r="W56" s="37"/>
     </row>
-    <row r="58" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+    <row r="57" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="39" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="39" t="s">
         <v>39</v>
       </c>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="8"/>
+      <c r="S57" s="8"/>
+      <c r="T57" s="8"/>
+      <c r="U57" s="8"/>
+      <c r="V57" s="8"/>
+      <c r="W57" s="24"/>
+    </row>
+    <row r="58" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="8"/>
+      <c r="S58" s="8"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="8"/>
+      <c r="V58" s="8"/>
+      <c r="W58" s="24"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="41" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="O59" s="41" t="n">
+        <v>6000</v>
+      </c>
+      <c r="P59" s="41"/>
+      <c r="Q59" s="41"/>
+      <c r="R59" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="S59" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="24"/>
+    </row>
+    <row r="60" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="26"/>
+      <c r="Q60" s="26"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="W60" s="24"/>
+    </row>
+    <row r="61" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="8"/>
+      <c r="S61" s="8"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="8"/>
+      <c r="V61" s="8"/>
+      <c r="W61" s="24"/>
+    </row>
+    <row r="62" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="8"/>
+      <c r="S62" s="8"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="8"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="24"/>
+    </row>
+    <row r="63" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
+      <c r="Q63" s="26"/>
+      <c r="R63" s="7"/>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="24"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="49" t="n">
+        <f aca="false">IF(YEAR(Admin!$B$17)=2024,D59,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="O64" s="49" t="n">
+        <f aca="false">IF(YEAR(Admin!$B$17)&lt;2024,0,O59/MAX(1,2029-YEAR(Admin!$B$17)))</f>
+        <v>3000</v>
+      </c>
+      <c r="P64" s="49"/>
+      <c r="Q64" s="49"/>
+      <c r="R64" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="S64" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="7"/>
+      <c r="V64" s="7"/>
+      <c r="W64" s="24"/>
+    </row>
+    <row r="65" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+      <c r="M65" s="7"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="26"/>
+      <c r="R65" s="7"/>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="24"/>
+    </row>
+    <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
+      <c r="Q66" s="8"/>
+      <c r="R66" s="8"/>
+      <c r="S66" s="8"/>
+      <c r="T66" s="8"/>
+      <c r="U66" s="8"/>
+      <c r="V66" s="8"/>
+      <c r="W66" s="24"/>
+    </row>
+    <row r="67" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="8"/>
+      <c r="S67" s="8"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="8"/>
+      <c r="V67" s="8"/>
+      <c r="W67" s="24"/>
+    </row>
+    <row r="68" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="26"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="26"/>
+      <c r="Q68" s="26"/>
+      <c r="R68" s="7"/>
+      <c r="S68" s="7"/>
+      <c r="T68" s="7"/>
+      <c r="U68" s="7"/>
+      <c r="V68" s="7"/>
+      <c r="W68" s="24"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" s="49" t="n">
+        <f aca="false">D59-D64</f>
+        <v>2400</v>
+      </c>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="O69" s="41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P69" s="41"/>
+      <c r="Q69" s="41"/>
+      <c r="R69" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="S69" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="7"/>
+      <c r="V69" s="7"/>
+      <c r="W69" s="24"/>
+    </row>
+    <row r="70" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="26"/>
+      <c r="R70" s="7"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
+      <c r="U70" s="7"/>
+      <c r="V70" s="7"/>
+      <c r="W70" s="24"/>
+    </row>
+    <row r="71" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="7"/>
+      <c r="N71" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8"/>
+      <c r="Q71" s="8"/>
+      <c r="R71" s="8"/>
+      <c r="S71" s="8"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="8"/>
+      <c r="V71" s="8"/>
+      <c r="W71" s="24"/>
+    </row>
+    <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
+      <c r="Q72" s="8"/>
+      <c r="R72" s="8"/>
+      <c r="S72" s="8"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="8"/>
+      <c r="V72" s="8"/>
+      <c r="W72" s="24"/>
+    </row>
+    <row r="73" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+      <c r="Q73" s="26"/>
+      <c r="R73" s="7"/>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="24"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" s="41"/>
+      <c r="E74" s="41"/>
+      <c r="F74" s="41"/>
+      <c r="G74" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H74" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="O74" s="49" t="n">
+        <f aca="false">O59-O64-O69</f>
+        <v>2000</v>
+      </c>
+      <c r="P74" s="49"/>
+      <c r="Q74" s="49"/>
+      <c r="R74" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="S74" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="7"/>
+      <c r="V74" s="7"/>
+      <c r="W74" s="24"/>
+    </row>
+    <row r="75" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+      <c r="Q75" s="26"/>
+      <c r="R75" s="7"/>
+      <c r="S75" s="7"/>
+      <c r="T75" s="7"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="7"/>
+      <c r="W75" s="24"/>
+    </row>
+    <row r="76" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="34">
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="C5:J5"/>
     <mergeCell ref="O5:P5"/>
@@ -8743,6 +9374,14 @@
     <mergeCell ref="O50:Q50"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="O55:Q55"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="O59:Q59"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="O64:Q64"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="O69:Q69"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="O74:Q74"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8779,7 +9418,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="344" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="345"/>
@@ -8802,7 +9441,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="348" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="E2" s="348"/>
       <c r="F2" s="348"/>
@@ -8813,7 +9452,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="350" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="K2" s="350"/>
       <c r="L2" s="348" t="str">
@@ -8850,7 +9489,7 @@
       </c>
       <c r="C4" s="63"/>
       <c r="D4" s="354" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E4" s="354"/>
       <c r="F4" s="354"/>
@@ -8859,7 +9498,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="354" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="J4" s="354"/>
       <c r="K4" s="354"/>
@@ -8879,7 +9518,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="354" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="E5" s="354"/>
       <c r="F5" s="354"/>
@@ -8888,7 +9527,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="354" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="J5" s="354"/>
       <c r="K5" s="354"/>
@@ -8908,7 +9547,7 @@
       </c>
       <c r="C6" s="63"/>
       <c r="D6" s="63" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="E6" s="63"/>
       <c r="F6" s="63"/>
@@ -8917,7 +9556,7 @@
       </c>
       <c r="H6" s="63"/>
       <c r="I6" s="354" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="J6" s="354"/>
       <c r="K6" s="354"/>
@@ -8927,7 +9566,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="351" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8937,14 +9576,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="354" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="E7" s="354"/>
       <c r="F7" s="354"/>
       <c r="G7" s="351"/>
       <c r="H7" s="63"/>
       <c r="I7" s="354" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="J7" s="354"/>
       <c r="K7" s="354"/>
@@ -8954,7 +9593,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="351" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8969,7 +9608,7 @@
       <c r="G8" s="357"/>
       <c r="H8" s="63"/>
       <c r="I8" s="354" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="J8" s="354"/>
       <c r="K8" s="354"/>
@@ -8979,7 +9618,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="351" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8989,7 +9628,7 @@
       </c>
       <c r="C9" s="63"/>
       <c r="D9" s="63" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="E9" s="351"/>
       <c r="F9" s="63"/>
@@ -8998,18 +9637,18 @@
       </c>
       <c r="H9" s="63"/>
       <c r="I9" s="354" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="J9" s="354"/>
       <c r="K9" s="354"/>
       <c r="L9" s="358" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="M9" s="358" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="N9" s="359" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="O9" s="351"/>
     </row>
@@ -9020,7 +9659,7 @@
       </c>
       <c r="C10" s="63"/>
       <c r="D10" s="63" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="E10" s="351"/>
       <c r="F10" s="63"/>
@@ -9043,16 +9682,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="348" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="E11" s="348"/>
       <c r="F11" s="348"/>
       <c r="G11" s="351" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="360" t="n">
@@ -9082,7 +9721,7 @@
       <c r="G12" s="351"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="360" t="n">
@@ -9104,7 +9743,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="354" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="E13" s="354"/>
       <c r="F13" s="354"/>
@@ -9113,7 +9752,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="360" t="n">
@@ -9135,7 +9774,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="354" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="E14" s="354"/>
       <c r="F14" s="354"/>
@@ -9144,7 +9783,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="348" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="J14" s="348"/>
       <c r="K14" s="348"/>
@@ -9163,7 +9802,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="354" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E15" s="354"/>
       <c r="F15" s="354"/>
@@ -9186,7 +9825,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="354" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="E16" s="354"/>
       <c r="F16" s="354"/>
@@ -9195,7 +9834,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="354" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="J16" s="354"/>
       <c r="K16" s="354"/>
@@ -9203,7 +9842,7 @@
         <v>3.65</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="N16" s="357" t="n">
         <v>7105</v>
@@ -9219,7 +9858,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="354" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="E17" s="354"/>
       <c r="F17" s="354"/>
@@ -9261,24 +9900,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="348" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="E19" s="348"/>
       <c r="F19" s="351" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="G19" s="351" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="363" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="J19" s="363"/>
       <c r="K19" s="363"/>
       <c r="L19" s="63"/>
       <c r="M19" s="364" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -9315,7 +9954,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="354" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="E21" s="354"/>
       <c r="F21" s="357" t="n">
@@ -9340,7 +9979,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="357" t="n">
@@ -9351,13 +9990,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="363" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="J22" s="363"/>
       <c r="K22" s="363"/>
       <c r="L22" s="63"/>
       <c r="M22" s="364" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -9365,7 +10004,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="353" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -9390,11 +10029,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="353" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="348" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="E24" s="348"/>
       <c r="F24" s="63"/>
@@ -9432,7 +10071,7 @@
       <c r="B26" s="367"/>
       <c r="C26" s="63"/>
       <c r="D26" s="354" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E26" s="354"/>
       <c r="F26" s="357" t="n">
@@ -9453,7 +10092,7 @@
       <c r="B27" s="367"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="355" t="n">
@@ -9559,7 +10198,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -9567,7 +10206,7 @@
       <c r="E1" s="51"/>
       <c r="F1" s="51"/>
       <c r="G1" s="52" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H1" s="52"/>
       <c r="I1" s="52"/>
@@ -9577,7 +10216,7 @@
       <c r="M1" s="52"/>
       <c r="N1" s="52"/>
       <c r="O1" s="53" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="P1" s="53"/>
       <c r="Q1" s="53"/>
@@ -9604,7 +10243,7 @@
       <c r="M2" s="52"/>
       <c r="N2" s="52"/>
       <c r="O2" s="54" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="P2" s="54"/>
       <c r="Q2" s="55" t="n">
@@ -9615,7 +10254,7 @@
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
       <c r="U2" s="56" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="V2" s="55" t="n">
         <f aca="false">Admin!B17</f>
@@ -9884,7 +10523,7 @@
       </c>
       <c r="M12" s="63"/>
       <c r="N12" s="64" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="O12" s="64"/>
       <c r="P12" s="64"/>
@@ -9914,7 +10553,7 @@
       <c r="L13" s="63"/>
       <c r="M13" s="63"/>
       <c r="N13" s="80" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O13" s="64"/>
       <c r="P13" s="64"/>
@@ -10027,7 +10666,7 @@
       </c>
       <c r="M17" s="63"/>
       <c r="N17" s="64" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="O17" s="64"/>
       <c r="P17" s="64"/>
@@ -10057,7 +10696,7 @@
       <c r="L18" s="63"/>
       <c r="M18" s="63"/>
       <c r="N18" s="85" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="O18" s="85"/>
       <c r="P18" s="85"/>
@@ -10199,7 +10838,7 @@
       </c>
       <c r="M23" s="64"/>
       <c r="N23" s="64" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="O23" s="90"/>
       <c r="P23" s="64"/>
@@ -10220,7 +10859,7 @@
       </c>
       <c r="B24" s="63"/>
       <c r="C24" s="64" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D24" s="63"/>
       <c r="E24" s="63"/>
@@ -10249,7 +10888,7 @@
       <c r="A25" s="79"/>
       <c r="B25" s="63"/>
       <c r="C25" s="64" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D25" s="63"/>
       <c r="E25" s="63"/>
@@ -10276,7 +10915,7 @@
       <c r="A26" s="79"/>
       <c r="B26" s="63"/>
       <c r="C26" s="80" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D26" s="81"/>
       <c r="E26" s="81"/>
@@ -10306,7 +10945,7 @@
       <c r="A27" s="79"/>
       <c r="B27" s="63"/>
       <c r="C27" s="80" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D27" s="63"/>
       <c r="E27" s="63"/>
@@ -10346,7 +10985,7 @@
       </c>
       <c r="M28" s="63"/>
       <c r="N28" s="80" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="O28" s="81"/>
       <c r="P28" s="81"/>
@@ -10373,7 +11012,7 @@
       <c r="L29" s="63"/>
       <c r="M29" s="63"/>
       <c r="N29" s="92" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="O29" s="81"/>
       <c r="P29" s="81"/>
@@ -10522,7 +11161,7 @@
       </c>
       <c r="B35" s="63"/>
       <c r="C35" s="64" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D35" s="64"/>
       <c r="E35" s="64"/>
@@ -10537,7 +11176,7 @@
       </c>
       <c r="M35" s="63"/>
       <c r="N35" s="64" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="O35" s="64"/>
       <c r="P35" s="64"/>
@@ -10553,7 +11192,7 @@
       <c r="A36" s="79"/>
       <c r="B36" s="63"/>
       <c r="C36" s="90" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D36" s="63"/>
       <c r="E36" s="63"/>
@@ -10566,7 +11205,7 @@
       <c r="L36" s="63"/>
       <c r="M36" s="63"/>
       <c r="N36" s="90" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="O36" s="63"/>
       <c r="P36" s="63"/>
@@ -10677,7 +11316,7 @@
     </row>
     <row r="40" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="103" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B40" s="103"/>
       <c r="C40" s="103"/>
@@ -10704,7 +11343,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="104" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B41" s="104"/>
       <c r="C41" s="104"/>
@@ -10965,7 +11604,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="104" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B42" s="104"/>
       <c r="C42" s="104"/>
@@ -11255,7 +11894,7 @@
       </c>
       <c r="B44" s="63"/>
       <c r="C44" s="64" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D44" s="64"/>
       <c r="E44" s="64"/>
@@ -11270,7 +11909,7 @@
       </c>
       <c r="M44" s="63"/>
       <c r="N44" s="64" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="O44" s="63"/>
       <c r="P44" s="63"/>
@@ -11385,7 +12024,7 @@
       </c>
       <c r="B48" s="63"/>
       <c r="C48" s="64" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D48" s="64"/>
       <c r="E48" s="64"/>
@@ -11400,7 +12039,7 @@
       </c>
       <c r="M48" s="63"/>
       <c r="N48" s="64" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="O48" s="63"/>
       <c r="P48" s="63"/>
@@ -11416,7 +12055,7 @@
       <c r="A49" s="79"/>
       <c r="B49" s="63"/>
       <c r="C49" s="90" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D49" s="63"/>
       <c r="E49" s="63"/>
@@ -11542,7 +12181,7 @@
       </c>
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D53" s="64"/>
       <c r="E53" s="64"/>
@@ -11557,7 +12196,7 @@
       </c>
       <c r="M53" s="63"/>
       <c r="N53" s="64" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O53" s="63"/>
       <c r="P53" s="63"/>
@@ -11672,7 +12311,7 @@
       </c>
       <c r="B57" s="63"/>
       <c r="C57" s="64" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D57" s="64"/>
       <c r="E57" s="64"/>
@@ -11687,7 +12326,7 @@
       </c>
       <c r="M57" s="63"/>
       <c r="N57" s="64" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="O57" s="63"/>
       <c r="P57" s="63"/>
@@ -11714,7 +12353,7 @@
       <c r="L58" s="63"/>
       <c r="M58" s="63"/>
       <c r="N58" s="90" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="O58" s="63"/>
       <c r="P58" s="63"/>
@@ -11829,7 +12468,7 @@
       </c>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D62" s="64"/>
       <c r="E62" s="64"/>
@@ -11844,7 +12483,7 @@
       </c>
       <c r="M62" s="63"/>
       <c r="N62" s="64" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="O62" s="63"/>
       <c r="P62" s="63"/>
@@ -11955,7 +12594,7 @@
     </row>
     <row r="66" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="107" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B66" s="107"/>
       <c r="C66" s="107"/>
@@ -12011,7 +12650,7 @@
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D68" s="64"/>
       <c r="E68" s="64"/>
@@ -12026,7 +12665,7 @@
       </c>
       <c r="M68" s="63"/>
       <c r="N68" s="64" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="O68" s="63"/>
       <c r="P68" s="63"/>
@@ -12042,7 +12681,7 @@
       <c r="A69" s="79"/>
       <c r="B69" s="63"/>
       <c r="C69" s="90" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D69" s="64"/>
       <c r="E69" s="64"/>
@@ -12055,7 +12694,7 @@
       <c r="L69" s="63"/>
       <c r="M69" s="63"/>
       <c r="N69" s="90" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="O69" s="63"/>
       <c r="P69" s="63"/>
@@ -12168,7 +12807,7 @@
     </row>
     <row r="73" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="103" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B73" s="103"/>
       <c r="C73" s="103"/>
@@ -12197,7 +12836,7 @@
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="104" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B74" s="104"/>
       <c r="C74" s="104"/>
@@ -12224,7 +12863,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="104" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B75" s="104"/>
       <c r="C75" s="104"/>
@@ -12253,7 +12892,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="104" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B76" s="104"/>
       <c r="C76" s="104"/>
@@ -12309,7 +12948,7 @@
       </c>
       <c r="B78" s="63"/>
       <c r="C78" s="64" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D78" s="64"/>
       <c r="E78" s="64"/>
@@ -12324,7 +12963,7 @@
       </c>
       <c r="M78" s="63"/>
       <c r="N78" s="64" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="O78" s="63"/>
       <c r="P78" s="63"/>
@@ -12439,7 +13078,7 @@
       </c>
       <c r="B82" s="63"/>
       <c r="C82" s="64" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D82" s="63"/>
       <c r="E82" s="63"/>
@@ -12454,7 +13093,7 @@
       </c>
       <c r="M82" s="63"/>
       <c r="N82" s="64" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="O82" s="63"/>
       <c r="P82" s="63"/>
@@ -12470,7 +13109,7 @@
       <c r="A83" s="79"/>
       <c r="B83" s="63"/>
       <c r="C83" s="64" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D83" s="63"/>
       <c r="E83" s="63"/>
@@ -12483,7 +13122,7 @@
       <c r="L83" s="64"/>
       <c r="M83" s="63"/>
       <c r="N83" s="64" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="O83" s="110"/>
       <c r="P83" s="110"/>
@@ -12594,7 +13233,7 @@
     </row>
     <row r="87" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="111" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B87" s="111"/>
       <c r="C87" s="111"/>
@@ -12621,7 +13260,7 @@
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="104" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B88" s="104"/>
       <c r="C88" s="104"/>
@@ -12648,7 +13287,7 @@
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="104" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B89" s="104"/>
       <c r="C89" s="104"/>
@@ -12704,7 +13343,7 @@
       </c>
       <c r="B91" s="63"/>
       <c r="C91" s="64" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D91" s="64"/>
       <c r="E91" s="64"/>
@@ -12719,7 +13358,7 @@
       </c>
       <c r="M91" s="63"/>
       <c r="N91" s="64" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="O91" s="63"/>
       <c r="P91" s="63"/>
@@ -12735,7 +13374,7 @@
       <c r="A92" s="64"/>
       <c r="B92" s="63"/>
       <c r="C92" s="90" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D92" s="64"/>
       <c r="E92" s="64"/>
@@ -12748,7 +13387,7 @@
       <c r="L92" s="64"/>
       <c r="M92" s="63"/>
       <c r="N92" s="64" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="O92" s="110"/>
       <c r="P92" s="110"/>
@@ -12863,7 +13502,7 @@
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D96" s="64"/>
       <c r="E96" s="64"/>
@@ -12878,7 +13517,7 @@
       </c>
       <c r="M96" s="63"/>
       <c r="N96" s="64" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="O96" s="63"/>
       <c r="P96" s="63"/>
@@ -12894,7 +13533,7 @@
       <c r="A97" s="106"/>
       <c r="B97" s="63"/>
       <c r="C97" s="64" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D97" s="64"/>
       <c r="E97" s="64"/>
@@ -12907,7 +13546,7 @@
       <c r="L97" s="64"/>
       <c r="M97" s="63"/>
       <c r="N97" s="90" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="O97" s="63"/>
       <c r="P97" s="63"/>
@@ -13020,7 +13659,7 @@
     </row>
     <row r="101" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="103" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B101" s="103"/>
       <c r="C101" s="103"/>
@@ -13076,7 +13715,7 @@
       </c>
       <c r="B103" s="63"/>
       <c r="C103" s="64" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D103" s="64"/>
       <c r="E103" s="64"/>
@@ -13091,7 +13730,7 @@
       </c>
       <c r="M103" s="63"/>
       <c r="N103" s="64" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="O103" s="63"/>
       <c r="P103" s="63"/>
@@ -13107,7 +13746,7 @@
       <c r="A104" s="79"/>
       <c r="B104" s="63"/>
       <c r="C104" s="80" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D104" s="112"/>
       <c r="E104" s="112"/>
@@ -13120,7 +13759,7 @@
       <c r="L104" s="64"/>
       <c r="M104" s="63"/>
       <c r="N104" s="64" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="O104" s="63"/>
       <c r="P104" s="63"/>
@@ -13231,7 +13870,7 @@
     </row>
     <row r="108" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="111" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B108" s="111"/>
       <c r="C108" s="111"/>
@@ -13258,7 +13897,7 @@
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="104" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B109" s="104"/>
       <c r="C109" s="104"/>
@@ -13314,7 +13953,7 @@
       </c>
       <c r="B111" s="63"/>
       <c r="C111" s="64" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D111" s="64"/>
       <c r="E111" s="64"/>
@@ -13346,7 +13985,7 @@
       <c r="A112" s="106"/>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D112" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -13362,7 +14001,7 @@
       <c r="L112" s="64"/>
       <c r="M112" s="63"/>
       <c r="N112" s="64" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="O112" s="110"/>
       <c r="P112" s="110"/>
@@ -13463,7 +14102,7 @@
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -13478,7 +14117,7 @@
       </c>
       <c r="M116" s="63"/>
       <c r="N116" s="64" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="O116" s="63"/>
       <c r="P116" s="63"/>
@@ -13494,7 +14133,7 @@
       <c r="A117" s="106"/>
       <c r="B117" s="63"/>
       <c r="C117" s="64" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D117" s="64"/>
       <c r="E117" s="64"/>
@@ -13507,7 +14146,7 @@
       <c r="L117" s="64"/>
       <c r="M117" s="63"/>
       <c r="N117" s="64" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="O117" s="63"/>
       <c r="P117" s="63"/>
@@ -13608,7 +14247,7 @@
       </c>
       <c r="B121" s="63"/>
       <c r="C121" s="64" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D121" s="64"/>
       <c r="E121" s="64"/>
@@ -13623,7 +14262,7 @@
       </c>
       <c r="M121" s="63"/>
       <c r="N121" s="64" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="O121" s="63"/>
       <c r="P121" s="63"/>
@@ -13639,7 +14278,7 @@
       <c r="A122" s="106"/>
       <c r="B122" s="63"/>
       <c r="C122" s="90" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D122" s="64"/>
       <c r="E122" s="64"/>
@@ -13652,7 +14291,7 @@
       <c r="L122" s="64"/>
       <c r="M122" s="63"/>
       <c r="N122" s="64" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="O122" s="63"/>
       <c r="P122" s="63"/>
@@ -13875,7 +14514,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -13893,7 +14532,7 @@
       <c r="L1" s="52"/>
       <c r="M1" s="52"/>
       <c r="N1" s="121" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="O1" s="121"/>
       <c r="P1" s="121"/>
@@ -13920,7 +14559,7 @@
       <c r="L2" s="52"/>
       <c r="M2" s="52"/>
       <c r="N2" s="54" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O2" s="54"/>
       <c r="P2" s="54"/>
@@ -13932,7 +14571,7 @@
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
       <c r="U2" s="56" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="V2" s="55" t="n">
         <f aca="false">Admin!B17</f>
@@ -14254,7 +14893,7 @@
       </c>
       <c r="M14" s="63"/>
       <c r="N14" s="64" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="O14" s="64"/>
       <c r="P14" s="64"/>
@@ -14284,7 +14923,7 @@
       <c r="L15" s="63"/>
       <c r="M15" s="63"/>
       <c r="N15" s="80" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="O15" s="64"/>
       <c r="P15" s="64"/>
@@ -14311,7 +14950,7 @@
       <c r="L16" s="63"/>
       <c r="M16" s="63"/>
       <c r="N16" s="64" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="O16" s="64"/>
       <c r="P16" s="64"/>
@@ -15002,7 +15641,7 @@
       </c>
       <c r="B32" s="63"/>
       <c r="C32" s="80" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -15050,7 +15689,7 @@
       <c r="L33" s="63"/>
       <c r="M33" s="63"/>
       <c r="N33" s="64" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="O33" s="64"/>
       <c r="P33" s="64"/>
@@ -15077,7 +15716,7 @@
       <c r="L34" s="63"/>
       <c r="M34" s="63"/>
       <c r="N34" s="90" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="O34" s="90"/>
       <c r="P34" s="64"/>
@@ -15384,7 +16023,7 @@
       <c r="L45" s="63"/>
       <c r="M45" s="63"/>
       <c r="N45" s="64" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="O45" s="64"/>
       <c r="P45" s="64"/>
@@ -15501,7 +16140,7 @@
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="103" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B50" s="103"/>
       <c r="C50" s="103"/>
@@ -15557,7 +16196,7 @@
       </c>
       <c r="B52" s="63"/>
       <c r="C52" s="64" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D52" s="64"/>
       <c r="E52" s="64"/>
@@ -15572,7 +16211,7 @@
       </c>
       <c r="M52" s="63"/>
       <c r="N52" s="64" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="64"/>
@@ -15588,7 +16227,7 @@
       <c r="A53" s="79"/>
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D53" s="63"/>
       <c r="E53" s="63"/>
@@ -15710,7 +16349,7 @@
     </row>
     <row r="57" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="103" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B57" s="103"/>
       <c r="C57" s="103"/>
@@ -15737,7 +16376,7 @@
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="104" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B58" s="104"/>
       <c r="C58" s="104"/>
@@ -16025,7 +16664,7 @@
       <c r="A60" s="79"/>
       <c r="B60" s="63"/>
       <c r="C60" s="129" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D60" s="63"/>
       <c r="E60" s="63"/>
@@ -16038,7 +16677,7 @@
       <c r="L60" s="63"/>
       <c r="M60" s="63"/>
       <c r="N60" s="129" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="O60" s="63"/>
       <c r="P60" s="63"/>
@@ -16054,7 +16693,7 @@
       <c r="A61" s="79"/>
       <c r="B61" s="63"/>
       <c r="C61" s="64" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D61" s="64"/>
       <c r="E61" s="64"/>
@@ -16067,7 +16706,7 @@
       <c r="L61" s="64"/>
       <c r="M61" s="64"/>
       <c r="N61" s="64" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="O61" s="64"/>
       <c r="P61" s="64"/>
@@ -16083,7 +16722,7 @@
       <c r="A62" s="79"/>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D62" s="64"/>
       <c r="E62" s="64"/>
@@ -16096,7 +16735,7 @@
       <c r="L62" s="64"/>
       <c r="M62" s="64"/>
       <c r="N62" s="64" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="O62" s="64"/>
       <c r="P62" s="64"/>
@@ -16139,7 +16778,7 @@
       </c>
       <c r="B64" s="63"/>
       <c r="C64" s="64" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D64" s="64"/>
       <c r="E64" s="64"/>
@@ -16267,7 +16906,7 @@
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D68" s="64"/>
       <c r="E68" s="64"/>
@@ -16395,7 +17034,7 @@
       </c>
       <c r="B72" s="63"/>
       <c r="C72" s="64" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D72" s="64"/>
       <c r="E72" s="64"/>
@@ -16523,7 +17162,7 @@
       </c>
       <c r="B76" s="63"/>
       <c r="C76" s="64" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D76" s="64"/>
       <c r="E76" s="64"/>
@@ -16651,7 +17290,7 @@
       </c>
       <c r="B80" s="63"/>
       <c r="C80" s="64" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D80" s="64"/>
       <c r="E80" s="64"/>
@@ -16779,7 +17418,7 @@
       </c>
       <c r="B84" s="63"/>
       <c r="C84" s="64" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D84" s="64"/>
       <c r="E84" s="64"/>
@@ -16907,7 +17546,7 @@
       </c>
       <c r="B88" s="63"/>
       <c r="C88" s="64" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D88" s="64"/>
       <c r="E88" s="64"/>
@@ -17035,7 +17674,7 @@
       </c>
       <c r="B92" s="63"/>
       <c r="C92" s="64" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D92" s="64"/>
       <c r="E92" s="64"/>
@@ -17163,7 +17802,7 @@
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D96" s="64"/>
       <c r="E96" s="64"/>
@@ -17291,7 +17930,7 @@
       </c>
       <c r="B100" s="63"/>
       <c r="C100" s="64" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D100" s="64"/>
       <c r="E100" s="64"/>
@@ -17419,7 +18058,7 @@
       </c>
       <c r="B104" s="63"/>
       <c r="C104" s="64" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D104" s="64"/>
       <c r="E104" s="64"/>
@@ -17547,7 +18186,7 @@
       </c>
       <c r="B108" s="63"/>
       <c r="C108" s="64" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D108" s="64"/>
       <c r="E108" s="64"/>
@@ -17675,7 +18314,7 @@
       </c>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D112" s="64"/>
       <c r="E112" s="64"/>
@@ -17803,7 +18442,7 @@
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -17931,7 +18570,7 @@
       </c>
       <c r="B120" s="63"/>
       <c r="C120" s="64" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D120" s="64"/>
       <c r="E120" s="64"/>
@@ -17946,7 +18585,7 @@
       </c>
       <c r="M120" s="63"/>
       <c r="N120" s="64" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="O120" s="63"/>
       <c r="P120" s="63"/>
@@ -18057,7 +18696,7 @@
     </row>
     <row r="124" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="107" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B124" s="107"/>
       <c r="C124" s="107"/>
@@ -18113,7 +18752,7 @@
       </c>
       <c r="B126" s="63"/>
       <c r="C126" s="64" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D126" s="64"/>
       <c r="E126" s="64"/>
@@ -18128,7 +18767,7 @@
       </c>
       <c r="M126" s="63"/>
       <c r="N126" s="64" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="O126" s="63"/>
       <c r="P126" s="63"/>
@@ -18144,7 +18783,7 @@
       <c r="A127" s="79"/>
       <c r="B127" s="63"/>
       <c r="C127" s="90" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D127" s="64"/>
       <c r="E127" s="64"/>
@@ -18157,7 +18796,7 @@
       <c r="L127" s="63"/>
       <c r="M127" s="63"/>
       <c r="N127" s="64" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="O127" s="63"/>
       <c r="P127" s="63"/>
@@ -18268,7 +18907,7 @@
     </row>
     <row r="131" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="103" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B131" s="103"/>
       <c r="C131" s="103"/>
@@ -18295,7 +18934,7 @@
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="104" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B132" s="104"/>
       <c r="C132" s="104"/>
@@ -18322,7 +18961,7 @@
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="104" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B133" s="104"/>
       <c r="C133" s="104"/>
@@ -18349,7 +18988,7 @@
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="104" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B134" s="104"/>
       <c r="C134" s="104"/>
@@ -18405,7 +19044,7 @@
       </c>
       <c r="B136" s="63"/>
       <c r="C136" s="130" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D136" s="64"/>
       <c r="E136" s="64"/>
@@ -18420,7 +19059,7 @@
       </c>
       <c r="M136" s="63"/>
       <c r="N136" s="64" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="O136" s="63"/>
       <c r="P136" s="63"/>
@@ -18557,7 +19196,7 @@
       </c>
       <c r="B141" s="63"/>
       <c r="C141" s="64" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D141" s="64"/>
       <c r="E141" s="64"/>
@@ -18568,7 +19207,7 @@
       </c>
       <c r="H141" s="131"/>
       <c r="I141" s="64" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J141" s="64"/>
       <c r="K141" s="64"/>
@@ -18577,7 +19216,7 @@
       </c>
       <c r="M141" s="63"/>
       <c r="N141" s="64" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="O141" s="63"/>
       <c r="P141" s="63"/>
@@ -18593,7 +19232,7 @@
       <c r="A142" s="106"/>
       <c r="B142" s="63"/>
       <c r="C142" s="64" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D142" s="64"/>
       <c r="E142" s="64"/>
@@ -18719,7 +19358,7 @@
       </c>
       <c r="B146" s="63"/>
       <c r="C146" s="130" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D146" s="64"/>
       <c r="E146" s="64"/>
@@ -18770,7 +19409,7 @@
       </c>
       <c r="M147" s="63"/>
       <c r="N147" s="64" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="O147" s="63"/>
       <c r="P147" s="63"/>
@@ -18797,7 +19436,7 @@
       <c r="L148" s="64"/>
       <c r="M148" s="63"/>
       <c r="N148" s="64" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="O148" s="63"/>
       <c r="P148" s="63"/>
@@ -18815,7 +19454,7 @@
       </c>
       <c r="B149" s="63"/>
       <c r="C149" s="64" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D149" s="64"/>
       <c r="E149" s="64"/>
@@ -18888,7 +19527,7 @@
       </c>
       <c r="B151" s="63"/>
       <c r="C151" s="64" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D151" s="64"/>
       <c r="E151" s="64"/>
@@ -18903,7 +19542,7 @@
       </c>
       <c r="M151" s="63"/>
       <c r="N151" s="64" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="O151" s="63"/>
       <c r="P151" s="63"/>
@@ -18981,7 +19620,7 @@
       </c>
       <c r="B154" s="63"/>
       <c r="C154" s="64" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D154" s="64"/>
       <c r="E154" s="64"/>
@@ -19068,7 +19707,7 @@
       </c>
       <c r="M156" s="63"/>
       <c r="N156" s="64" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="O156" s="63"/>
       <c r="P156" s="63"/>
@@ -19086,7 +19725,7 @@
       </c>
       <c r="B157" s="63"/>
       <c r="C157" s="64" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D157" s="64"/>
       <c r="E157" s="64"/>
@@ -19099,7 +19738,7 @@
       <c r="L157" s="63"/>
       <c r="M157" s="63"/>
       <c r="N157" s="64" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="O157" s="63"/>
       <c r="P157" s="63"/>
@@ -19126,7 +19765,7 @@
       <c r="L158" s="63"/>
       <c r="M158" s="63"/>
       <c r="N158" s="64" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="O158" s="63"/>
       <c r="P158" s="63"/>
@@ -19237,7 +19876,7 @@
     </row>
     <row r="162" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="103" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B162" s="103"/>
       <c r="C162" s="103"/>
@@ -19264,7 +19903,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="104" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B163" s="104"/>
       <c r="C163" s="104"/>
@@ -19291,7 +19930,7 @@
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="104" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B164" s="104"/>
       <c r="C164" s="104"/>
@@ -19347,7 +19986,7 @@
       </c>
       <c r="B166" s="63"/>
       <c r="C166" s="64" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D166" s="64"/>
       <c r="E166" s="64"/>
@@ -19362,7 +20001,7 @@
       </c>
       <c r="M166" s="63"/>
       <c r="N166" s="64" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="O166" s="63"/>
       <c r="P166" s="63"/>
@@ -19389,7 +20028,7 @@
       <c r="L167" s="64"/>
       <c r="M167" s="63"/>
       <c r="N167" s="64" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="O167" s="110"/>
       <c r="P167" s="110"/>
@@ -19504,7 +20143,7 @@
       </c>
       <c r="B171" s="63"/>
       <c r="C171" s="64" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D171" s="64"/>
       <c r="E171" s="64"/>
@@ -19519,7 +20158,7 @@
       </c>
       <c r="M171" s="63"/>
       <c r="N171" s="64" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="O171" s="63"/>
       <c r="P171" s="63"/>
@@ -19535,7 +20174,7 @@
       <c r="A172" s="106"/>
       <c r="B172" s="63"/>
       <c r="C172" s="64" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D172" s="64"/>
       <c r="E172" s="64"/>
@@ -19548,7 +20187,7 @@
       <c r="L172" s="64"/>
       <c r="M172" s="63"/>
       <c r="N172" s="64" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="O172" s="63"/>
       <c r="P172" s="63"/>
@@ -19663,7 +20302,7 @@
       </c>
       <c r="B176" s="63"/>
       <c r="C176" s="64" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D176" s="64"/>
       <c r="E176" s="64"/>
@@ -19678,7 +20317,7 @@
       </c>
       <c r="M176" s="63"/>
       <c r="N176" s="64" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="O176" s="63"/>
       <c r="P176" s="63"/>
@@ -19694,7 +20333,7 @@
       <c r="A177" s="79"/>
       <c r="B177" s="63"/>
       <c r="C177" s="64" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D177" s="63"/>
       <c r="E177" s="63"/>
@@ -19707,7 +20346,7 @@
       <c r="L177" s="63"/>
       <c r="M177" s="63"/>
       <c r="N177" s="64" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="O177" s="63"/>
       <c r="P177" s="63"/>
@@ -19817,7 +20456,7 @@
     </row>
     <row r="181" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="103" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B181" s="103"/>
       <c r="C181" s="103"/>
@@ -19844,7 +20483,7 @@
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="104" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B182" s="104"/>
       <c r="C182" s="104"/>
@@ -19871,7 +20510,7 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="104" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B183" s="104"/>
       <c r="C183" s="104"/>
@@ -19898,7 +20537,7 @@
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="133" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B184" s="133"/>
       <c r="C184" s="133"/>
@@ -19952,7 +20591,7 @@
       <c r="A186" s="75"/>
       <c r="B186" s="63"/>
       <c r="C186" s="64" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D186" s="64"/>
       <c r="E186" s="64"/>
@@ -19967,7 +20606,7 @@
       </c>
       <c r="M186" s="63"/>
       <c r="N186" s="64" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="O186" s="63"/>
       <c r="P186" s="63"/>
@@ -19994,7 +20633,7 @@
       <c r="L187" s="64"/>
       <c r="M187" s="63"/>
       <c r="N187" s="80" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="O187" s="63"/>
       <c r="P187" s="63"/>
@@ -20021,7 +20660,7 @@
       <c r="L188" s="64"/>
       <c r="M188" s="63"/>
       <c r="N188" s="92" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="O188" s="63"/>
       <c r="P188" s="63"/>
@@ -20048,7 +20687,7 @@
       <c r="L189" s="64"/>
       <c r="M189" s="63"/>
       <c r="N189" s="92" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="O189" s="110"/>
       <c r="P189" s="110"/>
@@ -20078,7 +20717,7 @@
         <v>33</v>
       </c>
       <c r="O190" s="136" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="P190" s="137"/>
       <c r="Q190" s="137"/>
@@ -20126,7 +20765,7 @@
       </c>
       <c r="B192" s="63"/>
       <c r="C192" s="64" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D192" s="112"/>
       <c r="E192" s="112"/>
@@ -20141,7 +20780,7 @@
       </c>
       <c r="M192" s="63"/>
       <c r="N192" s="64" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O192" s="63"/>
       <c r="P192" s="63"/>
@@ -20160,7 +20799,7 @@
       <c r="A193" s="79"/>
       <c r="B193" s="63"/>
       <c r="C193" s="64" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D193" s="64"/>
       <c r="E193" s="64"/>
@@ -20173,7 +20812,7 @@
       <c r="L193" s="64"/>
       <c r="M193" s="64"/>
       <c r="N193" s="80" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="O193" s="112"/>
       <c r="P193" s="112"/>
@@ -20189,7 +20828,7 @@
       <c r="A194" s="79"/>
       <c r="B194" s="63"/>
       <c r="C194" s="80" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D194" s="64"/>
       <c r="E194" s="64"/>
@@ -20265,7 +20904,7 @@
       </c>
       <c r="M196" s="63"/>
       <c r="N196" s="64" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="O196" s="63"/>
       <c r="P196" s="63"/>
@@ -20283,11 +20922,12 @@
       <c r="C197" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D197" s="136" t="s">
-        <v>197</v>
-      </c>
-      <c r="E197" s="137"/>
-      <c r="F197" s="137"/>
+      <c r="D197" s="98" t="n">
+        <f aca="false">IF(OR('Business Details'!N32="",'Business Details'!N32&gt;=DATE(YEAR(Admin!$B$17),3,31)),0,('Business Details'!N32-MAX('Business Details'!N27,Admin!$B$4)+1)/('Business Details'!N32-'Business Details'!N27+1)*(O174-O179)+(Admin!$B$17-'Business Details'!N32)/(EDATE('Business Details'!N32,12)-'Business Details'!N32)*'Business Details'!D74-(O174-O179))</f>
+        <v>0</v>
+      </c>
+      <c r="E197" s="98"/>
+      <c r="F197" s="98"/>
       <c r="G197" s="99" t="s">
         <v>34</v>
       </c>
@@ -20302,7 +20942,7 @@
       <c r="L197" s="63"/>
       <c r="M197" s="63"/>
       <c r="N197" s="80" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="O197" s="63"/>
       <c r="P197" s="63"/>
@@ -20340,10 +20980,12 @@
       <c r="W198" s="82"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="75"/>
+      <c r="A199" s="75" t="n">
+        <v>73.3</v>
+      </c>
       <c r="B199" s="63"/>
       <c r="C199" s="64" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D199" s="63"/>
       <c r="E199" s="63"/>
@@ -20380,7 +21022,9 @@
     <row r="200" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="106"/>
       <c r="B200" s="63"/>
-      <c r="C200" s="64"/>
+      <c r="C200" s="64" t="s">
+        <v>218</v>
+      </c>
       <c r="D200" s="64"/>
       <c r="E200" s="64"/>
       <c r="F200" s="64"/>
@@ -20405,13 +21049,24 @@
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="79"/>
       <c r="B201" s="63"/>
-      <c r="C201" s="64"/>
-      <c r="D201" s="134"/>
-      <c r="E201" s="134"/>
-      <c r="F201" s="134"/>
-      <c r="G201" s="99"/>
-      <c r="H201" s="64"/>
-      <c r="I201" s="64"/>
+      <c r="C201" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D201" s="98" t="n">
+        <f aca="false">'Business Details'!O64+'Business Details'!O69</f>
+        <v>4000</v>
+      </c>
+      <c r="E201" s="98"/>
+      <c r="F201" s="98"/>
+      <c r="G201" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H201" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" s="100" t="n">
+        <v>0</v>
+      </c>
       <c r="J201" s="63"/>
       <c r="K201" s="63"/>
       <c r="L201" s="75" t="n">
@@ -20419,7 +21074,7 @@
       </c>
       <c r="M201" s="63"/>
       <c r="N201" s="64" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="O201" s="63"/>
       <c r="P201" s="63"/>
@@ -20446,7 +21101,7 @@
       <c r="L202" s="63"/>
       <c r="M202" s="63"/>
       <c r="N202" s="64" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="O202" s="63"/>
       <c r="P202" s="63"/>
@@ -20486,7 +21141,9 @@
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="79"/>
       <c r="B204" s="63"/>
-      <c r="C204" s="80"/>
+      <c r="C204" s="64" t="s">
+        <v>221</v>
+      </c>
       <c r="D204" s="63"/>
       <c r="E204" s="63"/>
       <c r="F204" s="63"/>
@@ -20561,7 +21218,7 @@
       </c>
       <c r="M206" s="63"/>
       <c r="N206" s="64" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="O206" s="63"/>
       <c r="P206" s="63"/>
@@ -20588,7 +21245,7 @@
       <c r="L207" s="63"/>
       <c r="M207" s="63"/>
       <c r="N207" s="64" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="O207" s="63"/>
       <c r="P207" s="63"/>
@@ -20606,7 +21263,7 @@
       </c>
       <c r="B208" s="63"/>
       <c r="C208" s="64" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D208" s="64"/>
       <c r="E208" s="64"/>
@@ -20727,7 +21384,7 @@
     </row>
     <row r="212" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="111" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B212" s="111"/>
       <c r="C212" s="111"/>
@@ -20754,7 +21411,7 @@
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="104" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B213" s="104"/>
       <c r="C213" s="104"/>
@@ -20781,7 +21438,7 @@
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="104" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B214" s="104"/>
       <c r="C214" s="104"/>
@@ -20837,7 +21494,7 @@
       </c>
       <c r="B216" s="63"/>
       <c r="C216" s="64" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D216" s="64"/>
       <c r="E216" s="64"/>
@@ -20846,7 +21503,7 @@
         <v>2026-27</v>
       </c>
       <c r="G216" s="64" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H216" s="64"/>
       <c r="I216" s="64"/>
@@ -20857,7 +21514,7 @@
       </c>
       <c r="M216" s="63"/>
       <c r="N216" s="64" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="O216" s="63"/>
       <c r="P216" s="63"/>
@@ -20884,7 +21541,7 @@
       <c r="L217" s="64"/>
       <c r="M217" s="63"/>
       <c r="N217" s="64" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="O217" s="63"/>
       <c r="P217" s="63"/>
@@ -20996,7 +21653,7 @@
       </c>
       <c r="B221" s="63"/>
       <c r="C221" s="64" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D221" s="64"/>
       <c r="E221" s="64"/>
@@ -21011,7 +21668,7 @@
       </c>
       <c r="M221" s="63"/>
       <c r="N221" s="64" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="O221" s="63"/>
       <c r="P221" s="63"/>
@@ -21027,7 +21684,7 @@
       <c r="A222" s="79"/>
       <c r="B222" s="63"/>
       <c r="C222" s="64" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D222" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -21043,7 +21700,7 @@
       <c r="L222" s="63"/>
       <c r="M222" s="63"/>
       <c r="N222" s="90" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="O222" s="63"/>
       <c r="P222" s="63"/>
@@ -21151,7 +21808,7 @@
     </row>
     <row r="226" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="147" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B226" s="147"/>
       <c r="C226" s="147"/>
@@ -21207,7 +21864,7 @@
       </c>
       <c r="B228" s="63"/>
       <c r="C228" s="64" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D228" s="64"/>
       <c r="E228" s="64"/>
@@ -21222,7 +21879,7 @@
       </c>
       <c r="M228" s="63"/>
       <c r="N228" s="64" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="O228" s="63"/>
       <c r="P228" s="63"/>
@@ -21238,7 +21895,7 @@
       <c r="A229" s="106"/>
       <c r="B229" s="63"/>
       <c r="C229" s="64" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="D229" s="64"/>
       <c r="E229" s="64"/>
@@ -21357,7 +22014,7 @@
     </row>
     <row r="233" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="103" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B233" s="103"/>
       <c r="C233" s="103"/>
@@ -21384,7 +22041,7 @@
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="104" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B234" s="104"/>
       <c r="C234" s="104"/>
@@ -21411,7 +22068,7 @@
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="104" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B235" s="104"/>
       <c r="C235" s="104"/>
@@ -21465,7 +22122,7 @@
       <c r="A237" s="79"/>
       <c r="B237" s="63"/>
       <c r="C237" s="129" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D237" s="63"/>
       <c r="E237" s="63"/>
@@ -21478,7 +22135,7 @@
       <c r="L237" s="63"/>
       <c r="M237" s="63"/>
       <c r="N237" s="129" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="O237" s="63"/>
       <c r="P237" s="63"/>
@@ -21521,7 +22178,7 @@
       </c>
       <c r="B239" s="63"/>
       <c r="C239" s="64" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D239" s="64"/>
       <c r="E239" s="64"/>
@@ -21536,7 +22193,7 @@
       </c>
       <c r="M239" s="63"/>
       <c r="N239" s="64" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="O239" s="63"/>
       <c r="P239" s="63"/>
@@ -21645,7 +22302,7 @@
       </c>
       <c r="B243" s="63"/>
       <c r="C243" s="64" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D243" s="64"/>
       <c r="E243" s="64"/>
@@ -21660,7 +22317,7 @@
       </c>
       <c r="M243" s="63"/>
       <c r="N243" s="64" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="O243" s="63"/>
       <c r="P243" s="63"/>
@@ -21769,7 +22426,7 @@
       </c>
       <c r="B247" s="63"/>
       <c r="C247" s="64" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D247" s="64"/>
       <c r="E247" s="64"/>
@@ -21784,7 +22441,7 @@
       </c>
       <c r="M247" s="63"/>
       <c r="N247" s="64" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="O247" s="63"/>
       <c r="P247" s="63"/>
@@ -21893,7 +22550,7 @@
       </c>
       <c r="B251" s="63"/>
       <c r="C251" s="64" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D251" s="64"/>
       <c r="E251" s="64"/>
@@ -21906,7 +22563,7 @@
       <c r="L251" s="63"/>
       <c r="M251" s="63"/>
       <c r="N251" s="129" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="O251" s="112"/>
       <c r="P251" s="112"/>
@@ -21968,7 +22625,7 @@
       </c>
       <c r="M253" s="63"/>
       <c r="N253" s="64" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="O253" s="63"/>
       <c r="P253" s="63"/>
@@ -22011,7 +22668,7 @@
       </c>
       <c r="B255" s="63"/>
       <c r="C255" s="64" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D255" s="64"/>
       <c r="E255" s="64"/>
@@ -22027,7 +22684,7 @@
         <v>33</v>
       </c>
       <c r="O255" s="149" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="P255" s="98"/>
       <c r="Q255" s="98"/>
@@ -22092,7 +22749,7 @@
       <c r="L257" s="63"/>
       <c r="M257" s="63"/>
       <c r="N257" s="129" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="O257" s="63"/>
       <c r="P257" s="63"/>
@@ -22135,7 +22792,7 @@
       </c>
       <c r="B259" s="63"/>
       <c r="C259" s="64" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D259" s="64"/>
       <c r="E259" s="64"/>
@@ -22150,7 +22807,7 @@
       </c>
       <c r="M259" s="63"/>
       <c r="N259" s="64" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="O259" s="63"/>
       <c r="P259" s="63"/>
@@ -22213,7 +22870,7 @@
         <v>33</v>
       </c>
       <c r="O261" s="136" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="P261" s="98"/>
       <c r="Q261" s="98"/>
@@ -22261,7 +22918,7 @@
       </c>
       <c r="B263" s="63"/>
       <c r="C263" s="64" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D263" s="64"/>
       <c r="E263" s="64"/>
@@ -22276,7 +22933,7 @@
       </c>
       <c r="M263" s="63"/>
       <c r="N263" s="64" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="O263" s="63"/>
       <c r="P263" s="63"/>
@@ -22339,7 +22996,7 @@
         <v>33</v>
       </c>
       <c r="O265" s="136" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="P265" s="98"/>
       <c r="Q265" s="98"/>
@@ -22387,7 +23044,7 @@
       </c>
       <c r="B267" s="63"/>
       <c r="C267" s="64" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D267" s="64"/>
       <c r="E267" s="64"/>
@@ -22402,7 +23059,7 @@
       </c>
       <c r="M267" s="63"/>
       <c r="N267" s="64" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="O267" s="63"/>
       <c r="P267" s="63"/>
@@ -22522,7 +23179,7 @@
       </c>
       <c r="M271" s="63"/>
       <c r="N271" s="64" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="O271" s="63"/>
       <c r="P271" s="63"/>
@@ -22634,7 +23291,7 @@
       </c>
       <c r="M275" s="63"/>
       <c r="N275" s="64" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="O275" s="63"/>
       <c r="P275" s="63"/>
@@ -22689,7 +23346,7 @@
         <v>33</v>
       </c>
       <c r="O277" s="136" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="P277" s="98"/>
       <c r="Q277" s="98"/>
@@ -22733,7 +23390,7 @@
     </row>
     <row r="279" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="111" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B279" s="111"/>
       <c r="C279" s="111"/>
@@ -22760,7 +23417,7 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="104" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B280" s="104"/>
       <c r="C280" s="104"/>
@@ -22775,7 +23432,7 @@
         <v>12570</v>
       </c>
       <c r="K280" s="104" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="L280" s="104"/>
       <c r="M280" s="104"/>
@@ -22792,7 +23449,7 @@
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="151" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="151"/>
@@ -22848,7 +23505,7 @@
       </c>
       <c r="B283" s="63"/>
       <c r="C283" s="64" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D283" s="63"/>
       <c r="E283" s="63"/>
@@ -22863,7 +23520,7 @@
       </c>
       <c r="M283" s="63"/>
       <c r="N283" s="64" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="O283" s="63"/>
       <c r="P283" s="63"/>
@@ -22879,7 +23536,7 @@
       <c r="A284" s="79"/>
       <c r="B284" s="63"/>
       <c r="C284" s="64" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D284" s="63"/>
       <c r="E284" s="63"/>
@@ -22892,7 +23549,7 @@
       <c r="L284" s="63"/>
       <c r="M284" s="63"/>
       <c r="N284" s="90" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="O284" s="63"/>
       <c r="P284" s="63"/>
@@ -22993,7 +23650,7 @@
       </c>
       <c r="B288" s="63"/>
       <c r="C288" s="64" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="D288" s="63"/>
       <c r="E288" s="63"/>
@@ -23020,7 +23677,7 @@
       <c r="A289" s="79"/>
       <c r="B289" s="63"/>
       <c r="C289" s="64" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D289" s="63"/>
       <c r="E289" s="63"/>
@@ -23145,7 +23802,7 @@
     </row>
     <row r="294" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="103" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B294" s="103"/>
       <c r="C294" s="103"/>
@@ -23201,7 +23858,7 @@
       </c>
       <c r="B296" s="63"/>
       <c r="C296" s="64" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D296" s="63"/>
       <c r="E296" s="63"/>
@@ -24030,7 +24687,7 @@
     <mergeCell ref="C190:F190"/>
     <mergeCell ref="P190:Q190"/>
     <mergeCell ref="O194:Q194"/>
-    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="D197:F197"/>
     <mergeCell ref="O199:Q199"/>
     <mergeCell ref="D201:F201"/>
     <mergeCell ref="O204:Q204"/>
@@ -24128,10 +24785,10 @@
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="160" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B2" s="161" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C2" s="162" t="n">
         <f aca="false">Admin!B5</f>
@@ -24248,7 +24905,7 @@
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="169" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B5" s="170" t="n">
         <f aca="false">SUM(C5:N5)</f>
@@ -24306,7 +24963,7 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="169" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B6" s="170" t="n">
         <f aca="false">SUM(C6:N6)</f>
@@ -24364,7 +25021,7 @@
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="169" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B7" s="170" t="n">
         <f aca="false">SUM(C7:N7)</f>
@@ -24422,7 +25079,7 @@
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="169" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B8" s="170" t="n">
         <f aca="false">SUM(C8:N8)</f>
@@ -24480,7 +25137,7 @@
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="173" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B9" s="170" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -25039,7 +25696,7 @@
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="169" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B11" s="170" t="n">
         <f aca="false">SUM(C11:N11)</f>
@@ -25356,7 +26013,7 @@
     </row>
     <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="180" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B13" s="177"/>
       <c r="C13" s="177"/>
@@ -25617,7 +26274,7 @@
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="169" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B14" s="170" t="n">
         <f aca="false">SUM(C14:N14)</f>
@@ -25675,7 +26332,7 @@
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="169" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B15" s="170" t="n">
         <f aca="false">SUM(C15:N15)</f>
@@ -25733,7 +26390,7 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="169" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B16" s="170" t="n">
         <f aca="false">SUM(C16:N16)</f>
@@ -25791,7 +26448,7 @@
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="173" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B17" s="170" t="n">
         <f aca="false">SUM(B14:B16)</f>
@@ -26350,7 +27007,7 @@
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="173" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B19" s="170" t="n">
         <f aca="false">B9+B11-B17</f>
@@ -26650,7 +27307,7 @@
     </row>
     <row r="20" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="180" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B20" s="177"/>
       <c r="C20" s="181"/>
@@ -26911,7 +27568,7 @@
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="169" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B21" s="170" t="n">
         <f aca="false">SUM(C21:N21)</f>
@@ -26969,7 +27626,7 @@
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="182" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B22" s="170" t="n">
         <f aca="false">SUM(C22:N22)</f>
@@ -27027,7 +27684,7 @@
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="182" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B23" s="170" t="n">
         <f aca="false">SUM(C23:N23)</f>
@@ -27085,7 +27742,7 @@
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="182" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B24" s="170" t="n">
         <f aca="false">SUM(C24:N24)</f>
@@ -27143,7 +27800,7 @@
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="182" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B25" s="170" t="n">
         <f aca="false">SUM(C25:N25)</f>
@@ -27201,7 +27858,7 @@
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="182" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B26" s="170" t="n">
         <f aca="false">SUM(C26:N26)</f>
@@ -27259,7 +27916,7 @@
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="182" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B27" s="170" t="n">
         <f aca="false">SUM(C27:N27)</f>
@@ -27317,7 +27974,7 @@
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="182" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B28" s="170" t="n">
         <f aca="false">SUM(C28:N28)</f>
@@ -27375,7 +28032,7 @@
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="182" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B29" s="170" t="n">
         <f aca="false">SUM(C29:N29)</f>
@@ -27433,7 +28090,7 @@
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="182" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B30" s="170" t="n">
         <f aca="false">SUM(C30:N30)</f>
@@ -27491,7 +28148,7 @@
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="182" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B31" s="170" t="n">
         <f aca="false">SUM(C31:N31)</f>
@@ -27549,7 +28206,7 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="182" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B32" s="170" t="n">
         <f aca="false">SUM(C32:N32)</f>
@@ -27607,7 +28264,7 @@
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="169" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B33" s="170" t="n">
         <f aca="false">SUM(C33:N33)</f>
@@ -27665,7 +28322,7 @@
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="169" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B34" s="170" t="n">
         <f aca="false">SUM(C34:N34)</f>
@@ -27723,7 +28380,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="173" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
@@ -27798,7 +28455,7 @@
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="173" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
@@ -27856,7 +28513,7 @@
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="169" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B38" s="170" t="n">
         <f aca="false">SUM(C38:N38)</f>
@@ -27914,7 +28571,7 @@
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="173" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
@@ -27989,7 +28646,7 @@
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="187" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B41" s="156"/>
       <c r="C41" s="157"/>
@@ -28008,7 +28665,7 @@
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="182" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B42" s="177" t="n">
         <f aca="false">SUM(C42:N42)</f>
@@ -28066,7 +28723,7 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="182" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B43" s="177" t="n">
         <f aca="false">SUM(C43:N43)</f>
@@ -28124,7 +28781,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="182" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
@@ -28182,7 +28839,7 @@
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="188" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
@@ -28240,7 +28897,7 @@
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="182" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B46" s="177" t="n">
         <f aca="false">SUM(C46:N46)</f>
@@ -28315,7 +28972,7 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="182" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B49" s="170" t="n">
         <f aca="false">SUM(C49:N49)</f>
@@ -28430,25 +29087,25 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="195"/>
       <c r="B2" s="197" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C2" s="197" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D2" s="197" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="F2" s="197" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="G2" s="197" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="H2" s="197" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="I2" s="195"/>
       <c r="J2" s="196"/>
@@ -28973,7 +29630,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="195"/>
       <c r="B5" s="195" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C5" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -29001,7 +29658,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="195"/>
       <c r="B6" s="195" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C6" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -29029,7 +29686,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="195"/>
       <c r="B7" s="195" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C7" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -29327,7 +29984,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="195"/>
       <c r="B10" s="202" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C10" s="195"/>
       <c r="D10" s="195"/>
@@ -29351,7 +30008,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="195"/>
       <c r="B12" s="195" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C12" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -29379,7 +30036,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="195"/>
       <c r="B13" s="195" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C13" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -29407,7 +30064,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="195"/>
       <c r="B14" s="195" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="C14" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -29435,7 +30092,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="195"/>
       <c r="B15" s="195" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C15" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -29463,7 +30120,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="195"/>
       <c r="B16" s="195" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -29491,7 +30148,7 @@
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="195"/>
       <c r="B17" s="195" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="C17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -29519,7 +30176,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="195"/>
       <c r="B18" s="195" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C18" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -29547,7 +30204,7 @@
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="195"/>
       <c r="B19" s="195" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C19" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -29575,7 +30232,7 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="195"/>
       <c r="B20" s="195" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C20" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -29603,7 +30260,7 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="195"/>
       <c r="B21" s="195" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C21" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -29631,7 +30288,7 @@
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="195"/>
       <c r="B22" s="195" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C22" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -29670,7 +30327,7 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="195"/>
       <c r="B24" s="195" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C24" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -29698,7 +30355,7 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="195"/>
       <c r="B25" s="195" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C25" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C49:E49)</f>
@@ -29726,7 +30383,7 @@
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="195"/>
       <c r="B26" s="195" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
@@ -29776,7 +30433,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="195"/>
       <c r="B29" s="202" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
@@ -29848,7 +30505,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="195"/>
       <c r="B34" s="202" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C34" s="195"/>
       <c r="D34" s="195"/>
@@ -29872,7 +30529,7 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="195"/>
       <c r="B36" s="195" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C36" s="200" t="n">
         <f aca="false">C7*$I$36</f>
@@ -29895,7 +30552,7 @@
         <v>269.4</v>
       </c>
       <c r="H36" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I36" s="195" t="n">
         <v>0.02</v>
@@ -29904,7 +30561,7 @@
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="195"/>
       <c r="B37" s="195" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C37" s="200" t="n">
         <f aca="false">C24*$I$37</f>
@@ -29927,7 +30584,7 @@
         <v>200</v>
       </c>
       <c r="H37" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I37" s="195" t="n">
         <v>0.03</v>
@@ -29936,7 +30593,7 @@
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="195"/>
       <c r="B38" s="195" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C38" s="200" t="n">
         <f aca="false">C12*$I$38</f>
@@ -29959,7 +30616,7 @@
         <v>3709.42933333333</v>
       </c>
       <c r="H38" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I38" s="195" t="n">
         <v>0.04</v>
@@ -29968,7 +30625,7 @@
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="195"/>
       <c r="B39" s="195" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C39" s="200" t="n">
         <f aca="false">C17*$I$39</f>
@@ -29991,7 +30648,7 @@
         <v>1996.0625</v>
       </c>
       <c r="H39" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I39" s="195" t="n">
         <v>0.25</v>
@@ -30000,7 +30657,7 @@
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="195"/>
       <c r="B40" s="195" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C40" s="200" t="n">
         <f aca="false">C13*$I$40</f>
@@ -30023,7 +30680,7 @@
         <v>660</v>
       </c>
       <c r="H40" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I40" s="195" t="n">
         <v>0.05</v>
@@ -30032,7 +30689,7 @@
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="195"/>
       <c r="B41" s="195" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="C41" s="200" t="n">
         <f aca="false">C14*$I$41</f>
@@ -30055,7 +30712,7 @@
         <v>57</v>
       </c>
       <c r="H41" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I41" s="195" t="n">
         <v>0.06</v>
@@ -30064,7 +30721,7 @@
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="195"/>
       <c r="B42" s="195" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C42" s="200" t="n">
         <f aca="false">C15*$I$42</f>
@@ -30087,7 +30744,7 @@
         <v>212.45</v>
       </c>
       <c r="H42" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I42" s="195" t="n">
         <v>0.07</v>
@@ -30096,7 +30753,7 @@
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="195"/>
       <c r="B43" s="195" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C43" s="200" t="n">
         <f aca="false">C18*$I$43</f>
@@ -30119,7 +30776,7 @@
         <v>327.333333333333</v>
       </c>
       <c r="H43" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I43" s="195" t="n">
         <v>0.08</v>
@@ -30128,7 +30785,7 @@
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="195"/>
       <c r="B44" s="195" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C44" s="200" t="n">
         <f aca="false">C25</f>
@@ -30151,14 +30808,14 @@
         <v>291.666666666667</v>
       </c>
       <c r="H44" s="195" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I44" s="195"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="195"/>
       <c r="B45" s="195" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C45" s="200" t="n">
         <f aca="false">C21*$I$45</f>
@@ -30181,7 +30838,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I45" s="195" t="n">
         <v>0.09</v>
@@ -30190,7 +30847,7 @@
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="195"/>
       <c r="B46" s="195" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="C46" s="200" t="n">
         <f aca="false">C16*$I$46</f>
@@ -30213,7 +30870,7 @@
         <v>390</v>
       </c>
       <c r="H46" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I46" s="195" t="n">
         <v>0.1</v>
@@ -30222,7 +30879,7 @@
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="195"/>
       <c r="B47" s="195" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C47" s="200" t="n">
         <f aca="false">C20*$I$47</f>
@@ -30245,7 +30902,7 @@
         <v>-33</v>
       </c>
       <c r="H47" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I47" s="195" t="n">
         <v>0.11</v>
@@ -30254,7 +30911,7 @@
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="195"/>
       <c r="B48" s="195" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C48" s="200" t="n">
         <f aca="false">C19*$I$48</f>
@@ -30277,7 +30934,7 @@
         <v>831</v>
       </c>
       <c r="H48" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I48" s="195" t="n">
         <v>0.12</v>
@@ -30286,7 +30943,7 @@
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="195"/>
       <c r="B49" s="195" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C49" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C34:E34)</f>
@@ -30309,14 +30966,14 @@
         <v>20865</v>
       </c>
       <c r="H49" s="195" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="I49" s="195"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="195"/>
       <c r="B50" s="195" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C50" s="200" t="n">
         <f aca="false">C22*$I$50</f>
@@ -30339,7 +30996,7 @@
         <v>420.116666666666</v>
       </c>
       <c r="H50" s="195" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="I50" s="195" t="n">
         <v>0.13</v>
@@ -30412,14 +31069,14 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="211"/>
       <c r="B2" s="215" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C2" s="216" t="str">
         <f aca="false">Admin!L2</f>
         <v>2026-27</v>
       </c>
       <c r="D2" s="217" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="E2" s="217"/>
       <c r="F2" s="217"/>
@@ -30446,7 +31103,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="211"/>
       <c r="B5" s="222" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C5" s="222"/>
       <c r="D5" s="222"/>
@@ -30461,7 +31118,7 @@
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="211"/>
       <c r="B6" s="220" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C6" s="220" t="str">
         <f aca="false">C2</f>
@@ -30479,7 +31136,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="211"/>
       <c r="B7" s="222" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C7" s="222"/>
       <c r="D7" s="222"/>
@@ -30494,7 +31151,7 @@
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="211"/>
       <c r="B8" s="220" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C8" s="220" t="n">
         <f aca="false">Admin!N$11</f>
@@ -30516,7 +31173,7 @@
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="211"/>
       <c r="B9" s="220" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C9" s="220" t="n">
         <f aca="false">Admin!M$11</f>
@@ -30537,7 +31194,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="211"/>
       <c r="B10" s="220" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C10" s="220" t="n">
         <f aca="false">Admin!N$13</f>
@@ -30558,7 +31215,7 @@
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="211"/>
       <c r="B11" s="228" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C11" s="229"/>
       <c r="D11" s="230"/>
@@ -30573,7 +31230,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="211"/>
       <c r="B12" s="220" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C12" s="220"/>
       <c r="D12" s="234"/>
@@ -30588,7 +31245,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="211"/>
       <c r="B13" s="235" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C13" s="236" t="n">
         <f aca="false">Admin!B21</f>
@@ -30602,26 +31259,31 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="211"/>
-      <c r="B14" s="220"/>
+      <c r="B14" s="220" t="s">
+        <v>349</v>
+      </c>
       <c r="C14" s="220"/>
       <c r="D14" s="237"/>
-      <c r="E14" s="238"/>
+      <c r="E14" s="213" t="n">
+        <f aca="false">IF('SE Full'!D201&gt;0,IF(E7+'SE Full'!D201&lt;C9,(E7+'SE Full'!D201)*D8,C9*D8)+IF(E7+'SE Full'!D201&gt;C9,(MIN(E7+'SE Full'!D201,C10)-C9)*D9,0)+IF(E7+'SE Full'!D201&gt;C10,(E7+'SE Full'!D201-C10)*D10,0)-E11,0)</f>
+        <v>1735.81132243148</v>
+      </c>
       <c r="F14" s="214"/>
       <c r="G14" s="233"/>
       <c r="M14" s="224"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="211"/>
-      <c r="B15" s="239" t="s">
-        <v>335</v>
-      </c>
-      <c r="C15" s="239"/>
+      <c r="B15" s="238" t="s">
+        <v>350</v>
+      </c>
+      <c r="C15" s="238"/>
       <c r="D15" s="226" t="n">
         <f aca="false">Admin!L20</f>
         <v>0.06</v>
       </c>
-      <c r="E15" s="240" t="n">
-        <f aca="false">IF(E5&gt;Admin!N20,IF(E5&lt;Admin!N$23,(E5-Admin!N20)*D15,(Admin!N$23-Admin!N20)*D15),0)</f>
+      <c r="E15" s="239" t="n">
+        <f aca="false">IF((E5+'SE Full'!D201)&gt;Admin!N20,IF((E5+'SE Full'!D201)&lt;Admin!N$23,((E5+'SE Full'!D201)-Admin!N20)*D15,(Admin!N$23-Admin!N20)*D15),0)</f>
         <v>2262</v>
       </c>
       <c r="F15" s="214"/>
@@ -30630,17 +31292,17 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="211"/>
-      <c r="B16" s="239" t="s">
-        <v>336</v>
-      </c>
-      <c r="C16" s="239"/>
+      <c r="B16" s="238" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="238"/>
       <c r="D16" s="226" t="n">
         <f aca="false">Admin!L23</f>
         <v>0.02</v>
       </c>
-      <c r="E16" s="240" t="n">
-        <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1480.28301931506</v>
+      <c r="E16" s="239" t="n">
+        <f aca="false">IF(((E5+'SE Full'!D201)&gt;Admin!N$23),(((E5+'SE Full'!D201)-Admin!N$23)*D16),0)</f>
+        <v>1560.28301931506</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -30651,7 +31313,7 @@
       <c r="B17" s="220"/>
       <c r="C17" s="220"/>
       <c r="D17" s="237"/>
-      <c r="E17" s="238"/>
+      <c r="E17" s="240"/>
       <c r="F17" s="214"/>
       <c r="G17" s="233"/>
       <c r="M17" s="224"/>
@@ -30659,13 +31321,13 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="211"/>
       <c r="B18" s="241" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C18" s="241"/>
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>45744.7735987669</v>
+        <v>47560.5849211983</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -30676,7 +31338,7 @@
       <c r="B19" s="242"/>
       <c r="C19" s="242"/>
       <c r="D19" s="237"/>
-      <c r="E19" s="238"/>
+      <c r="E19" s="240"/>
       <c r="F19" s="214"/>
       <c r="G19" s="218"/>
     </row>
@@ -30685,18 +31347,18 @@
       <c r="B20" s="242"/>
       <c r="C20" s="242"/>
       <c r="D20" s="237"/>
-      <c r="E20" s="238"/>
+      <c r="E20" s="240"/>
       <c r="F20" s="214"/>
       <c r="G20" s="218"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="211"/>
       <c r="B21" s="228" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C21" s="243"/>
       <c r="D21" s="244" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="E21" s="244"/>
       <c r="F21" s="244"/>
@@ -30707,7 +31369,7 @@
       <c r="B22" s="220"/>
       <c r="C22" s="220"/>
       <c r="D22" s="237"/>
-      <c r="E22" s="238"/>
+      <c r="E22" s="240"/>
       <c r="F22" s="214"/>
       <c r="G22" s="233"/>
     </row>
@@ -30716,10 +31378,10 @@
       <c r="B23" s="220"/>
       <c r="C23" s="220"/>
       <c r="D23" s="246" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="E23" s="247" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="F23" s="248"/>
       <c r="G23" s="218"/>
@@ -31236,18 +31898,18 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="211"/>
       <c r="B25" s="220" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C25" s="250" t="str">
         <f aca="false">Admin!B24</f>
         <v>2027-28</v>
       </c>
       <c r="D25" s="251" t="s">
-        <v>343</v>
-      </c>
-      <c r="E25" s="240" t="n">
+        <v>358</v>
+      </c>
+      <c r="E25" s="239" t="n">
         <f aca="false">E18</f>
-        <v>45744.7735987669</v>
+        <v>47560.5849211983</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -31255,7 +31917,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="211"/>
       <c r="B26" s="220" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C26" s="220"/>
       <c r="D26" s="252" t="n">
@@ -31264,7 +31926,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>22872.3867993834</v>
+        <v>23780.2924605992</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -31272,7 +31934,7 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="211"/>
       <c r="B27" s="220" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C27" s="220"/>
       <c r="D27" s="252" t="n">
@@ -31281,7 +31943,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>22872.3867993834</v>
+        <v>23780.2924605992</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -31298,7 +31960,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="211"/>
       <c r="B29" s="253" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C29" s="254"/>
       <c r="D29" s="237"/>
@@ -31309,7 +31971,7 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="211"/>
       <c r="B30" s="255" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="C30" s="255"/>
       <c r="D30" s="211"/>
@@ -31320,7 +31982,7 @@
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="211"/>
       <c r="B31" s="258" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C31" s="258"/>
       <c r="D31" s="259"/>
@@ -31331,7 +31993,7 @@
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="211"/>
       <c r="B32" s="260" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="C32" s="258"/>
       <c r="D32" s="259"/>
@@ -31342,7 +32004,7 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="211"/>
       <c r="B33" s="254" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="C33" s="254"/>
       <c r="D33" s="259"/>
@@ -31353,7 +32015,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="211"/>
       <c r="B34" s="254" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C34" s="254"/>
       <c r="D34" s="259"/>
@@ -31364,7 +32026,7 @@
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="211"/>
       <c r="B35" s="254" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C35" s="254"/>
       <c r="D35" s="259"/>
@@ -31439,32 +32101,32 @@
     <row r="2" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="267"/>
       <c r="B2" s="268" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C2" s="269" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="D2" s="269" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="E2" s="269" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="F2" s="269" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="G2" s="269" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="H2" s="269" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="I2" s="269" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="J2" s="270"/>
       <c r="K2" s="268" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="L2" s="271"/>
       <c r="M2" s="272"/>
@@ -31716,7 +32378,7 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="267"/>
       <c r="B3" s="273" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="C3" s="273"/>
       <c r="D3" s="274"/>
@@ -32010,7 +32672,7 @@
       </c>
       <c r="J4" s="158"/>
       <c r="K4" s="278" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="L4" s="164"/>
     </row>
@@ -32164,7 +32826,7 @@
       </c>
       <c r="J8" s="158"/>
       <c r="K8" s="278" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="L8" s="164"/>
     </row>
@@ -32516,7 +33178,7 @@
       <c r="F1" s="287"/>
       <c r="G1" s="287"/>
       <c r="H1" s="288" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="I1" s="288"/>
       <c r="J1" s="288"/>
@@ -32524,7 +33186,7 @@
       <c r="L1" s="288"/>
       <c r="M1" s="287"/>
       <c r="N1" s="288" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="O1" s="288"/>
       <c r="P1" s="288"/>
@@ -32532,7 +33194,7 @@
       <c r="R1" s="288"/>
       <c r="S1" s="287"/>
       <c r="T1" s="288" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="U1" s="288"/>
       <c r="V1" s="288"/>
@@ -32552,63 +33214,63 @@
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="292"/>
       <c r="B2" s="293" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C2" s="294"/>
       <c r="D2" s="295" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="E2" s="296"/>
       <c r="F2" s="295" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G2" s="296"/>
       <c r="H2" s="297" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="I2" s="296"/>
       <c r="J2" s="295" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="K2" s="296"/>
       <c r="L2" s="295" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="M2" s="296"/>
       <c r="N2" s="297" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="O2" s="296"/>
       <c r="P2" s="295" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="Q2" s="296"/>
       <c r="R2" s="295" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="S2" s="296"/>
       <c r="T2" s="297" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="U2" s="296"/>
       <c r="V2" s="295" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="W2" s="296"/>
       <c r="X2" s="298" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="Y2" s="299"/>
       <c r="Z2" s="295" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="AA2" s="296"/>
       <c r="AB2" s="295" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="AC2" s="300"/>
       <c r="AD2" s="301" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="AE2" s="301"/>
       <c r="AF2" s="301"/>
@@ -32869,7 +33531,7 @@
       <c r="AB3" s="305"/>
       <c r="AC3" s="164"/>
       <c r="AD3" s="309" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="AE3" s="309"/>
       <c r="AF3" s="309"/>
@@ -32879,7 +33541,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="276"/>
       <c r="B4" s="310" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C4" s="310"/>
       <c r="D4" s="310"/>
@@ -33259,7 +33921,7 @@
       <c r="AB11" s="177"/>
       <c r="AC11" s="164"/>
       <c r="AD11" s="309" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="AE11" s="309"/>
       <c r="AF11" s="309"/>
@@ -33489,7 +34151,7 @@
       <c r="AB15" s="177"/>
       <c r="AC15" s="164"/>
       <c r="AD15" s="309" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="AE15" s="309"/>
       <c r="AF15" s="309"/>
@@ -33719,7 +34381,7 @@
       <c r="AB19" s="177"/>
       <c r="AC19" s="164"/>
       <c r="AD19" s="309" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="AE19" s="309"/>
       <c r="AF19" s="309"/>
@@ -33949,7 +34611,7 @@
       <c r="AB23" s="177"/>
       <c r="AC23" s="164"/>
       <c r="AD23" s="309" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="AE23" s="309"/>
       <c r="AF23" s="309"/>
@@ -34257,7 +34919,7 @@
       </c>
       <c r="AC28" s="164"/>
       <c r="AD28" s="309" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="AE28" s="309"/>
       <c r="AF28" s="309"/>
@@ -34475,10 +35137,10 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="158"/>
       <c r="B2" s="330" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="C2" s="161" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D2" s="162" t="n">
         <f aca="false">Admin!B5</f>
@@ -34598,7 +35260,7 @@
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="178"/>
       <c r="B5" s="332" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C5" s="170" t="n">
         <f aca="false">SUM(D5:O5)</f>
@@ -35157,7 +35819,7 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="158"/>
       <c r="B7" s="334" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C7" s="170" t="n">
         <f aca="false">SUM(D7:O7)</f>
@@ -35234,7 +35896,7 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="178"/>
       <c r="B9" s="333" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C9" s="170" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -35793,7 +36455,7 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="178"/>
       <c r="B11" s="332" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C11" s="170" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -36352,7 +37014,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="158"/>
       <c r="B13" s="333" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
@@ -36429,7 +37091,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="158"/>
       <c r="B15" s="332" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -36488,7 +37150,7 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="158"/>
       <c r="B16" s="334" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C16" s="170" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -36547,7 +37209,7 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="158"/>
       <c r="B17" s="335" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
@@ -36624,10 +37286,10 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="158"/>
       <c r="B19" s="337" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C19" s="161" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D19" s="162" t="n">
         <f aca="false">D2</f>
@@ -36760,7 +37422,7 @@
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="178"/>
       <c r="B22" s="332" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C22" s="170" t="n">
         <f aca="false">SUM(D22:O22)</f>
@@ -37319,7 +37981,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="158"/>
       <c r="B24" s="334" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C24" s="170" t="n">
         <f aca="false">SUM(D24:O24)</f>
@@ -37396,7 +38058,7 @@
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="178"/>
       <c r="B26" s="333" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C26" s="170" t="n">
         <f aca="false">SUM(D26:O26)</f>
@@ -37955,7 +38617,7 @@
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="178"/>
       <c r="B28" s="332" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C28" s="170" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -38514,7 +39176,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="158"/>
       <c r="B30" s="333" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -38591,7 +39253,7 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="158"/>
       <c r="B32" s="332" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
@@ -38650,7 +39312,7 @@
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="158"/>
       <c r="B33" s="334" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C33" s="170" t="n">
         <f aca="false">SUM(D33:O33)</f>
@@ -38709,7 +39371,7 @@
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="158"/>
       <c r="B34" s="335" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
@@ -38786,7 +39448,7 @@
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="158"/>
       <c r="B36" s="338" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="C36" s="338"/>
       <c r="D36" s="158"/>
@@ -38806,7 +39468,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="158"/>
       <c r="B37" s="169" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C37" s="339" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
@@ -38829,7 +39491,7 @@
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="158"/>
       <c r="B38" s="169" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="C38" s="339" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$AC$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
@@ -38852,7 +39514,7 @@
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="158"/>
       <c r="B39" s="169" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
@@ -38875,7 +39537,7 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="158"/>
       <c r="B40" s="182" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C40" s="339" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
@@ -38898,7 +39560,7 @@
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="158"/>
       <c r="B41" s="182" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
@@ -38921,7 +39583,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="158"/>
       <c r="B42" s="182" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="C42" s="339" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
@@ -38944,7 +39606,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="158"/>
       <c r="B43" s="182" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
@@ -38967,7 +39629,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="158"/>
       <c r="B44" s="182" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="C44" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
@@ -38990,7 +39652,7 @@
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="158"/>
       <c r="B45" s="182" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C45" s="339" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
@@ -39013,7 +39675,7 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="158"/>
       <c r="B46" s="182" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44+C45</f>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4906,7 +4906,7 @@
             <v>262.5</v>
           </cell>
           <cell r="W1">
-            <v>508.25</v>
+            <v>516.75</v>
           </cell>
           <cell r="X1">
             <v>76.6666666666667</v>
@@ -4951,7 +4951,7 @@
             <v>277.5</v>
           </cell>
           <cell r="W1">
-            <v>564</v>
+            <v>576</v>
           </cell>
           <cell r="X1">
             <v>126.666666666667</v>
@@ -4996,7 +4996,7 @@
             <v>192.5</v>
           </cell>
           <cell r="W1">
-            <v>560</v>
+            <v>580</v>
           </cell>
           <cell r="X1">
             <v>226.666666666667</v>
@@ -5041,7 +5041,7 @@
             <v>382.5</v>
           </cell>
           <cell r="W1">
-            <v>490.25</v>
+            <v>494.75</v>
           </cell>
           <cell r="X1">
             <v>76.6666666666667</v>
@@ -5086,7 +5086,7 @@
             <v>112.5</v>
           </cell>
           <cell r="W1">
-            <v>508.25</v>
+            <v>516.75</v>
           </cell>
           <cell r="X1">
             <v>116.666666666667</v>
@@ -5131,7 +5131,7 @@
             <v>202.5</v>
           </cell>
           <cell r="W1">
-            <v>602</v>
+            <v>618</v>
           </cell>
           <cell r="X1">
             <v>76.6666666666667</v>
@@ -5176,7 +5176,7 @@
             <v>262.5</v>
           </cell>
           <cell r="W1">
-            <v>512.75</v>
+            <v>522.25</v>
           </cell>
           <cell r="X1">
             <v>176.666666666667</v>
@@ -5221,7 +5221,7 @@
             <v>337.5</v>
           </cell>
           <cell r="W1">
-            <v>551</v>
+            <v>569</v>
           </cell>
           <cell r="X1">
             <v>136.666666666667</v>
@@ -5266,7 +5266,7 @@
             <v>212.5</v>
           </cell>
           <cell r="W1">
-            <v>519.5</v>
+            <v>530.5</v>
           </cell>
           <cell r="X1">
             <v>76.6666666666667</v>
@@ -5311,7 +5311,7 @@
             <v>427.5</v>
           </cell>
           <cell r="W1">
-            <v>538.25</v>
+            <v>546.75</v>
           </cell>
           <cell r="X1">
             <v>76.6666666666667</v>
@@ -5356,7 +5356,7 @@
             <v>112.5</v>
           </cell>
           <cell r="W1">
-            <v>501.5</v>
+            <v>508.5</v>
           </cell>
           <cell r="X1">
             <v>306.666666666667</v>
@@ -5401,7 +5401,7 @@
             <v>252.5</v>
           </cell>
           <cell r="W1">
-            <v>578.5</v>
+            <v>591.5</v>
           </cell>
           <cell r="X1">
             <v>76.6666666666667</v>
@@ -9961,7 +9961,7 @@
         <v>10000</v>
       </c>
       <c r="G21" s="361" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="H21" s="63"/>
       <c r="I21" s="366"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="D51" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26-'SE Full'!O78," ")</f>
-        <v>5988.1875</v>
+        <v>6090.5625</v>
       </c>
       <c r="E51" s="98"/>
       <c r="F51" s="98"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="O64" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'SE Full'!O122</f>
-        <v>146730.524833333</v>
+        <v>146832.899833333</v>
       </c>
       <c r="P64" s="98"/>
       <c r="Q64" s="98"/>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="D71" s="98" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>192469.475166666</v>
+        <v>192367.100166666</v>
       </c>
       <c r="E71" s="98"/>
       <c r="F71" s="98"/>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>127785.475166666</v>
+        <v>127683.100166666</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>129868.8085</v>
+        <v>129766.4335</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="D78" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26</f>
-        <v>7984.25</v>
+        <v>8120.75</v>
       </c>
       <c r="E78" s="98"/>
       <c r="F78" s="98"/>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="O78" s="98" t="n">
         <f aca="false">VitalTax!G39</f>
-        <v>1996.0625</v>
+        <v>2030.1875</v>
       </c>
       <c r="P78" s="98"/>
       <c r="Q78" s="98"/>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>176926.983333333</v>
+        <v>177063.483333333</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="O122" s="98" t="n">
         <f aca="false">O66+O70+O74+O78+O82+O86+O90+O94+O98+O102+O106+O110+O114+O118</f>
-        <v>30196.4585</v>
+        <v>30230.5835</v>
       </c>
       <c r="P122" s="98"/>
       <c r="Q122" s="98"/>
@@ -18841,7 +18841,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>162273.016666666</v>
+        <v>162136.516666666</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -20232,7 +20232,7 @@
       </c>
       <c r="D174" s="98" t="n">
         <f aca="false">O122+O160+D169</f>
-        <v>30836.4585</v>
+        <v>30870.5835</v>
       </c>
       <c r="E174" s="98"/>
       <c r="F174" s="98"/>
@@ -20254,7 +20254,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>122110.81763242</v>
+        <v>122008.44263242</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">MAX(0,O174-O179+N(D197)+D210+N(O190))</f>
-        <v>122200.81763242</v>
+        <v>122098.44263242</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>124284.150965753</v>
+        <v>124181.775965753</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -27804,55 +27804,55 @@
       </c>
       <c r="B25" s="170" t="n">
         <f aca="false">SUM(C25:N25)</f>
-        <v>6434.25</v>
+        <v>6570.75</v>
       </c>
       <c r="C25" s="171" t="n">
         <f aca="false">[3]Apr!$W$1</f>
-        <v>508.25</v>
+        <v>516.75</v>
       </c>
       <c r="D25" s="171" t="n">
         <f aca="false">[3]May!$W$1</f>
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="E25" s="172" t="n">
         <f aca="false">[3]Jun!$W$1</f>
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="F25" s="171" t="n">
         <f aca="false">[3]Jul!$W$1</f>
-        <v>490.25</v>
+        <v>494.75</v>
       </c>
       <c r="G25" s="171" t="n">
         <f aca="false">[3]Aug!$W$1</f>
-        <v>508.25</v>
+        <v>516.75</v>
       </c>
       <c r="H25" s="172" t="n">
         <f aca="false">[3]Sep!$W$1</f>
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="I25" s="171" t="n">
         <f aca="false">[3]Oct!$W$1</f>
-        <v>512.75</v>
+        <v>522.25</v>
       </c>
       <c r="J25" s="171" t="n">
         <f aca="false">[3]Nov!$W$1</f>
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="K25" s="172" t="n">
         <f aca="false">[3]Dec!$W$1</f>
-        <v>519.5</v>
+        <v>530.5</v>
       </c>
       <c r="L25" s="171" t="n">
         <f aca="false">[3]Jan!$W$1</f>
-        <v>538.25</v>
+        <v>546.75</v>
       </c>
       <c r="M25" s="171" t="n">
         <f aca="false">[3]Feb!$W$1</f>
-        <v>501.5</v>
+        <v>508.5</v>
       </c>
       <c r="N25" s="171" t="n">
         <f aca="false">[3]Mar!$W$1</f>
-        <v>578.5</v>
+        <v>591.5</v>
       </c>
       <c r="O25" s="164"/>
     </row>
@@ -28384,55 +28384,55 @@
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>156790.316666667</v>
+        <v>156926.816666667</v>
       </c>
       <c r="C35" s="170" t="n">
         <f aca="false">SUM(C21:C34)</f>
-        <v>12606.5333333333</v>
+        <v>12615.0333333333</v>
       </c>
       <c r="D35" s="170" t="n">
         <f aca="false">SUM(D21:D34)</f>
-        <v>11917.2833333333</v>
+        <v>11929.2833333333</v>
       </c>
       <c r="E35" s="170" t="n">
         <f aca="false">SUM(E21:E34)</f>
-        <v>14186.6166666667</v>
+        <v>14206.6166666667</v>
       </c>
       <c r="F35" s="174" t="n">
         <f aca="false">SUM(F21:F34)</f>
-        <v>14423.5333333333</v>
+        <v>14428.0333333333</v>
       </c>
       <c r="G35" s="170" t="n">
         <f aca="false">SUM(G21:G34)</f>
-        <v>12359.8666666667</v>
+        <v>12368.3666666667</v>
       </c>
       <c r="H35" s="170" t="n">
         <f aca="false">SUM(H21:H34)</f>
-        <v>13836.6166666667</v>
+        <v>13852.6166666667</v>
       </c>
       <c r="I35" s="174" t="n">
         <f aca="false">SUM(I21:I34)</f>
-        <v>14286.0333333333</v>
+        <v>14295.5333333333</v>
       </c>
       <c r="J35" s="170" t="n">
         <f aca="false">SUM(J21:J34)</f>
-        <v>11474.2833333333</v>
+        <v>11492.2833333333</v>
       </c>
       <c r="K35" s="170" t="n">
         <f aca="false">SUM(K21:K34)</f>
-        <v>16492.2833333333</v>
+        <v>16503.2833333333</v>
       </c>
       <c r="L35" s="174" t="n">
         <f aca="false">SUM(L21:L34)</f>
-        <v>11986.5333333333</v>
+        <v>11995.0333333333</v>
       </c>
       <c r="M35" s="170" t="n">
         <f aca="false">SUM(M21:M34)</f>
-        <v>11659.7833333333</v>
+        <v>11666.7833333333</v>
       </c>
       <c r="N35" s="170" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>11560.95</v>
+        <v>11573.95</v>
       </c>
       <c r="O35" s="164"/>
     </row>
@@ -28459,55 +28459,55 @@
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
-        <v>164356.35</v>
+        <v>164219.85</v>
       </c>
       <c r="C37" s="170" t="n">
         <f aca="false">C19-C35</f>
-        <v>14489.3</v>
+        <v>14480.8</v>
       </c>
       <c r="D37" s="170" t="n">
         <f aca="false">D19-D35</f>
-        <v>14508.55</v>
+        <v>14496.55</v>
       </c>
       <c r="E37" s="170" t="n">
         <f aca="false">E19-E35</f>
-        <v>10442.55</v>
+        <v>10422.55</v>
       </c>
       <c r="F37" s="174" t="n">
         <f aca="false">F19-F35</f>
-        <v>12502.3</v>
+        <v>12497.8</v>
       </c>
       <c r="G37" s="170" t="n">
         <f aca="false">G19-G35</f>
-        <v>16969.3</v>
+        <v>16960.8</v>
       </c>
       <c r="H37" s="170" t="n">
         <f aca="false">H19-H35</f>
-        <v>13589.2166666666</v>
+        <v>13573.2166666666</v>
       </c>
       <c r="I37" s="174" t="n">
         <f aca="false">I19-I35</f>
-        <v>14709.8</v>
+        <v>14700.3</v>
       </c>
       <c r="J37" s="170" t="n">
         <f aca="false">J19-J35</f>
-        <v>14551.55</v>
+        <v>14533.55</v>
       </c>
       <c r="K37" s="170" t="n">
         <f aca="false">K19-K35</f>
-        <v>10203.55</v>
+        <v>10192.55</v>
       </c>
       <c r="L37" s="174" t="n">
         <f aca="false">L19-L35</f>
-        <v>16689.3</v>
+        <v>16680.8</v>
       </c>
       <c r="M37" s="170" t="n">
         <f aca="false">M19-M35</f>
-        <v>15886.05</v>
+        <v>15879.05</v>
       </c>
       <c r="N37" s="170" t="n">
         <f aca="false">N19-N35</f>
-        <v>9814.8833333333</v>
+        <v>9801.8833333333</v>
       </c>
       <c r="O37" s="164"/>
     </row>
@@ -28575,55 +28575,55 @@
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
-        <v>164356.35</v>
+        <v>164219.85</v>
       </c>
       <c r="C39" s="170" t="n">
         <f aca="false">C37+C38</f>
-        <v>14489.3</v>
+        <v>14480.8</v>
       </c>
       <c r="D39" s="170" t="n">
         <f aca="false">D37+D38</f>
-        <v>14508.55</v>
+        <v>14496.55</v>
       </c>
       <c r="E39" s="170" t="n">
         <f aca="false">E37+E38</f>
-        <v>10442.55</v>
+        <v>10422.55</v>
       </c>
       <c r="F39" s="174" t="n">
         <f aca="false">F37+F38</f>
-        <v>12502.3</v>
+        <v>12497.8</v>
       </c>
       <c r="G39" s="170" t="n">
         <f aca="false">G37+G38</f>
-        <v>16969.3</v>
+        <v>16960.8</v>
       </c>
       <c r="H39" s="170" t="n">
         <f aca="false">H37+H38</f>
-        <v>13589.2166666666</v>
+        <v>13573.2166666666</v>
       </c>
       <c r="I39" s="174" t="n">
         <f aca="false">I37+I38</f>
-        <v>14709.8</v>
+        <v>14700.3</v>
       </c>
       <c r="J39" s="170" t="n">
         <f aca="false">J37+J38</f>
-        <v>14551.55</v>
+        <v>14533.55</v>
       </c>
       <c r="K39" s="170" t="n">
         <f aca="false">K37+K38</f>
-        <v>10203.55</v>
+        <v>10192.55</v>
       </c>
       <c r="L39" s="174" t="n">
         <f aca="false">L37+L38</f>
-        <v>16689.3</v>
+        <v>16680.8</v>
       </c>
       <c r="M39" s="170" t="n">
         <f aca="false">M37+M38</f>
-        <v>15886.05</v>
+        <v>15879.05</v>
       </c>
       <c r="N39" s="170" t="n">
         <f aca="false">N37+N38</f>
-        <v>9814.8833333333</v>
+        <v>9801.8833333333</v>
       </c>
       <c r="O39" s="164"/>
     </row>
@@ -28785,55 +28785,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>43131.5969999998</v>
+        <v>43046.9669999998</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3594.29974999998</v>
+        <v>3587.24724999998</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -28843,55 +28843,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>94224.7529999998</v>
+        <v>94172.8829999998</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>9895.00024999999</v>
+        <v>9893.55274999999</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>9914.25024999999</v>
+        <v>9909.30274999999</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>5848.25024999998</v>
+        <v>5835.30274999998</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>4908.00024999999</v>
+        <v>4910.55274999999</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>12375.00025</v>
+        <v>12373.55275</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>8994.91691666666</v>
+        <v>8985.96941666666</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7115.50024999999</v>
+        <v>7113.05274999999</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>9957.25024999999</v>
+        <v>9946.30274999999</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>5609.25024999998</v>
+        <v>5605.30274999998</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9095.00024999999</v>
+        <v>9093.55274999999</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11291.75025</v>
+        <v>11291.80275</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-779.416416666681</v>
+        <v>-785.36391666668</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -30152,23 +30152,23 @@
       </c>
       <c r="C17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
-        <v>2062.25</v>
+        <v>2102.75</v>
       </c>
       <c r="D17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F25:H26)</f>
-        <v>1870.5</v>
+        <v>1899.5</v>
       </c>
       <c r="E17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I25:K26)</f>
-        <v>1973.25</v>
+        <v>2011.75</v>
       </c>
       <c r="F17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L25:N26)</f>
-        <v>2078.25</v>
+        <v>2106.75</v>
       </c>
       <c r="G17" s="200" t="n">
         <f aca="false">SUM(C17:F17)</f>
-        <v>7984.25</v>
+        <v>8120.75</v>
       </c>
       <c r="H17" s="195"/>
       <c r="I17" s="195"/>
@@ -30437,23 +30437,23 @@
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
-        <v>45159.6</v>
+        <v>45200.1</v>
       </c>
       <c r="D29" s="203" t="n">
         <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D26)</f>
-        <v>43222.5166666667</v>
+        <v>43251.5166666667</v>
       </c>
       <c r="E29" s="203" t="n">
         <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E26)</f>
-        <v>46935.1</v>
+        <v>46973.6</v>
       </c>
       <c r="F29" s="203" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F26)</f>
-        <v>41609.7666666667</v>
+        <v>41638.2666666667</v>
       </c>
       <c r="G29" s="203" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G26)</f>
-        <v>176926.983333333</v>
+        <v>177063.483333333</v>
       </c>
       <c r="H29" s="204"/>
       <c r="I29" s="195"/>
@@ -30629,23 +30629,23 @@
       </c>
       <c r="C39" s="200" t="n">
         <f aca="false">C17*$I$39</f>
-        <v>515.5625</v>
+        <v>525.6875</v>
       </c>
       <c r="D39" s="200" t="n">
         <f aca="false">D17*$I$39</f>
-        <v>467.625</v>
+        <v>474.875</v>
       </c>
       <c r="E39" s="200" t="n">
         <f aca="false">E17*$I$39</f>
-        <v>493.3125</v>
+        <v>502.9375</v>
       </c>
       <c r="F39" s="200" t="n">
         <f aca="false">F17*$I$39</f>
-        <v>519.5625</v>
+        <v>526.6875</v>
       </c>
       <c r="G39" s="200" t="n">
         <f aca="false">SUM(C39:F39)</f>
-        <v>1996.0625</v>
+        <v>2030.1875</v>
       </c>
       <c r="H39" s="195" t="s">
         <v>332</v>
@@ -31109,7 +31109,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>124284.150965753</v>
+        <v>124181.775965753</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -31127,7 +31127,7 @@
       <c r="D6" s="225"/>
       <c r="E6" s="218" t="n">
         <f aca="false">IF(E5&lt;=0,0,MAX(0,Admin!N$4-MAX(0,E5-Admin!N$5)/2))</f>
-        <v>427.924517123494</v>
+        <v>479.112017123494</v>
       </c>
       <c r="F6" s="214"/>
       <c r="G6" s="218"/>
@@ -31142,7 +31142,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>123856.22644863</v>
+        <v>123702.66394863</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="E9" s="213" t="n">
         <f aca="false">IF(E7&gt;C9,(MIN(E7,C10)-C9)*D9,0)</f>
-        <v>34462.4905794518</v>
+        <v>34401.0655794518</v>
       </c>
       <c r="F9" s="214"/>
       <c r="G9" s="218"/>
@@ -31221,7 +31221,7 @@
       <c r="D11" s="230"/>
       <c r="E11" s="231" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>42002.4905794518</v>
+        <v>41941.0655794518</v>
       </c>
       <c r="F11" s="232"/>
       <c r="G11" s="233"/>
@@ -31266,7 +31266,7 @@
       <c r="D14" s="237"/>
       <c r="E14" s="213" t="n">
         <f aca="false">IF('SE Full'!D201&gt;0,IF(E7+'SE Full'!D201&lt;C9,(E7+'SE Full'!D201)*D8,C9*D8)+IF(E7+'SE Full'!D201&gt;C9,(MIN(E7+'SE Full'!D201,C10)-C9)*D9,0)+IF(E7+'SE Full'!D201&gt;C10,(E7+'SE Full'!D201-C10)*D10,0)-E11,0)</f>
-        <v>1735.81132243148</v>
+        <v>1728.13319743147</v>
       </c>
       <c r="F14" s="214"/>
       <c r="G14" s="233"/>
@@ -31302,7 +31302,7 @@
       </c>
       <c r="E16" s="239" t="n">
         <f aca="false">IF(((E5+'SE Full'!D201)&gt;Admin!N$23),(((E5+'SE Full'!D201)-Admin!N$23)*D16),0)</f>
-        <v>1560.28301931506</v>
+        <v>1558.23551931506</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -31327,7 +31327,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>47560.5849211983</v>
+        <v>47489.4342961983</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -31909,7 +31909,7 @@
       </c>
       <c r="E25" s="239" t="n">
         <f aca="false">E18</f>
-        <v>47560.5849211983</v>
+        <v>47489.4342961983</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23780.2924605992</v>
+        <v>23744.7171480992</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23780.2924605992</v>
+        <v>23744.7171480992</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -37018,55 +37018,55 @@
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>156790.316666667</v>
+        <v>156926.816666667</v>
       </c>
       <c r="D13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
-        <v>12606.5333333333</v>
+        <v>12615.0333333333</v>
       </c>
       <c r="E13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D35</f>
-        <v>11917.2833333333</v>
+        <v>11929.2833333333</v>
       </c>
       <c r="F13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E35</f>
-        <v>14186.6166666667</v>
+        <v>14206.6166666667</v>
       </c>
       <c r="G13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F35</f>
-        <v>14423.5333333333</v>
+        <v>14428.0333333333</v>
       </c>
       <c r="H13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G35</f>
-        <v>12359.8666666667</v>
+        <v>12368.3666666667</v>
       </c>
       <c r="I13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
-        <v>13836.6166666667</v>
+        <v>13852.6166666667</v>
       </c>
       <c r="J13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I35</f>
-        <v>14286.0333333333</v>
+        <v>14295.5333333333</v>
       </c>
       <c r="K13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J35</f>
-        <v>11474.2833333333</v>
+        <v>11492.2833333333</v>
       </c>
       <c r="L13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K35</f>
-        <v>16492.2833333333</v>
+        <v>16503.2833333333</v>
       </c>
       <c r="M13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L35</f>
-        <v>11986.5333333333</v>
+        <v>11995.0333333333</v>
       </c>
       <c r="N13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M35</f>
-        <v>11659.7833333333</v>
+        <v>11666.7833333333</v>
       </c>
       <c r="O13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>11560.95</v>
+        <v>11573.95</v>
       </c>
       <c r="P13" s="158"/>
     </row>
@@ -37095,55 +37095,55 @@
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>164356.35</v>
+        <v>164219.85</v>
       </c>
       <c r="D15" s="170" t="n">
         <f aca="false">D11-D13</f>
-        <v>14489.3</v>
+        <v>14480.8</v>
       </c>
       <c r="E15" s="170" t="n">
         <f aca="false">E11-E13</f>
-        <v>14508.55</v>
+        <v>14496.55</v>
       </c>
       <c r="F15" s="170" t="n">
         <f aca="false">F11-F13</f>
-        <v>10442.55</v>
+        <v>10422.55</v>
       </c>
       <c r="G15" s="170" t="n">
         <f aca="false">G11-G13</f>
-        <v>12502.3</v>
+        <v>12497.8</v>
       </c>
       <c r="H15" s="170" t="n">
         <f aca="false">H11-H13</f>
-        <v>16969.3</v>
+        <v>16960.8</v>
       </c>
       <c r="I15" s="170" t="n">
         <f aca="false">I11-I13</f>
-        <v>13589.2166666666</v>
+        <v>13573.2166666666</v>
       </c>
       <c r="J15" s="170" t="n">
         <f aca="false">J11-J13</f>
-        <v>14709.8</v>
+        <v>14700.3</v>
       </c>
       <c r="K15" s="170" t="n">
         <f aca="false">K11-K13</f>
-        <v>14551.55</v>
+        <v>14533.55</v>
       </c>
       <c r="L15" s="170" t="n">
         <f aca="false">L11-L13</f>
-        <v>10203.55</v>
+        <v>10192.55</v>
       </c>
       <c r="M15" s="170" t="n">
         <f aca="false">M11-M13</f>
-        <v>16689.3</v>
+        <v>16680.8</v>
       </c>
       <c r="N15" s="170" t="n">
         <f aca="false">N11-N13</f>
-        <v>15886.05</v>
+        <v>15879.05</v>
       </c>
       <c r="O15" s="170" t="n">
         <f aca="false">O11-O13</f>
-        <v>9814.8833333333</v>
+        <v>9801.8833333333</v>
       </c>
       <c r="P15" s="158"/>
     </row>
@@ -37213,55 +37213,55 @@
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>164356.35</v>
+        <v>164219.85</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">D15+D16</f>
-        <v>14489.3</v>
+        <v>14480.8</v>
       </c>
       <c r="E17" s="170" t="n">
         <f aca="false">E15+E16</f>
-        <v>14508.55</v>
+        <v>14496.55</v>
       </c>
       <c r="F17" s="170" t="n">
         <f aca="false">F15+F16</f>
-        <v>10442.55</v>
+        <v>10422.55</v>
       </c>
       <c r="G17" s="170" t="n">
         <f aca="false">G15+G16</f>
-        <v>12502.3</v>
+        <v>12497.8</v>
       </c>
       <c r="H17" s="170" t="n">
         <f aca="false">H15+H16</f>
-        <v>16969.3</v>
+        <v>16960.8</v>
       </c>
       <c r="I17" s="170" t="n">
         <f aca="false">I15+I16</f>
-        <v>13589.2166666666</v>
+        <v>13573.2166666666</v>
       </c>
       <c r="J17" s="170" t="n">
         <f aca="false">J15+J16</f>
-        <v>14709.8</v>
+        <v>14700.3</v>
       </c>
       <c r="K17" s="170" t="n">
         <f aca="false">K15+K16</f>
-        <v>14551.55</v>
+        <v>14533.55</v>
       </c>
       <c r="L17" s="170" t="n">
         <f aca="false">L15+L16</f>
-        <v>10203.55</v>
+        <v>10192.55</v>
       </c>
       <c r="M17" s="170" t="n">
         <f aca="false">M15+M16</f>
-        <v>16689.3</v>
+        <v>16680.8</v>
       </c>
       <c r="N17" s="170" t="n">
         <f aca="false">N15+N16</f>
-        <v>15886.05</v>
+        <v>15879.05</v>
       </c>
       <c r="O17" s="170" t="n">
         <f aca="false">O15+O16</f>
-        <v>9814.8833333333</v>
+        <v>9801.8833333333</v>
       </c>
       <c r="P17" s="158"/>
     </row>
@@ -39180,55 +39180,55 @@
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>156790.316666667</v>
+        <v>156926.816666667</v>
       </c>
       <c r="D30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
-        <v>12606.5333333333</v>
+        <v>12615.0333333333</v>
       </c>
       <c r="E30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E13,C13/C21),0)</f>
-        <v>11917.2833333333</v>
+        <v>11929.2833333333</v>
       </c>
       <c r="F30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F13,C13/C21),0)</f>
-        <v>14186.6166666667</v>
+        <v>14206.6166666667</v>
       </c>
       <c r="G30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G13,C13/C21),0)</f>
-        <v>14423.5333333333</v>
+        <v>14428.0333333333</v>
       </c>
       <c r="H30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H13,C13/C21),0)</f>
-        <v>12359.8666666667</v>
+        <v>12368.3666666667</v>
       </c>
       <c r="I30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
-        <v>13836.6166666667</v>
+        <v>13852.6166666667</v>
       </c>
       <c r="J30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J13,C13/C21),0)</f>
-        <v>14286.0333333333</v>
+        <v>14295.5333333333</v>
       </c>
       <c r="K30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K13,C13/C21),0)</f>
-        <v>11474.2833333333</v>
+        <v>11492.2833333333</v>
       </c>
       <c r="L30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L13,C13/C21),0)</f>
-        <v>16492.2833333333</v>
+        <v>16503.2833333333</v>
       </c>
       <c r="M30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M13,C13/C21),0)</f>
-        <v>11986.5333333333</v>
+        <v>11995.0333333333</v>
       </c>
       <c r="N30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N13,C13/C21),0)</f>
-        <v>11659.7833333333</v>
+        <v>11666.7833333333</v>
       </c>
       <c r="O30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>11560.95</v>
+        <v>11573.95</v>
       </c>
       <c r="P30" s="158"/>
     </row>
@@ -39257,55 +39257,55 @@
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>164356.35</v>
+        <v>164219.85</v>
       </c>
       <c r="D32" s="170" t="n">
         <f aca="false">D28-D30</f>
-        <v>14489.3</v>
+        <v>14480.8</v>
       </c>
       <c r="E32" s="170" t="n">
         <f aca="false">E28-E30</f>
-        <v>14508.55</v>
+        <v>14496.55</v>
       </c>
       <c r="F32" s="170" t="n">
         <f aca="false">F28-F30</f>
-        <v>10442.55</v>
+        <v>10422.55</v>
       </c>
       <c r="G32" s="170" t="n">
         <f aca="false">G28-G30</f>
-        <v>12502.3</v>
+        <v>12497.8</v>
       </c>
       <c r="H32" s="170" t="n">
         <f aca="false">H28-H30</f>
-        <v>16969.3</v>
+        <v>16960.8</v>
       </c>
       <c r="I32" s="170" t="n">
         <f aca="false">I28-I30</f>
-        <v>13589.2166666666</v>
+        <v>13573.2166666666</v>
       </c>
       <c r="J32" s="170" t="n">
         <f aca="false">J28-J30</f>
-        <v>14709.8</v>
+        <v>14700.3</v>
       </c>
       <c r="K32" s="170" t="n">
         <f aca="false">K28-K30</f>
-        <v>14551.55</v>
+        <v>14533.55</v>
       </c>
       <c r="L32" s="170" t="n">
         <f aca="false">L28-L30</f>
-        <v>10203.55</v>
+        <v>10192.55</v>
       </c>
       <c r="M32" s="170" t="n">
         <f aca="false">M28-M30</f>
-        <v>16689.3</v>
+        <v>16680.8</v>
       </c>
       <c r="N32" s="170" t="n">
         <f aca="false">N28-N30</f>
-        <v>15886.05</v>
+        <v>15879.05</v>
       </c>
       <c r="O32" s="170" t="n">
         <f aca="false">O28-O30</f>
-        <v>9814.8833333333</v>
+        <v>9801.8833333333</v>
       </c>
       <c r="P32" s="158"/>
     </row>
@@ -39375,55 +39375,55 @@
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>164356.35</v>
+        <v>164219.85</v>
       </c>
       <c r="D34" s="170" t="n">
         <f aca="false">D32+D33</f>
-        <v>14489.3</v>
+        <v>14480.8</v>
       </c>
       <c r="E34" s="170" t="n">
         <f aca="false">E32+E33</f>
-        <v>14508.55</v>
+        <v>14496.55</v>
       </c>
       <c r="F34" s="170" t="n">
         <f aca="false">F32+F33</f>
-        <v>10442.55</v>
+        <v>10422.55</v>
       </c>
       <c r="G34" s="170" t="n">
         <f aca="false">G32+G33</f>
-        <v>12502.3</v>
+        <v>12497.8</v>
       </c>
       <c r="H34" s="170" t="n">
         <f aca="false">H32+H33</f>
-        <v>16969.3</v>
+        <v>16960.8</v>
       </c>
       <c r="I34" s="170" t="n">
         <f aca="false">I32+I33</f>
-        <v>13589.2166666666</v>
+        <v>13573.2166666666</v>
       </c>
       <c r="J34" s="170" t="n">
         <f aca="false">J32+J33</f>
-        <v>14709.8</v>
+        <v>14700.3</v>
       </c>
       <c r="K34" s="170" t="n">
         <f aca="false">K32+K33</f>
-        <v>14551.55</v>
+        <v>14533.55</v>
       </c>
       <c r="L34" s="170" t="n">
         <f aca="false">L32+L33</f>
-        <v>10203.55</v>
+        <v>10192.55</v>
       </c>
       <c r="M34" s="170" t="n">
         <f aca="false">M32+M33</f>
-        <v>16689.3</v>
+        <v>16680.8</v>
       </c>
       <c r="N34" s="170" t="n">
         <f aca="false">N32+N33</f>
-        <v>15886.05</v>
+        <v>15879.05</v>
       </c>
       <c r="O34" s="170" t="n">
         <f aca="false">O32+O33</f>
-        <v>9814.8833333333</v>
+        <v>9801.8833333333</v>
       </c>
       <c r="P34" s="158"/>
     </row>
@@ -39518,7 +39518,7 @@
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>120069.35</v>
+        <v>119932.85</v>
       </c>
       <c r="D39" s="158"/>
       <c r="E39" s="158"/>
@@ -39541,7 +39541,7 @@
       </c>
       <c r="C40" s="339" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>2535.3250000002</v>
+        <v>2603.5750000002</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -39564,7 +39564,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>117534.024999999</v>
+        <v>117329.274999999</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -39610,7 +39610,7 @@
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>31933.6099999998</v>
+        <v>31851.7099999998</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -39656,7 +39656,7 @@
       </c>
       <c r="C45" s="339" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3657.98699999999</v>
+        <v>3655.25699999999</v>
       </c>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
@@ -39679,7 +39679,7 @@
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44+C45</f>
-        <v>43131.5969999998</v>
+        <v>43046.9669999998</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4843,7 +4843,7 @@
             <v>0</v>
           </cell>
           <cell r="U1">
-            <v>300</v>
+            <v>-300</v>
           </cell>
         </row>
         <row r="1">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="O60" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33-'SE Full'!O94-'SE Full'!O106-'SE Full'!O118," ")</f>
-        <v>6189.21666666666</v>
+        <v>6723.21666666666</v>
       </c>
       <c r="P60" s="98"/>
       <c r="Q60" s="98"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="O64" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'SE Full'!O122</f>
-        <v>146832.899833333</v>
+        <v>147366.899833333</v>
       </c>
       <c r="P64" s="98"/>
       <c r="Q64" s="98"/>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="D71" s="98" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>192367.100166666</v>
+        <v>191833.100166666</v>
       </c>
       <c r="E71" s="98"/>
       <c r="F71" s="98"/>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>127683.100166666</v>
+        <v>127149.100166666</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>129766.4335</v>
+        <v>129232.4335</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B29</f>
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="O106" s="98" t="n">
         <f aca="false">VitalTax!G47</f>
-        <v>-33</v>
+        <v>33</v>
       </c>
       <c r="P106" s="98"/>
       <c r="Q106" s="98"/>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>177063.483333333</v>
+        <v>177663.483333333</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="O122" s="98" t="n">
         <f aca="false">O66+O70+O74+O78+O82+O86+O90+O94+O98+O102+O106+O110+O114+O118</f>
-        <v>30230.5835</v>
+        <v>30296.5835</v>
       </c>
       <c r="P122" s="98"/>
       <c r="Q122" s="98"/>
@@ -18841,7 +18841,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>162136.516666666</v>
+        <v>161536.516666666</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -20232,7 +20232,7 @@
       </c>
       <c r="D174" s="98" t="n">
         <f aca="false">O122+O160+D169</f>
-        <v>30870.5835</v>
+        <v>30936.5835</v>
       </c>
       <c r="E174" s="98"/>
       <c r="F174" s="98"/>
@@ -20254,7 +20254,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>122008.44263242</v>
+        <v>121474.44263242</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">MAX(0,O174-O179+N(D197)+D210+N(O190))</f>
-        <v>122098.44263242</v>
+        <v>121564.44263242</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>124181.775965753</v>
+        <v>123647.775965753</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -28036,7 +28036,7 @@
       </c>
       <c r="B29" s="170" t="n">
         <f aca="false">SUM(C29:N29)</f>
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="C29" s="171" t="n">
         <f aca="false">-[2]Apr!$U$1</f>
@@ -28084,7 +28084,7 @@
       </c>
       <c r="N29" s="171" t="n">
         <f aca="false">-[2]Mar!$U$1</f>
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="O29" s="164"/>
     </row>
@@ -28384,7 +28384,7 @@
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>156926.816666667</v>
+        <v>157526.816666667</v>
       </c>
       <c r="C35" s="170" t="n">
         <f aca="false">SUM(C21:C34)</f>
@@ -28432,7 +28432,7 @@
       </c>
       <c r="N35" s="170" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>11573.95</v>
+        <v>12173.95</v>
       </c>
       <c r="O35" s="164"/>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
-        <v>164219.85</v>
+        <v>163619.85</v>
       </c>
       <c r="C37" s="170" t="n">
         <f aca="false">C19-C35</f>
@@ -28507,7 +28507,7 @@
       </c>
       <c r="N37" s="170" t="n">
         <f aca="false">N19-N35</f>
-        <v>9801.8833333333</v>
+        <v>9201.8833333333</v>
       </c>
       <c r="O37" s="164"/>
     </row>
@@ -28575,7 +28575,7 @@
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
-        <v>164219.85</v>
+        <v>163619.85</v>
       </c>
       <c r="C39" s="170" t="n">
         <f aca="false">C37+C38</f>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="N39" s="170" t="n">
         <f aca="false">N37+N38</f>
-        <v>9801.8833333333</v>
+        <v>9201.8833333333</v>
       </c>
       <c r="O39" s="164"/>
     </row>
@@ -28785,55 +28785,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>43046.9669999998</v>
+        <v>42674.9669999998</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3587.24724999998</v>
+        <v>3556.24724999998</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -28843,55 +28843,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>94172.8829999998</v>
+        <v>93944.8829999998</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>9893.55274999999</v>
+        <v>9924.55274999999</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>9909.30274999999</v>
+        <v>9940.30274999999</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>5835.30274999998</v>
+        <v>5866.30274999998</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>4910.55274999999</v>
+        <v>4941.55274999999</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>12373.55275</v>
+        <v>12404.55275</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>8985.96941666666</v>
+        <v>9016.96941666666</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7113.05274999999</v>
+        <v>7144.05274999999</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>9946.30274999999</v>
+        <v>9977.30274999999</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>5605.30274999998</v>
+        <v>5636.30274999998</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9093.55274999999</v>
+        <v>9124.55274999999</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11291.80275</v>
+        <v>11322.80275</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-785.36391666668</v>
+        <v>-1354.36391666668</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -30248,11 +30248,11 @@
       </c>
       <c r="F20" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L29:N29)</f>
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="G20" s="200" t="n">
         <f aca="false">SUM(C20:F20)</f>
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="H20" s="195"/>
       <c r="I20" s="195"/>
@@ -30449,11 +30449,11 @@
       </c>
       <c r="F29" s="203" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F26)</f>
-        <v>41638.2666666667</v>
+        <v>42238.2666666667</v>
       </c>
       <c r="G29" s="203" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G26)</f>
-        <v>177063.483333333</v>
+        <v>177663.483333333</v>
       </c>
       <c r="H29" s="204"/>
       <c r="I29" s="195"/>
@@ -30895,11 +30895,11 @@
       </c>
       <c r="F47" s="200" t="n">
         <f aca="false">F20*$I$47</f>
-        <v>-33</v>
+        <v>33</v>
       </c>
       <c r="G47" s="200" t="n">
         <f aca="false">SUM(C47:F47)</f>
-        <v>-33</v>
+        <v>33</v>
       </c>
       <c r="H47" s="195" t="s">
         <v>332</v>
@@ -31109,7 +31109,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>124181.775965753</v>
+        <v>123647.775965753</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -31127,7 +31127,7 @@
       <c r="D6" s="225"/>
       <c r="E6" s="218" t="n">
         <f aca="false">IF(E5&lt;=0,0,MAX(0,Admin!N$4-MAX(0,E5-Admin!N$5)/2))</f>
-        <v>479.112017123494</v>
+        <v>746.112017123494</v>
       </c>
       <c r="F6" s="214"/>
       <c r="G6" s="218"/>
@@ -31142,7 +31142,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>123702.66394863</v>
+        <v>122901.66394863</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="E9" s="213" t="n">
         <f aca="false">IF(E7&gt;C9,(MIN(E7,C10)-C9)*D9,0)</f>
-        <v>34401.0655794518</v>
+        <v>34080.6655794518</v>
       </c>
       <c r="F9" s="214"/>
       <c r="G9" s="218"/>
@@ -31221,7 +31221,7 @@
       <c r="D11" s="230"/>
       <c r="E11" s="231" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>41941.0655794518</v>
+        <v>41620.6655794518</v>
       </c>
       <c r="F11" s="232"/>
       <c r="G11" s="233"/>
@@ -31266,7 +31266,7 @@
       <c r="D14" s="237"/>
       <c r="E14" s="213" t="n">
         <f aca="false">IF('SE Full'!D201&gt;0,IF(E7+'SE Full'!D201&lt;C9,(E7+'SE Full'!D201)*D8,C9*D8)+IF(E7+'SE Full'!D201&gt;C9,(MIN(E7+'SE Full'!D201,C10)-C9)*D9,0)+IF(E7+'SE Full'!D201&gt;C10,(E7+'SE Full'!D201-C10)*D10,0)-E11,0)</f>
-        <v>1728.13319743147</v>
+        <v>1688.08319743147</v>
       </c>
       <c r="F14" s="214"/>
       <c r="G14" s="233"/>
@@ -31302,7 +31302,7 @@
       </c>
       <c r="E16" s="239" t="n">
         <f aca="false">IF(((E5+'SE Full'!D201)&gt;Admin!N$23),(((E5+'SE Full'!D201)-Admin!N$23)*D16),0)</f>
-        <v>1558.23551931506</v>
+        <v>1547.55551931506</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -31327,7 +31327,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>47489.4342961983</v>
+        <v>47118.3042961983</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -31909,7 +31909,7 @@
       </c>
       <c r="E25" s="239" t="n">
         <f aca="false">E18</f>
-        <v>47489.4342961983</v>
+        <v>47118.3042961983</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23744.7171480992</v>
+        <v>23559.1521480992</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>23744.7171480992</v>
+        <v>23559.1521480992</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -37018,7 +37018,7 @@
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>156926.816666667</v>
+        <v>157526.816666667</v>
       </c>
       <c r="D13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
@@ -37066,7 +37066,7 @@
       </c>
       <c r="O13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>11573.95</v>
+        <v>12173.95</v>
       </c>
       <c r="P13" s="158"/>
     </row>
@@ -37095,7 +37095,7 @@
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>164219.85</v>
+        <v>163619.85</v>
       </c>
       <c r="D15" s="170" t="n">
         <f aca="false">D11-D13</f>
@@ -37143,7 +37143,7 @@
       </c>
       <c r="O15" s="170" t="n">
         <f aca="false">O11-O13</f>
-        <v>9801.8833333333</v>
+        <v>9201.8833333333</v>
       </c>
       <c r="P15" s="158"/>
     </row>
@@ -37213,7 +37213,7 @@
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>164219.85</v>
+        <v>163619.85</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">D15+D16</f>
@@ -37261,7 +37261,7 @@
       </c>
       <c r="O17" s="170" t="n">
         <f aca="false">O15+O16</f>
-        <v>9801.8833333333</v>
+        <v>9201.8833333333</v>
       </c>
       <c r="P17" s="158"/>
     </row>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>156926.816666667</v>
+        <v>157526.816666667</v>
       </c>
       <c r="D30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
@@ -39228,7 +39228,7 @@
       </c>
       <c r="O30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>11573.95</v>
+        <v>12173.95</v>
       </c>
       <c r="P30" s="158"/>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>164219.85</v>
+        <v>163619.85</v>
       </c>
       <c r="D32" s="170" t="n">
         <f aca="false">D28-D30</f>
@@ -39305,7 +39305,7 @@
       </c>
       <c r="O32" s="170" t="n">
         <f aca="false">O28-O30</f>
-        <v>9801.8833333333</v>
+        <v>9201.8833333333</v>
       </c>
       <c r="P32" s="158"/>
     </row>
@@ -39375,7 +39375,7 @@
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>164219.85</v>
+        <v>163619.85</v>
       </c>
       <c r="D34" s="170" t="n">
         <f aca="false">D32+D33</f>
@@ -39423,7 +39423,7 @@
       </c>
       <c r="O34" s="170" t="n">
         <f aca="false">O32+O33</f>
-        <v>9801.8833333333</v>
+        <v>9201.8833333333</v>
       </c>
       <c r="P34" s="158"/>
     </row>
@@ -39518,7 +39518,7 @@
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>119932.85</v>
+        <v>119332.85</v>
       </c>
       <c r="D39" s="158"/>
       <c r="E39" s="158"/>
@@ -39541,7 +39541,7 @@
       </c>
       <c r="C40" s="339" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>2603.5750000002</v>
+        <v>2903.5750000002</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -39564,7 +39564,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>117329.274999999</v>
+        <v>116429.274999999</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -39610,7 +39610,7 @@
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>31851.7099999998</v>
+        <v>31491.7099999998</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -39656,7 +39656,7 @@
       </c>
       <c r="C45" s="339" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3655.25699999999</v>
+        <v>3643.25699999999</v>
       </c>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
@@ -39679,7 +39679,7 @@
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44+C45</f>
-        <v>43046.9669999998</v>
+        <v>42674.9669999998</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>
